--- a/詳細設計＿練習.xlsx
+++ b/詳細設計＿練習.xlsx
@@ -5,14 +5,15 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SudeepFuji\Documents\Study\設計書\基本設計書練習\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SudeepFuji\Documents\Study\Java\bookstore\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="12760"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="12760" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Rough＿企画" sheetId="1" r:id="rId1"/>
+    <sheet name="表紙" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -586,4 +587,13 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/詳細設計＿練習.xlsx
+++ b/詳細設計＿練習.xlsx
@@ -9,11 +9,17 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="12760" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="12760" activeTab="5"/>
   </bookViews>
   <sheets>
-    <sheet name="Rough＿企画" sheetId="1" r:id="rId1"/>
-    <sheet name="表紙" sheetId="2" r:id="rId2"/>
+    <sheet name="表紙" sheetId="2" r:id="rId1"/>
+    <sheet name="更新履歴" sheetId="3" r:id="rId2"/>
+    <sheet name="内容" sheetId="4" r:id="rId3"/>
+    <sheet name="DB項目定義・テーブル名" sheetId="5" r:id="rId4"/>
+    <sheet name="シーケンス図計画" sheetId="6" r:id="rId5"/>
+    <sheet name="シーケンス図" sheetId="7" r:id="rId6"/>
+    <sheet name="Rough＿企画" sheetId="1" r:id="rId7"/>
+    <sheet name="概要" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="154">
   <si>
     <t>レイアウト</t>
   </si>
@@ -45,9 +51,6 @@
     <t>入門シート</t>
   </si>
   <si>
-    <t>３．</t>
-  </si>
-  <si>
     <t>本体</t>
   </si>
   <si>
@@ -118,16 +121,410 @@
   </si>
   <si>
     <t>※RagプロジェクトのTicket機能→　調査</t>
+  </si>
+  <si>
+    <t>プロジェクト番号</t>
+  </si>
+  <si>
+    <t>XXX-2026</t>
+  </si>
+  <si>
+    <t>作成者</t>
+  </si>
+  <si>
+    <t>作成日</t>
+  </si>
+  <si>
+    <t>スディプスベディ</t>
+  </si>
+  <si>
+    <t>システムID</t>
+  </si>
+  <si>
+    <t>システム名称</t>
+  </si>
+  <si>
+    <t>最終更新者</t>
+  </si>
+  <si>
+    <t>最終更新日</t>
+  </si>
+  <si>
+    <t>SYS-1023</t>
+  </si>
+  <si>
+    <t>本システム</t>
+  </si>
+  <si>
+    <t>○○○○株式会社</t>
+  </si>
+  <si>
+    <t>○○○○部</t>
+  </si>
+  <si>
+    <t>詳細設計</t>
+  </si>
+  <si>
+    <t>変更履歴</t>
+  </si>
+  <si>
+    <t>No.</t>
+  </si>
+  <si>
+    <t>更新者</t>
+  </si>
+  <si>
+    <t>更新日</t>
+  </si>
+  <si>
+    <t>更新内容</t>
+  </si>
+  <si>
+    <t>備考</t>
+  </si>
+  <si>
+    <t>１</t>
+  </si>
+  <si>
+    <t>スベディスディプ</t>
+  </si>
+  <si>
+    <t>スベディ</t>
+  </si>
+  <si>
+    <t>詳細設計初期化作成</t>
+  </si>
+  <si>
+    <t>システム名</t>
+  </si>
+  <si>
+    <t>サブシステム名</t>
+  </si>
+  <si>
+    <t>ー</t>
+  </si>
+  <si>
+    <t>３</t>
+  </si>
+  <si>
+    <t>４．</t>
+  </si>
+  <si>
+    <t>DB項目定義・テーブル名</t>
+  </si>
+  <si>
+    <t>テーブル名</t>
+  </si>
+  <si>
+    <t>Books</t>
+  </si>
+  <si>
+    <t>列名</t>
+  </si>
+  <si>
+    <t>データ型</t>
+  </si>
+  <si>
+    <t>主キー</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>〇</t>
+  </si>
+  <si>
+    <t>BigInt</t>
+  </si>
+  <si>
+    <t>Author</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>isbn</t>
+  </si>
+  <si>
+    <t>String</t>
+  </si>
+  <si>
+    <t>自動増えすID</t>
+  </si>
+  <si>
+    <t>null</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>デフォルト値</t>
+  </si>
+  <si>
+    <t>Null</t>
+  </si>
+  <si>
+    <t>ウェブブラウザ</t>
+  </si>
+  <si>
+    <t>BookController</t>
+  </si>
+  <si>
+    <t>// GET /api/books - 全部本取得する</t>
+  </si>
+  <si>
+    <t>// POST /api/books - 新しい本作成する</t>
+  </si>
+  <si>
+    <t>// DELETE /api/books/{id} - 本を削除する</t>
+  </si>
+  <si>
+    <t>// Dataloader →本データを生成するFactory</t>
+  </si>
+  <si>
+    <t>DB</t>
+  </si>
+  <si>
+    <t>DB操作</t>
+  </si>
+  <si>
+    <t>→</t>
+  </si>
+  <si>
+    <t>BookRepositoryに三つのダミーデータを加える</t>
+  </si>
+  <si>
+    <t>全本を取得する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bookService.getAllBooks()→BookRepository.findAll() </t>
+  </si>
+  <si>
+    <t>削除</t>
+  </si>
+  <si>
+    <t>作成</t>
+  </si>
+  <si>
+    <t>BookRepository.deleteById(ID)</t>
+  </si>
+  <si>
+    <t>BookRepository.save(Book)</t>
+  </si>
+  <si>
+    <t>bookService.deleteBook(ID)→</t>
+  </si>
+  <si>
+    <t>bookService.saveBooks(Book)→</t>
+  </si>
+  <si>
+    <t>BookRepository</t>
+  </si>
+  <si>
+    <t>CRUD操作</t>
+  </si>
+  <si>
+    <t>※</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Controller </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service </t>
+  </si>
+  <si>
+    <t>Repository</t>
+  </si>
+  <si>
+    <t>BookService</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BookRepository </t>
+  </si>
+  <si>
+    <t>※BookRepository implements JpaRepository</t>
+  </si>
+  <si>
+    <t>Get</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User / Request matching </t>
+  </si>
+  <si>
+    <t>Post</t>
+  </si>
+  <si>
+    <t>Delete</t>
+  </si>
+  <si>
+    <t>listメソッド</t>
+  </si>
+  <si>
+    <t>createメソッド</t>
+  </si>
+  <si>
+    <t>deleteメソッド</t>
+  </si>
+  <si>
+    <t>findAll</t>
+  </si>
+  <si>
+    <t>save(book)</t>
+  </si>
+  <si>
+    <t>deleteById(id)</t>
+  </si>
+  <si>
+    <t>saveBook(book)</t>
+  </si>
+  <si>
+    <t>deleteBook(id)</t>
+  </si>
+  <si>
+    <t>getAllBooks()</t>
+  </si>
+  <si>
+    <t>select b1_0.id,b1_0.author,b1_0.isbn,b1_0.title from books b1_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> insert into books (author,isbn,title,id) values (?,?,?,default)</t>
+  </si>
+  <si>
+    <t>Hibernate: select b1_0.id,b1_0.author,b1_0.isbn,b1_0.title from books b1_0 where b1_0.id=?</t>
+  </si>
+  <si>
+    <t>Hibernate: delete from books where id=?</t>
+  </si>
+  <si>
+    <t>Read操作</t>
+  </si>
+  <si>
+    <t>Create操作</t>
+  </si>
+  <si>
+    <t>Read操作とDelete操作</t>
+  </si>
+  <si>
+    <t>図２</t>
+  </si>
+  <si>
+    <t>図１</t>
+  </si>
+  <si>
+    <t>insert into books (author,isbn,title,id) values (?,?,?,default)</t>
+  </si>
+  <si>
+    <t>CommandLineRunner</t>
+  </si>
+  <si>
+    <t>インターフェース CrudRepository の saveAll</t>
+  </si>
+  <si>
+    <t>repository</t>
+  </si>
+  <si>
+    <t>SaveAll</t>
+  </si>
+  <si>
+    <t>コンポーネント</t>
+  </si>
+  <si>
+    <t>DataLoader</t>
+  </si>
+  <si>
+    <t>初期化</t>
+  </si>
+  <si>
+    <t># Hibernate will automatically create the table based on the Entity
+spring.jpa.hibernate.ddl-auto=update
+spring.jpa.show-sql=true</t>
+  </si>
+  <si>
+    <t>シーケンス図１：</t>
+  </si>
+  <si>
+    <t>システム初期化</t>
+  </si>
+  <si>
+    <t>本システムを起動したら、最初は全部Springコンポーネントを起動した後はDataloaderコンポーネントを起動します。</t>
+  </si>
+  <si>
+    <t>Dataloaderコンポーネントのシーケンス図は以下の通りです。</t>
+  </si>
+  <si>
+    <t>DataloaderコンポーネントはCommandLineRunnerを実装し、今回のテストシステムにFactoryメソッドをとして、ダミーデータを加える。</t>
+  </si>
+  <si>
+    <t>シーケンス図２：</t>
+  </si>
+  <si>
+    <t>システムコントローラやCRUD操作のシーケンス図</t>
+  </si>
+  <si>
+    <t>本システムを起動して、ユーザーやブラウザからのAPIを公開した後の処理のシーケンス図であります。</t>
+  </si>
+  <si>
+    <t>以下では全部公開したAPIの処理の行動をシーケンス図で書いております。</t>
+  </si>
+  <si>
+    <t>Bookコントローラ</t>
+  </si>
+  <si>
+    <t>Bookサービス</t>
+  </si>
+  <si>
+    <t>Bookレポジトリ</t>
+  </si>
+  <si>
+    <t>BookRepositoryインターフェース</t>
+  </si>
+  <si>
+    <t>Select操作後Delete操作</t>
+  </si>
+  <si>
+    <t>Ｈ2　DB処理</t>
+  </si>
+  <si>
+    <t>Javaオブジェクト・Bookエンティティ</t>
+  </si>
+  <si>
+    <t>※トランザクション管理</t>
+  </si>
+  <si>
+    <t>コントローラ・MVC</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック Medium"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF808080"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -141,7 +538,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -149,12 +546,67 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -170,6 +622,3749 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="正方形/長方形 1"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="622300" y="368300"/>
+          <a:ext cx="10356850" cy="2406650"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>本システム</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>詳細設計</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>63500</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>508000</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="正方形/長方形 1"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2501900" y="3187700"/>
+          <a:ext cx="2273300" cy="3930650"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>Dataloader</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" baseline="0"/>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>Factory</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>メソッドコンポーネント</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t/>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t/>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>DataLoader </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>implements CommandLineRunner</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>→</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t/>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t/>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>BookRepository.saveAll(List.of(some1,som2,some3,....));</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>387350</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>222250</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>44450</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="正方形/長方形 2"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5873750" y="3200400"/>
+          <a:ext cx="2273300" cy="3930650"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>BookRepository</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>extends </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>JpaRepository</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-IN" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-IN" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t/>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-IN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>saveAll</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>→</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Save</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>操作を行って、</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>SaveAll</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>で全部</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>List</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>をラップする</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t/>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-IN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t/>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-IN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:endParaRPr lang="en-IN" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>603250</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="正方形/長方形 3"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9747250" y="3206750"/>
+          <a:ext cx="2273300" cy="3930650"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>H2 DB</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100"/>
+            <a:t>insert into books (author,isbn,title,id) values (?,?,?,default)</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>215900</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="楕円 4"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="215900" y="3759200"/>
+          <a:ext cx="1612900" cy="1809750"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>　　開始</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t/>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>システム起動</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>155575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>63500</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>92075</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="7" name="直線矢印コネクタ 6"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="5" idx="6"/>
+          <a:endCxn id="2" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828800" y="4664075"/>
+          <a:ext cx="673100" cy="488950"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>508000</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>92075</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>387350</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="9" name="直線矢印コネクタ 8"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="2" idx="3"/>
+          <a:endCxn id="3" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4775200" y="5153025"/>
+          <a:ext cx="1098550" cy="12700"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>222250</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>603250</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>111125</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="11" name="直線矢印コネクタ 10"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="3" idx="3"/>
+          <a:endCxn id="4" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8147050" y="5165725"/>
+          <a:ext cx="1600200" cy="6350"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>82550</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>158750</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>527050</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="正方形/長方形 13"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12884150" y="3194050"/>
+          <a:ext cx="2273300" cy="3930650"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>ブラウザ・ユーザー側</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>GET /api/books - </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>全本を取得して、表示する</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>98425</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>82550</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>111125</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="15" name="直線矢印コネクタ 14"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="4" idx="3"/>
+          <a:endCxn id="14" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="12020550" y="5159375"/>
+          <a:ext cx="863600" cy="12700"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="楕円 15"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="400050" y="10801350"/>
+          <a:ext cx="2152650" cy="3314700"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>ブラウザ・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>Postman</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>127000</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>44450</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="正方形/長方形 17"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3333750" y="10972800"/>
+          <a:ext cx="2889250" cy="730250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>list</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>メソッド</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t/>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>Get</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" altLang="ja-JP" sz="1100"/>
+            <a:t>/api/books</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t/>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>298450</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>139700</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="正方形/長方形 19"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3346450" y="12934950"/>
+          <a:ext cx="2889250" cy="730250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>delete</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>メソッド</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t/>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>DELETE /api/books/{id}</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>292100</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="正方形/長方形 20"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3340100" y="11944350"/>
+          <a:ext cx="2889250" cy="730250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>create</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>メソッド</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t/>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>POST /api/books</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t/>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>136525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="24" name="直線矢印コネクタ 23"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="16" idx="6"/>
+          <a:endCxn id="18" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="2552700" y="11337925"/>
+          <a:ext cx="781050" cy="1120775"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>193675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>292100</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="27" name="直線矢印コネクタ 26"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="16" idx="6"/>
+          <a:endCxn id="21" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="2552700" y="12309475"/>
+          <a:ext cx="787400" cy="149225"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>298450</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>41275</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="29" name="直線矢印コネクタ 28"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="16" idx="6"/>
+          <a:endCxn id="20" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2552700" y="12458700"/>
+          <a:ext cx="793750" cy="841375"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>107950</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>44450</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="32" name="正方形/長方形 31"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6972300" y="10972800"/>
+          <a:ext cx="2889250" cy="730250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>getAllBooks()</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>メソッド</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t/>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>：</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>bookRepository.findAll()</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t/>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>241300</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>82550</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="33" name="正方形/長方形 32"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6946900" y="11944350"/>
+          <a:ext cx="2889250" cy="730250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>saveBook(book)</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>メソッド</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN"/>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t/>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>：</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>bookRepository.save(books)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>222250</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>63500</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="34" name="正方形/長方形 33"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6927850" y="12928600"/>
+          <a:ext cx="2889250" cy="730250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>deleteBook(id)</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>メソッド</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN"/>
+            <a:t> </a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-IN"/>
+          </a:br>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US"/>
+            <a:t>：</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>bookRepository.deleteById(id)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>127000</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>136525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>136525</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="31" name="直線矢印コネクタ 30"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="18" idx="3"/>
+          <a:endCxn id="32" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6223000" y="11337925"/>
+          <a:ext cx="749300" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>193675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>241300</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>193675</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="36" name="直線矢印コネクタ 35"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="21" idx="3"/>
+          <a:endCxn id="33" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6229350" y="12309475"/>
+          <a:ext cx="717550" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>139700</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>34925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>222250</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>41275</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="40" name="直線矢印コネクタ 39"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="20" idx="3"/>
+          <a:endCxn id="34" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="6235700" y="13293725"/>
+          <a:ext cx="692150" cy="6350"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>584200</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>425450</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="45" name="正方形/長方形 44"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10947400" y="10147300"/>
+          <a:ext cx="2889250" cy="1079500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>bookRepository.findAll()</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>→インターフェース </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" altLang="ja-JP" sz="1100"/>
+            <a:t>CrudRepository </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>の </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>findAll()</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>リターン値：</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>BookRepository</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>にある全部エンティティ</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t/>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>88900</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>539750</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>82550</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="46" name="正方形/長方形 45"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11061700" y="11487150"/>
+          <a:ext cx="2889250" cy="1625600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>bookRepository.save()</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>→インターフェース </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" altLang="ja-JP" sz="1100"/>
+            <a:t>CrudRepository </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>の </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>save(books)</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>リターン値：</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>BookRepository</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>インターフェースに保存する操作。</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>save</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>メソッドを使った時はパラメータインティティは</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>null</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>以外設定する必要</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>107950</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>44450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>558800</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="47" name="正方形/長方形 46"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11080750" y="13303250"/>
+          <a:ext cx="2889250" cy="1212850"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>bookRepository.deleteByID()</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>→インターフェース </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" altLang="ja-JP" sz="1100"/>
+            <a:t>CrudRepository </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>の </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>deleteById(id)</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>リターン値：パラメータ</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>ID</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>のデータを削除する</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>107950</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>584200</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>136525</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="43" name="直線矢印コネクタ 42"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="32" idx="3"/>
+          <a:endCxn id="45" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="9861550" y="10687050"/>
+          <a:ext cx="1085850" cy="650875"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>82550</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>184150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>88900</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>193675</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="49" name="直線矢印コネクタ 48"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="33" idx="3"/>
+          <a:endCxn id="46" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="9836150" y="12299950"/>
+          <a:ext cx="1225550" cy="9525"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>63500</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>34925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>107950</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>193675</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="51" name="直線矢印コネクタ 50"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="34" idx="3"/>
+          <a:endCxn id="47" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9817100" y="13293725"/>
+          <a:ext cx="1263650" cy="615950"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>520700</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>196850</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>215900</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="63" name="正方形/長方形 62"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15151100" y="10483850"/>
+          <a:ext cx="3962400" cy="730250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>ステートメント：</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t/>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>＊</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>select b1.id,b1.author,b1.isbn,b1.title from books b1</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>488950</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>184150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>146050</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="64" name="正方形/長方形 63"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15119350" y="11385550"/>
+          <a:ext cx="5143500" cy="1835150"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>ステートメント：</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t/>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>save:Hibernate</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>は「</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>insert</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>の前</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>select</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>」</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>操作</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>を行われる。</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t/>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-IN" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>＊</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>select b1_0.id,b1_0.author,b1_0.isbn,b1_0.title from books b1_0 where b1_0.id=?</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>既にデータが存在した場合、</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t/>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>＊</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>update books set author=?,isbn=?,title=? where id=? </a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>新規データを作成の場合、</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t/>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-IN" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>＊</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>insert into books (author,isbn,title,id) value (?,?,?,default)</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:endParaRPr lang="en-IN">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>520700</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>196850</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="65" name="正方形/長方形 64"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15151100" y="13315950"/>
+          <a:ext cx="4318000" cy="1054100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>ステートメント：</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t/>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>削除する前に確認のため、</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>ID</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>で</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>select</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>操作を行われる</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t/>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>＊</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>select b1.id,b1.author,b1.isbn,b1.title from books b1 where b1.id=?</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>＊</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>delete from books where id=?</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>425450</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>520700</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="62" name="直線矢印コネクタ 61"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="45" idx="3"/>
+          <a:endCxn id="63" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13836650" y="10687050"/>
+          <a:ext cx="1314450" cy="161925"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>539750</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>184150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>488950</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>187325</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="7170" name="直線矢印コネクタ 7169"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="46" idx="3"/>
+          <a:endCxn id="64" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13950950" y="12299950"/>
+          <a:ext cx="1168400" cy="3175"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>558800</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>520700</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>193675</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="7173" name="直線矢印コネクタ 7172"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="47" idx="3"/>
+          <a:endCxn id="65" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="13970000" y="13843000"/>
+          <a:ext cx="1181100" cy="66675"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>120650</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>336550</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7203" name="正方形/長方形 7202"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="22066250" y="10414000"/>
+          <a:ext cx="2654300" cy="4229100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>DB</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>側に更新されたデータを取って新しい</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>Book</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>オブジェクトに登録する。</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t/>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t/>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>結果：</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>List&lt;Book&gt;</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>にデータがある</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t/>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t/>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>BookService</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>と</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>BookController</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>でも</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>Book</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>オブジェクトのデータをアクセス可能。</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>44</xdr:col>
+      <xdr:colOff>590792</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>141559</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>603491</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>12013</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7204" name="楕円 7203"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="27483042" y="11190559"/>
+          <a:ext cx="1846262" cy="3093079"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>ブラウザを再起動したら、更新した記録を表示する</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>215900</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>120650</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>184150</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="7206" name="直線矢印コネクタ 7205"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="63" idx="3"/>
+          <a:endCxn id="7203" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19113500" y="10848975"/>
+          <a:ext cx="2952750" cy="1679575"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>146050</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>187325</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>120650</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>184150</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="7208" name="直線矢印コネクタ 7207"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="64" idx="3"/>
+          <a:endCxn id="7203" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="20262850" y="12303125"/>
+          <a:ext cx="1803400" cy="225425"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>184150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>120650</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="7210" name="直線矢印コネクタ 7209"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="65" idx="3"/>
+          <a:endCxn id="7203" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="19469100" y="12528550"/>
+          <a:ext cx="2597150" cy="1314450"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>335623</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>55561</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>44</xdr:col>
+      <xdr:colOff>563265</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>103486</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7211" name="右矢印 7210"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="24783123" y="10874374"/>
+          <a:ext cx="2672392" cy="3730925"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>MVC</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>は</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>Json</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>型のデータに変換して、ブラウザ側に移る。</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t/>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>List&lt;Book&gt;</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>→</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" altLang="ja-JP" sz="1100"/>
+            <a:t>Java</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>オブジェクトをテキスト文字列にシリアライズします。</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -435,10 +4630,1246 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="C19:R26"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="16384" width="8.7265625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="19" spans="3:18">
+      <c r="C19" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+    </row>
+    <row r="20" spans="3:18">
+      <c r="C20" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+    </row>
+    <row r="21" spans="3:18">
+      <c r="C21" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D21" s="1"/>
+      <c r="E21" s="3">
+        <f>DATE(2026,4,6)</f>
+        <v>46118</v>
+      </c>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+    </row>
+    <row r="22" spans="3:18">
+      <c r="C22" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+    </row>
+    <row r="23" spans="3:18">
+      <c r="C23" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+    </row>
+    <row r="24" spans="3:18">
+      <c r="C24" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+    </row>
+    <row r="25" spans="3:18">
+      <c r="C25" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="O25" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="P25" s="4"/>
+      <c r="Q25" s="4"/>
+      <c r="R25" s="4"/>
+    </row>
+    <row r="26" spans="3:18">
+      <c r="O26" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="P26" s="4"/>
+      <c r="Q26" s="4"/>
+      <c r="R26" s="4"/>
+    </row>
+  </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="O25:R25"/>
+    <mergeCell ref="O26:R26"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="E23:G23"/>
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:Q14"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="16384" width="8.7265625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17">
+      <c r="A1" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q1" s="1"/>
+    </row>
+    <row r="2" spans="1:17">
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O2" s="1"/>
+      <c r="P2" s="3">
+        <f>DATE(2026,4,6)</f>
+        <v>46118</v>
+      </c>
+      <c r="Q2" s="1"/>
+    </row>
+    <row r="5" spans="1:17">
+      <c r="B5" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+    </row>
+    <row r="6" spans="1:17">
+      <c r="B6" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="3">
+        <f>DATE(2026,4,6)</f>
+        <v>46118</v>
+      </c>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="B7" s="7"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+    </row>
+    <row r="8" spans="1:17">
+      <c r="B8" s="7"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+    </row>
+    <row r="9" spans="1:17">
+      <c r="B9" s="7"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+    </row>
+    <row r="10" spans="1:17">
+      <c r="B10" s="7"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
+    </row>
+    <row r="11" spans="1:17">
+      <c r="B11" s="7"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+    </row>
+    <row r="12" spans="1:17">
+      <c r="B12" s="7"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+    </row>
+    <row r="13" spans="1:17">
+      <c r="B13" s="7"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+    </row>
+    <row r="14" spans="1:17">
+      <c r="B14" s="7"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="46">
+    <mergeCell ref="G13:L13"/>
+    <mergeCell ref="G14:L14"/>
+    <mergeCell ref="M7:O7"/>
+    <mergeCell ref="M8:O8"/>
+    <mergeCell ref="M9:O9"/>
+    <mergeCell ref="M10:O10"/>
+    <mergeCell ref="M11:O11"/>
+    <mergeCell ref="M12:O12"/>
+    <mergeCell ref="M13:O13"/>
+    <mergeCell ref="M14:O14"/>
+    <mergeCell ref="G7:L7"/>
+    <mergeCell ref="G8:L8"/>
+    <mergeCell ref="G9:L9"/>
+    <mergeCell ref="G10:L10"/>
+    <mergeCell ref="G11:L11"/>
+    <mergeCell ref="G12:L12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:L6"/>
+    <mergeCell ref="M5:O5"/>
+    <mergeCell ref="G5:L5"/>
+    <mergeCell ref="M6:O6"/>
+    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="E1:M2"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="P2:Q2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:U2"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="16384" width="8.7265625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:21">
+      <c r="A1" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+    </row>
+    <row r="2" spans="1:21">
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O2" s="1"/>
+      <c r="P2" s="3">
+        <f>DATE(2026,4,6)</f>
+        <v>46118</v>
+      </c>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="T2:U2"/>
+    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="H2:M2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:Q11"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="16384" width="8.7265625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17">
+      <c r="A1" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q1" s="1"/>
+    </row>
+    <row r="2" spans="1:17">
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O2" s="1"/>
+      <c r="P2" s="3">
+        <f>DATE(2026,4,6)</f>
+        <v>46118</v>
+      </c>
+      <c r="Q2" s="1"/>
+    </row>
+    <row r="6" spans="1:17">
+      <c r="A6" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" s="8"/>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="A7" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="L7" s="1"/>
+    </row>
+    <row r="8" spans="1:17">
+      <c r="A8" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L8" s="1"/>
+    </row>
+    <row r="9" spans="1:17">
+      <c r="A9" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+    </row>
+    <row r="10" spans="1:17">
+      <c r="A10" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+    </row>
+    <row r="11" spans="1:17">
+      <c r="A11" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="38">
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="E1:M2"/>
+    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E8:F11">
+      <formula1>"〇,ー"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G8:H11">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A6:Z113"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="2" max="2" width="14.90625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="6" spans="2:20">
+      <c r="T6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="7" spans="2:20">
+      <c r="L7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="8" spans="2:20">
+      <c r="B8" t="s">
+        <v>78</v>
+      </c>
+      <c r="F8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9" spans="2:20">
+      <c r="E9" t="s">
+        <v>83</v>
+      </c>
+      <c r="J9" t="s">
+        <v>86</v>
+      </c>
+      <c r="L9" t="s">
+        <v>87</v>
+      </c>
+      <c r="T9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="11" spans="2:20">
+      <c r="E11" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="J11" t="s">
+        <v>86</v>
+      </c>
+      <c r="L11" t="s">
+        <v>88</v>
+      </c>
+      <c r="N11" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="13" spans="2:20">
+      <c r="E13" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="J13" t="s">
+        <v>86</v>
+      </c>
+      <c r="L13" t="s">
+        <v>91</v>
+      </c>
+      <c r="M13" t="s">
+        <v>95</v>
+      </c>
+      <c r="P13" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="15" spans="2:20">
+      <c r="E15" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="J15" t="s">
+        <v>86</v>
+      </c>
+      <c r="L15" t="s">
+        <v>90</v>
+      </c>
+      <c r="M15" t="s">
+        <v>94</v>
+      </c>
+      <c r="P15" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17">
+      <c r="B21" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17">
+      <c r="A23" t="s">
+        <v>98</v>
+      </c>
+      <c r="B23" t="s">
+        <v>78</v>
+      </c>
+      <c r="C23" t="s">
+        <v>45</v>
+      </c>
+      <c r="E23" t="s">
+        <v>106</v>
+      </c>
+      <c r="G23" t="s">
+        <v>99</v>
+      </c>
+      <c r="I23" t="s">
+        <v>97</v>
+      </c>
+      <c r="J23" t="s">
+        <v>100</v>
+      </c>
+      <c r="M23" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17">
+      <c r="G25" t="s">
+        <v>79</v>
+      </c>
+      <c r="J25" t="s">
+        <v>102</v>
+      </c>
+      <c r="M25" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17">
+      <c r="C26" t="s">
+        <v>50</v>
+      </c>
+      <c r="E26" t="s">
+        <v>105</v>
+      </c>
+      <c r="G26" t="s">
+        <v>109</v>
+      </c>
+      <c r="I26" t="s">
+        <v>122</v>
+      </c>
+      <c r="J26" t="s">
+        <v>117</v>
+      </c>
+      <c r="M26" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17">
+      <c r="C28" t="s">
+        <v>3</v>
+      </c>
+      <c r="E28" t="s">
+        <v>107</v>
+      </c>
+      <c r="G28" t="s">
+        <v>110</v>
+      </c>
+      <c r="I28" t="s">
+        <v>123</v>
+      </c>
+      <c r="J28" t="s">
+        <v>115</v>
+      </c>
+      <c r="M28" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17">
+      <c r="C30" t="s">
+        <v>57</v>
+      </c>
+      <c r="E30" t="s">
+        <v>108</v>
+      </c>
+      <c r="G30" t="s">
+        <v>111</v>
+      </c>
+      <c r="I30" t="s">
+        <v>124</v>
+      </c>
+      <c r="J30" t="s">
+        <v>116</v>
+      </c>
+      <c r="M30" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17">
+      <c r="Q31" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="38" spans="2:26">
+      <c r="N38" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="41" spans="2:26">
+      <c r="B41" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26">
+      <c r="C43" t="s">
+        <v>132</v>
+      </c>
+      <c r="E43" t="s">
+        <v>128</v>
+      </c>
+      <c r="M43" t="s">
+        <v>130</v>
+      </c>
+      <c r="Z43" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" ht="246.5">
+      <c r="B44" t="s">
+        <v>134</v>
+      </c>
+      <c r="C44" t="s">
+        <v>133</v>
+      </c>
+      <c r="Z44" s="10" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26">
+      <c r="M46" t="s">
+        <v>131</v>
+      </c>
+      <c r="T46" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="113" spans="18:18">
+      <c r="R113" t="s">
+        <v>129</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AR62"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="16384" width="8.7265625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:21">
+      <c r="A1" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+    </row>
+    <row r="2" spans="1:21">
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O2" s="1"/>
+      <c r="P2" s="3">
+        <f>DATE(2026,4,6)</f>
+        <v>46118</v>
+      </c>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+    </row>
+    <row r="10" spans="1:21">
+      <c r="B10" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21">
+      <c r="C11" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21">
+      <c r="C12" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21">
+      <c r="C13" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21">
+      <c r="C14" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="42" spans="2:44">
+      <c r="B42" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="43" spans="2:44">
+      <c r="C43" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="S43" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="T43" s="4"/>
+      <c r="U43" s="4"/>
+      <c r="V43" s="4"/>
+      <c r="W43" s="4"/>
+      <c r="Z43" s="6"/>
+      <c r="AA43" s="6"/>
+      <c r="AB43" s="6"/>
+    </row>
+    <row r="44" spans="2:44">
+      <c r="C44" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="Z44" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="AA44" s="4"/>
+      <c r="AB44" s="4"/>
+      <c r="AK44" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="AL44" s="4"/>
+      <c r="AM44" s="4"/>
+      <c r="AN44" s="4"/>
+      <c r="AO44" s="4"/>
+      <c r="AP44" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="AQ44" s="4"/>
+      <c r="AR44" s="4"/>
+    </row>
+    <row r="45" spans="2:44">
+      <c r="C45" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="46" spans="2:44">
+      <c r="AG46" s="11"/>
+    </row>
+    <row r="47" spans="2:44">
+      <c r="G47" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="M47" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="N47" s="4"/>
+      <c r="O47" s="4"/>
+      <c r="P47" s="4"/>
+      <c r="S47" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="T47" s="4"/>
+      <c r="U47" s="4"/>
+      <c r="V47" s="4"/>
+    </row>
+    <row r="48" spans="2:44">
+      <c r="Q48" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="53" spans="13:18">
+      <c r="R53" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="61" spans="13:18">
+      <c r="Q61" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="62" spans="13:18">
+      <c r="M62" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="20">
+    <mergeCell ref="AK44:AO44"/>
+    <mergeCell ref="AP44:AR44"/>
+    <mergeCell ref="G47:J47"/>
+    <mergeCell ref="M47:P47"/>
+    <mergeCell ref="S47:V47"/>
+    <mergeCell ref="S43:W43"/>
+    <mergeCell ref="Z44:AB44"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:M2"/>
+    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="T2:U2"/>
+    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="H1:M1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A3:T27"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:20">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -446,7 +5877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:20">
       <c r="B4" t="s">
         <v>2</v>
       </c>
@@ -454,133 +5885,133 @@
         <v>5</v>
       </c>
       <c r="P4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20">
       <c r="B5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
         <v>4</v>
       </c>
       <c r="P5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20">
+      <c r="B6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="B6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" t="s">
+    <row r="7" spans="1:20">
+      <c r="B7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C7" t="s">
+        <v>6</v>
+      </c>
+      <c r="T7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20">
+      <c r="B8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C8" t="s">
+        <v>7</v>
+      </c>
+      <c r="T8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20">
+      <c r="B9">
+        <v>4.2</v>
+      </c>
+      <c r="C9" t="s">
         <v>10</v>
       </c>
-      <c r="H6" t="s">
+    </row>
+    <row r="10" spans="1:20">
+      <c r="B10">
+        <v>4.3</v>
+      </c>
+      <c r="C10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20">
+      <c r="B11">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="C11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20">
+      <c r="B12">
+        <v>4.5</v>
+      </c>
+      <c r="C12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" t="s">
+        <v>13</v>
+      </c>
+      <c r="P12" t="s">
         <v>23</v>
       </c>
-      <c r="Q6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="B7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" t="s">
-        <v>7</v>
-      </c>
-      <c r="T7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="B8">
-        <v>3.1</v>
-      </c>
-      <c r="C8" t="s">
-        <v>8</v>
-      </c>
-      <c r="T8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="B9">
-        <v>3.2</v>
-      </c>
-      <c r="C9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="B10">
-        <v>3.3</v>
-      </c>
-      <c r="C10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="B11">
-        <v>3.4</v>
-      </c>
-      <c r="C11" t="s">
+    </row>
+    <row r="13" spans="1:20">
+      <c r="B13">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="C13" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20">
+      <c r="P15" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="B12">
-        <v>3.5</v>
-      </c>
-      <c r="C12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" t="s">
-        <v>14</v>
-      </c>
-      <c r="P12" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="B13">
-        <v>3.6</v>
-      </c>
-      <c r="C13" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" t="s">
+    <row r="18" spans="16:17">
+      <c r="P18" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="16:17">
+      <c r="P22" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="P15" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18" spans="16:17" x14ac:dyDescent="0.35">
-      <c r="P18" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="22" spans="16:17" x14ac:dyDescent="0.35">
-      <c r="P22" t="s">
+    <row r="23" spans="16:17">
+      <c r="Q23" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="16:17" x14ac:dyDescent="0.35">
-      <c r="Q23" t="s">
+    <row r="26" spans="16:17">
+      <c r="P26" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="27" spans="16:17">
+      <c r="Q27" t="s">
         <v>28</v>
-      </c>
-    </row>
-    <row r="26" spans="16:17" x14ac:dyDescent="0.35">
-      <c r="P26" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="27" spans="16:17" x14ac:dyDescent="0.35">
-      <c r="Q27" t="s">
-        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -589,10 +6020,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/詳細設計＿練習.xlsx
+++ b/詳細設計＿練習.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="155">
   <si>
     <t>レイアウト</t>
   </si>
@@ -446,9 +446,6 @@
     <t>シーケンス図１：</t>
   </si>
   <si>
-    <t>システム初期化</t>
-  </si>
-  <si>
     <t>本システムを起動したら、最初は全部Springコンポーネントを起動した後はDataloaderコンポーネントを起動します。</t>
   </si>
   <si>
@@ -495,6 +492,12 @@
   </si>
   <si>
     <t>コントローラ・MVC</t>
+  </si>
+  <si>
+    <t>システム初期化・初期化投入</t>
+  </si>
+  <si>
+    <t>※正常系と異常系の比較はまだ</t>
   </si>
 </sst>
 </file>
@@ -580,24 +583,9 @@
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -606,6 +594,21 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4053,16 +4056,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>44</xdr:col>
-      <xdr:colOff>590792</xdr:colOff>
+      <xdr:col>48</xdr:col>
+      <xdr:colOff>266235</xdr:colOff>
       <xdr:row>48</xdr:row>
-      <xdr:rowOff>141559</xdr:rowOff>
+      <xdr:rowOff>14555</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>47</xdr:col>
-      <xdr:colOff>603491</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>12013</xdr:rowOff>
+      <xdr:col>51</xdr:col>
+      <xdr:colOff>278934</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>110787</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4071,8 +4074,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="27483042" y="11190559"/>
-          <a:ext cx="1846262" cy="3093079"/>
+          <a:off x="29391568" y="10851888"/>
+          <a:ext cx="1833033" cy="3031343"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
           <a:avLst/>
@@ -4260,15 +4263,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>40</xdr:col>
-      <xdr:colOff>335623</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>55561</xdr:rowOff>
+      <xdr:colOff>366889</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>21165</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>44</xdr:col>
-      <xdr:colOff>563265</xdr:colOff>
+      <xdr:col>48</xdr:col>
+      <xdr:colOff>218723</xdr:colOff>
       <xdr:row>63</xdr:row>
-      <xdr:rowOff>103486</xdr:rowOff>
+      <xdr:rowOff>84666</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4277,11 +4280,14 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="24783123" y="10874374"/>
-          <a:ext cx="2672392" cy="3730925"/>
+          <a:off x="24638000" y="10406943"/>
+          <a:ext cx="4706056" cy="3901723"/>
         </a:xfrm>
         <a:prstGeom prst="rightArrow">
-          <a:avLst/>
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 48469"/>
+            <a:gd name="adj2" fmla="val 81221"/>
+          </a:avLst>
         </a:prstGeom>
       </xdr:spPr>
       <xdr:style>
@@ -4313,6 +4319,65 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
+            <a:t>JSON Serialization (</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>シリアライズ</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t/>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
             <a:t>MVC</a:t>
           </a:r>
           <a:r>
@@ -4358,6 +4423,62 @@
             <a:rPr lang="ja-JP" altLang="en-US" sz="1100"/>
             <a:t>オブジェクトをテキスト文字列にシリアライズします。</a:t>
           </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t/>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>Get</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>→</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>200 OK</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>POST</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>→</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>201</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" baseline="0"/>
+            <a:t> OK</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" baseline="0"/>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" baseline="0"/>
+            <a:t>Delete</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" baseline="0"/>
+            <a:t>→</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" baseline="0"/>
+            <a:t>200 OK</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
           <a:endParaRPr lang="en-IN" sz="1100"/>
         </a:p>
       </xdr:txBody>
@@ -4633,99 +4754,104 @@
   <dimension ref="C19:R26"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="16384" width="8.7265625" style="2"/>
+    <col min="1" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
     <row r="19" spans="3:18">
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1" t="s">
+      <c r="D19" s="8"/>
+      <c r="E19" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
     </row>
     <row r="20" spans="3:18">
-      <c r="C20" s="1" t="s">
+      <c r="C20" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1" t="s">
+      <c r="D20" s="8"/>
+      <c r="E20" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
     </row>
     <row r="21" spans="3:18">
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="D21" s="1"/>
-      <c r="E21" s="3">
+      <c r="D21" s="8"/>
+      <c r="E21" s="9">
         <f>DATE(2026,4,6)</f>
         <v>46118</v>
       </c>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
     </row>
     <row r="22" spans="3:18">
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1" t="s">
+      <c r="D22" s="8"/>
+      <c r="E22" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
     </row>
     <row r="23" spans="3:18">
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1" t="s">
+      <c r="D23" s="8"/>
+      <c r="E23" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
     </row>
     <row r="24" spans="3:18">
-      <c r="C24" s="1" t="s">
+      <c r="C24" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
     </row>
     <row r="25" spans="3:18">
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="O25" s="4" t="s">
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="O25" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="P25" s="4"/>
-      <c r="Q25" s="4"/>
-      <c r="R25" s="4"/>
+      <c r="P25" s="7"/>
+      <c r="Q25" s="7"/>
+      <c r="R25" s="7"/>
     </row>
     <row r="26" spans="3:18">
-      <c r="O26" s="4" t="s">
+      <c r="O26" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="P26" s="4"/>
-      <c r="Q26" s="4"/>
-      <c r="R26" s="4"/>
+      <c r="P26" s="7"/>
+      <c r="Q26" s="7"/>
+      <c r="R26" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C22:D22"/>
     <mergeCell ref="O25:R25"/>
     <mergeCell ref="O26:R26"/>
     <mergeCell ref="C24:D24"/>
@@ -4736,11 +4862,6 @@
     <mergeCell ref="E23:G23"/>
     <mergeCell ref="E24:G24"/>
     <mergeCell ref="E25:G25"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:G19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C22:D22"/>
     <mergeCell ref="C23:D23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4754,241 +4875,271 @@
   <dimension ref="A1:Q14"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="16384" width="8.7265625" style="2"/>
+    <col min="1" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="1" t="s">
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1" t="s">
+      <c r="O1" s="8"/>
+      <c r="P1" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="Q1" s="1"/>
+      <c r="Q1" s="8"/>
     </row>
     <row r="2" spans="1:17">
-      <c r="A2" s="5"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="1" t="s">
+      <c r="A2" s="10"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="O2" s="1"/>
-      <c r="P2" s="3">
+      <c r="O2" s="8"/>
+      <c r="P2" s="9">
         <f>DATE(2026,4,6)</f>
         <v>46118</v>
       </c>
-      <c r="Q2" s="1"/>
+      <c r="Q2" s="8"/>
     </row>
     <row r="5" spans="1:17">
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1" t="s">
+      <c r="D5" s="8"/>
+      <c r="E5" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1" t="s">
+      <c r="F5" s="8"/>
+      <c r="G5" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1" t="s">
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="8"/>
     </row>
     <row r="6" spans="1:17">
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="D6" s="1"/>
-      <c r="E6" s="3">
+      <c r="D6" s="8"/>
+      <c r="E6" s="9">
         <f>DATE(2026,4,6)</f>
         <v>46118</v>
       </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1" t="s">
+      <c r="F6" s="8"/>
+      <c r="G6" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="8"/>
+      <c r="N6" s="8"/>
+      <c r="O6" s="8"/>
     </row>
     <row r="7" spans="1:17">
-      <c r="B7" s="7"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
-      <c r="O7" s="1"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
     </row>
     <row r="8" spans="1:17">
-      <c r="B8" s="7"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
     </row>
     <row r="9" spans="1:17">
-      <c r="B9" s="7"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-      <c r="O9" s="1"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
+      <c r="O9" s="8"/>
     </row>
     <row r="10" spans="1:17">
-      <c r="B10" s="7"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8"/>
     </row>
     <row r="11" spans="1:17">
-      <c r="B11" s="7"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="8"/>
     </row>
     <row r="12" spans="1:17">
-      <c r="B12" s="7"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8"/>
     </row>
     <row r="13" spans="1:17">
-      <c r="B13" s="7"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="8"/>
+      <c r="N13" s="8"/>
+      <c r="O13" s="8"/>
     </row>
     <row r="14" spans="1:17">
-      <c r="B14" s="7"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="8"/>
+      <c r="O14" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="46">
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="M5:O5"/>
+    <mergeCell ref="G5:L5"/>
+    <mergeCell ref="M6:O6"/>
+    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="E1:M2"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:L6"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
     <mergeCell ref="G13:L13"/>
     <mergeCell ref="G14:L14"/>
     <mergeCell ref="M7:O7"/>
@@ -5005,36 +5156,6 @@
     <mergeCell ref="G10:L10"/>
     <mergeCell ref="G11:L11"/>
     <mergeCell ref="G12:L12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:L6"/>
-    <mergeCell ref="M5:O5"/>
-    <mergeCell ref="G5:L5"/>
-    <mergeCell ref="M6:O6"/>
-    <mergeCell ref="A1:D2"/>
-    <mergeCell ref="E1:M2"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="P2:Q2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5045,77 +5166,77 @@
   <dimension ref="A1:U2"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="16384" width="8.7265625" style="2"/>
+    <col min="1" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5" t="s">
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="1" t="s">
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1" t="s">
+      <c r="O1" s="8"/>
+      <c r="P1" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1" t="s">
+      <c r="Q1" s="8"/>
+      <c r="R1" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
+      <c r="S1" s="8"/>
+      <c r="T1" s="8"/>
+      <c r="U1" s="8"/>
     </row>
     <row r="2" spans="1:21">
-      <c r="A2" s="5"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5" t="s">
+      <c r="A2" s="10"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5" t="s">
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="1" t="s">
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="O2" s="1"/>
-      <c r="P2" s="3">
+      <c r="O2" s="8"/>
+      <c r="P2" s="9">
         <f>DATE(2026,4,6)</f>
         <v>46118</v>
       </c>
-      <c r="Q2" s="1"/>
-      <c r="R2" s="1" t="s">
+      <c r="Q2" s="8"/>
+      <c r="R2" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="S2" s="1"/>
-      <c r="T2" s="1"/>
-      <c r="U2" s="1"/>
+      <c r="S2" s="8"/>
+      <c r="T2" s="8"/>
+      <c r="U2" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -5142,208 +5263,213 @@
   <dimension ref="A1:Q11"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="16384" width="8.7265625" style="2"/>
+    <col min="1" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="1" t="s">
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1" t="s">
+      <c r="O1" s="8"/>
+      <c r="P1" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="Q1" s="1"/>
+      <c r="Q1" s="8"/>
     </row>
     <row r="2" spans="1:17">
-      <c r="A2" s="5"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="1" t="s">
+      <c r="A2" s="10"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="O2" s="1"/>
-      <c r="P2" s="3">
+      <c r="O2" s="8"/>
+      <c r="P2" s="9">
         <f>DATE(2026,4,6)</f>
         <v>46118</v>
       </c>
-      <c r="Q2" s="1"/>
+      <c r="Q2" s="8"/>
     </row>
     <row r="6" spans="1:17">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8" t="s">
+      <c r="B6" s="11"/>
+      <c r="C6" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="D6" s="8"/>
+      <c r="D6" s="11"/>
     </row>
     <row r="7" spans="1:17">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1" t="s">
+      <c r="B7" s="8"/>
+      <c r="C7" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1" t="s">
+      <c r="D7" s="8"/>
+      <c r="E7" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1" t="s">
+      <c r="F7" s="8"/>
+      <c r="G7" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1" t="s">
+      <c r="H7" s="8"/>
+      <c r="I7" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1" t="s">
+      <c r="J7" s="8"/>
+      <c r="K7" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="L7" s="1"/>
+      <c r="L7" s="8"/>
     </row>
     <row r="8" spans="1:17">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1" t="s">
+      <c r="B8" s="8"/>
+      <c r="C8" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1" t="s">
+      <c r="D8" s="8"/>
+      <c r="E8" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1" t="s">
+      <c r="F8" s="8"/>
+      <c r="G8" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1" t="s">
+      <c r="H8" s="8"/>
+      <c r="I8" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1" t="s">
+      <c r="J8" s="8"/>
+      <c r="K8" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="L8" s="1"/>
+      <c r="L8" s="8"/>
     </row>
     <row r="9" spans="1:17">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1" t="s">
+      <c r="B9" s="8"/>
+      <c r="C9" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1" t="s">
+      <c r="D9" s="8"/>
+      <c r="E9" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1" t="s">
+      <c r="F9" s="8"/>
+      <c r="G9" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1" t="s">
+      <c r="H9" s="8"/>
+      <c r="I9" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
     </row>
     <row r="10" spans="1:17">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1" t="s">
+      <c r="B10" s="8"/>
+      <c r="C10" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1" t="s">
+      <c r="D10" s="8"/>
+      <c r="E10" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1" t="s">
+      <c r="F10" s="8"/>
+      <c r="G10" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1" t="s">
+      <c r="H10" s="8"/>
+      <c r="I10" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
     </row>
     <row r="11" spans="1:17">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1" t="s">
+      <c r="B11" s="8"/>
+      <c r="C11" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1" t="s">
+      <c r="D11" s="8"/>
+      <c r="E11" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1" t="s">
+      <c r="F11" s="8"/>
+      <c r="G11" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1" t="s">
+      <c r="H11" s="8"/>
+      <c r="I11" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="E1:M2"/>
+    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="G9:H9"/>
     <mergeCell ref="E9:F9"/>
     <mergeCell ref="E10:F10"/>
     <mergeCell ref="E11:F11"/>
@@ -5352,24 +5478,19 @@
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="C11:D11"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I11:J11"/>
     <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="E1:M2"/>
-    <mergeCell ref="A1:D2"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="K11:L11"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E8:F11">
@@ -5425,7 +5546,7 @@
       </c>
     </row>
     <row r="11" spans="2:20">
-      <c r="E11" s="9" t="s">
+      <c r="E11" s="4" t="s">
         <v>80</v>
       </c>
       <c r="J11" t="s">
@@ -5439,7 +5560,7 @@
       </c>
     </row>
     <row r="13" spans="2:20">
-      <c r="E13" s="9" t="s">
+      <c r="E13" s="4" t="s">
         <v>81</v>
       </c>
       <c r="J13" t="s">
@@ -5456,7 +5577,7 @@
       </c>
     </row>
     <row r="15" spans="2:20">
-      <c r="E15" s="9" t="s">
+      <c r="E15" s="4" t="s">
         <v>82</v>
       </c>
       <c r="J15" t="s">
@@ -5622,7 +5743,7 @@
       <c r="C44" t="s">
         <v>133</v>
       </c>
-      <c r="Z44" s="10" t="s">
+      <c r="Z44" s="5" t="s">
         <v>135</v>
       </c>
     </row>
@@ -5646,203 +5767,210 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AR62"/>
+  <dimension ref="A1:AR66"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="16384" width="8.7265625" style="2"/>
+    <col min="1" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5" t="s">
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="1" t="s">
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1" t="s">
+      <c r="O1" s="8"/>
+      <c r="P1" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1" t="s">
+      <c r="Q1" s="8"/>
+      <c r="R1" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
+      <c r="S1" s="8"/>
+      <c r="T1" s="8"/>
+      <c r="U1" s="8"/>
     </row>
     <row r="2" spans="1:21">
-      <c r="A2" s="5"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5" t="s">
+      <c r="A2" s="10"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5" t="s">
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="1" t="s">
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="O2" s="1"/>
-      <c r="P2" s="3">
+      <c r="O2" s="8"/>
+      <c r="P2" s="9">
         <f>DATE(2026,4,6)</f>
         <v>46118</v>
       </c>
-      <c r="Q2" s="1"/>
-      <c r="R2" s="1" t="s">
+      <c r="Q2" s="8"/>
+      <c r="R2" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="S2" s="1"/>
-      <c r="T2" s="1"/>
-      <c r="U2" s="1"/>
+      <c r="S2" s="8"/>
+      <c r="T2" s="8"/>
+      <c r="U2" s="8"/>
     </row>
     <row r="10" spans="1:21">
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="11" spans="1:21">
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21">
+      <c r="C12" s="1" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="12" spans="1:21">
-      <c r="C12" s="2" t="s">
+    <row r="13" spans="1:21">
+      <c r="C13" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21">
+      <c r="C14" s="1" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="13" spans="1:21">
-      <c r="C13" s="2" t="s">
+    <row r="42" spans="2:44">
+      <c r="B42" s="1" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="14" spans="1:21">
-      <c r="C14" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="42" spans="2:44">
-      <c r="B42" s="2" t="s">
+    <row r="43" spans="2:44">
+      <c r="C43" s="1" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="43" spans="2:44">
-      <c r="C43" s="2" t="s">
+      <c r="S43" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="T43" s="7"/>
+      <c r="U43" s="7"/>
+      <c r="V43" s="7"/>
+      <c r="W43" s="7"/>
+      <c r="Z43" s="2"/>
+      <c r="AA43" s="2"/>
+      <c r="AB43" s="2"/>
+    </row>
+    <row r="44" spans="2:44">
+      <c r="C44" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="S43" s="4" t="s">
+      <c r="Z44" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="AA44" s="7"/>
+      <c r="AB44" s="7"/>
+      <c r="AK44" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="AL44" s="7"/>
+      <c r="AM44" s="7"/>
+      <c r="AN44" s="7"/>
+      <c r="AO44" s="7"/>
+      <c r="AP44" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="AQ44" s="7"/>
+      <c r="AR44" s="7"/>
+    </row>
+    <row r="45" spans="2:44">
+      <c r="C45" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="46" spans="2:44">
+      <c r="AG46" s="6"/>
+    </row>
+    <row r="47" spans="2:44">
+      <c r="G47" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="H47" s="7"/>
+      <c r="I47" s="7"/>
+      <c r="J47" s="7"/>
+      <c r="M47" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="N47" s="7"/>
+      <c r="O47" s="7"/>
+      <c r="P47" s="7"/>
+      <c r="S47" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="T47" s="7"/>
+      <c r="U47" s="7"/>
+      <c r="V47" s="7"/>
+    </row>
+    <row r="48" spans="2:44">
+      <c r="Q48" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="53" spans="13:18">
+      <c r="R53" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="61" spans="13:18">
+      <c r="Q61" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="T43" s="4"/>
-      <c r="U43" s="4"/>
-      <c r="V43" s="4"/>
-      <c r="W43" s="4"/>
-      <c r="Z43" s="6"/>
-      <c r="AA43" s="6"/>
-      <c r="AB43" s="6"/>
-    </row>
-    <row r="44" spans="2:44">
-      <c r="C44" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="Z44" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="AA44" s="4"/>
-      <c r="AB44" s="4"/>
-      <c r="AK44" s="4" t="s">
+    </row>
+    <row r="62" spans="13:18">
+      <c r="M62" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="AL44" s="4"/>
-      <c r="AM44" s="4"/>
-      <c r="AN44" s="4"/>
-      <c r="AO44" s="4"/>
-      <c r="AP44" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="AQ44" s="4"/>
-      <c r="AR44" s="4"/>
-    </row>
-    <row r="45" spans="2:44">
-      <c r="C45" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="46" spans="2:44">
-      <c r="AG46" s="11"/>
-    </row>
-    <row r="47" spans="2:44">
-      <c r="G47" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="H47" s="4"/>
-      <c r="I47" s="4"/>
-      <c r="J47" s="4"/>
-      <c r="M47" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="N47" s="4"/>
-      <c r="O47" s="4"/>
-      <c r="P47" s="4"/>
-      <c r="S47" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="T47" s="4"/>
-      <c r="U47" s="4"/>
-      <c r="V47" s="4"/>
-    </row>
-    <row r="48" spans="2:44">
-      <c r="Q48" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="53" spans="13:18">
-      <c r="R53" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="61" spans="13:18">
-      <c r="Q61" s="2" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="62" spans="13:18">
-      <c r="M62" s="2" t="s">
-        <v>152</v>
+    </row>
+    <row r="66" spans="19:19">
+      <c r="S66" s="1" t="s">
+        <v>154</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="AK44:AO44"/>
-    <mergeCell ref="AP44:AR44"/>
-    <mergeCell ref="G47:J47"/>
-    <mergeCell ref="M47:P47"/>
-    <mergeCell ref="S47:V47"/>
+    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="H1:M1"/>
     <mergeCell ref="S43:W43"/>
     <mergeCell ref="Z44:AB44"/>
     <mergeCell ref="R1:S1"/>
@@ -5851,13 +5979,11 @@
     <mergeCell ref="H2:M2"/>
     <mergeCell ref="R2:S2"/>
     <mergeCell ref="T2:U2"/>
-    <mergeCell ref="A1:D2"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="AK44:AO44"/>
+    <mergeCell ref="AP44:AR44"/>
+    <mergeCell ref="G47:J47"/>
+    <mergeCell ref="M47:P47"/>
+    <mergeCell ref="S47:V47"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/詳細設計＿練習.xlsx
+++ b/詳細設計＿練習.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25560" windowHeight="1910" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25560" windowHeight="1910" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="2" r:id="rId1"/>
@@ -1194,10 +1194,33 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1206,10 +1229,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1237,27 +1256,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -11331,100 +11331,95 @@
   </cols>
   <sheetData>
     <row r="19" spans="3:18">
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8" t="s">
+      <c r="D19" s="22"/>
+      <c r="E19" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
+      <c r="F19" s="22"/>
+      <c r="G19" s="22"/>
     </row>
     <row r="20" spans="3:18">
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8" t="s">
+      <c r="D20" s="22"/>
+      <c r="E20" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
     </row>
     <row r="21" spans="3:18">
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="D21" s="8"/>
-      <c r="E21" s="9">
+      <c r="D21" s="22"/>
+      <c r="E21" s="24">
         <f>DATE(2026,4,6)</f>
         <v>46118</v>
       </c>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="22"/>
     </row>
     <row r="22" spans="3:18">
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8" t="s">
+      <c r="D22" s="22"/>
+      <c r="E22" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
     </row>
     <row r="23" spans="3:18">
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8" t="s">
+      <c r="D23" s="22"/>
+      <c r="E23" s="22" t="s">
         <v>155</v>
       </c>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
     </row>
     <row r="24" spans="3:18">
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="22"/>
     </row>
     <row r="25" spans="3:18">
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="O25" s="7" t="s">
+      <c r="D25" s="22"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="22"/>
+      <c r="O25" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="P25" s="7"/>
-      <c r="Q25" s="7"/>
-      <c r="R25" s="7"/>
+      <c r="P25" s="23"/>
+      <c r="Q25" s="23"/>
+      <c r="R25" s="23"/>
     </row>
     <row r="26" spans="3:18">
-      <c r="O26" s="7" t="s">
+      <c r="O26" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="P26" s="7"/>
-      <c r="Q26" s="7"/>
-      <c r="R26" s="7"/>
+      <c r="P26" s="23"/>
+      <c r="Q26" s="23"/>
+      <c r="R26" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:G19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C22:D22"/>
     <mergeCell ref="O25:R25"/>
     <mergeCell ref="O26:R26"/>
     <mergeCell ref="C24:D24"/>
@@ -11436,6 +11431,11 @@
     <mergeCell ref="E24:G24"/>
     <mergeCell ref="E25:G25"/>
     <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C22:D22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -11452,640 +11452,564 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10" t="s">
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="8" t="s">
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="O1" s="8"/>
-      <c r="P1" s="8" t="s">
+      <c r="O1" s="22"/>
+      <c r="P1" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="Q1" s="8"/>
+      <c r="Q1" s="22"/>
     </row>
     <row r="2" spans="1:17">
-      <c r="A2" s="10"/>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="8" t="s">
+      <c r="A2" s="25"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
+      <c r="M2" s="25"/>
+      <c r="N2" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="O2" s="8"/>
-      <c r="P2" s="9">
+      <c r="O2" s="22"/>
+      <c r="P2" s="24">
         <f>DATE(2026,4,6)</f>
         <v>46118</v>
       </c>
-      <c r="Q2" s="8"/>
+      <c r="Q2" s="22"/>
     </row>
     <row r="5" spans="1:17">
       <c r="B5" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8" t="s">
+      <c r="D5" s="22"/>
+      <c r="E5" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8" t="s">
+      <c r="F5" s="22"/>
+      <c r="G5" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
-      <c r="M5" s="8" t="s">
+      <c r="H5" s="22"/>
+      <c r="I5" s="22"/>
+      <c r="J5" s="22"/>
+      <c r="K5" s="22"/>
+      <c r="L5" s="22"/>
+      <c r="M5" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="N5" s="8"/>
-      <c r="O5" s="8"/>
+      <c r="N5" s="22"/>
+      <c r="O5" s="22"/>
     </row>
     <row r="6" spans="1:17">
       <c r="B6" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="D6" s="8"/>
-      <c r="E6" s="9">
+      <c r="D6" s="22"/>
+      <c r="E6" s="24">
         <f>DATE(2026,4,6)</f>
         <v>46118</v>
       </c>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8" t="s">
+      <c r="F6" s="22"/>
+      <c r="G6" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
-      <c r="M6" s="8"/>
-      <c r="N6" s="8"/>
-      <c r="O6" s="8"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="22"/>
+      <c r="J6" s="22"/>
+      <c r="K6" s="22"/>
+      <c r="L6" s="22"/>
+      <c r="M6" s="22"/>
+      <c r="N6" s="22"/>
+      <c r="O6" s="22"/>
     </row>
     <row r="7" spans="1:17">
       <c r="B7" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="9">
+      <c r="D7" s="22"/>
+      <c r="E7" s="24">
         <f>DATE(2026,4,7)</f>
         <v>46119</v>
       </c>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8" t="s">
+      <c r="F7" s="22"/>
+      <c r="G7" s="22" t="s">
         <v>152</v>
       </c>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="8"/>
+      <c r="H7" s="22"/>
+      <c r="I7" s="22"/>
+      <c r="J7" s="22"/>
+      <c r="K7" s="22"/>
+      <c r="L7" s="22"/>
+      <c r="M7" s="22"/>
+      <c r="N7" s="22"/>
+      <c r="O7" s="22"/>
     </row>
     <row r="8" spans="1:17">
       <c r="B8" s="3"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
-      <c r="N8" s="8"/>
-      <c r="O8" s="8"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="22"/>
+      <c r="G8" s="22"/>
+      <c r="H8" s="22"/>
+      <c r="I8" s="22"/>
+      <c r="J8" s="22"/>
+      <c r="K8" s="22"/>
+      <c r="L8" s="22"/>
+      <c r="M8" s="22"/>
+      <c r="N8" s="22"/>
+      <c r="O8" s="22"/>
     </row>
     <row r="9" spans="1:17">
       <c r="B9" s="3"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8"/>
-      <c r="N9" s="8"/>
-      <c r="O9" s="8"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="22"/>
+      <c r="K9" s="22"/>
+      <c r="L9" s="22"/>
+      <c r="M9" s="22"/>
+      <c r="N9" s="22"/>
+      <c r="O9" s="22"/>
     </row>
     <row r="10" spans="1:17">
       <c r="B10" s="3"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
-      <c r="N10" s="8"/>
-      <c r="O10" s="8"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="22"/>
+      <c r="K10" s="22"/>
+      <c r="L10" s="22"/>
+      <c r="M10" s="22"/>
+      <c r="N10" s="22"/>
+      <c r="O10" s="22"/>
     </row>
     <row r="11" spans="1:17">
       <c r="B11" s="3"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="8"/>
-      <c r="N11" s="8"/>
-      <c r="O11" s="8"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="22"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="22"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="22"/>
+      <c r="K11" s="22"/>
+      <c r="L11" s="22"/>
+      <c r="M11" s="22"/>
+      <c r="N11" s="22"/>
+      <c r="O11" s="22"/>
     </row>
     <row r="12" spans="1:17">
       <c r="B12" s="3"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="8"/>
-      <c r="M12" s="8"/>
-      <c r="N12" s="8"/>
-      <c r="O12" s="8"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="22"/>
+      <c r="G12" s="22"/>
+      <c r="H12" s="22"/>
+      <c r="I12" s="22"/>
+      <c r="J12" s="22"/>
+      <c r="K12" s="22"/>
+      <c r="L12" s="22"/>
+      <c r="M12" s="22"/>
+      <c r="N12" s="22"/>
+      <c r="O12" s="22"/>
     </row>
     <row r="13" spans="1:17">
       <c r="B13" s="3"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8"/>
-      <c r="M13" s="8"/>
-      <c r="N13" s="8"/>
-      <c r="O13" s="8"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="22"/>
+      <c r="H13" s="22"/>
+      <c r="I13" s="22"/>
+      <c r="J13" s="22"/>
+      <c r="K13" s="22"/>
+      <c r="L13" s="22"/>
+      <c r="M13" s="22"/>
+      <c r="N13" s="22"/>
+      <c r="O13" s="22"/>
     </row>
     <row r="14" spans="1:17">
       <c r="B14" s="3"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8"/>
-      <c r="L14" s="8"/>
-      <c r="M14" s="8"/>
-      <c r="N14" s="8"/>
-      <c r="O14" s="8"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="22"/>
+      <c r="H14" s="22"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="22"/>
+      <c r="K14" s="22"/>
+      <c r="L14" s="22"/>
+      <c r="M14" s="22"/>
+      <c r="N14" s="22"/>
+      <c r="O14" s="22"/>
     </row>
     <row r="15" spans="1:17">
       <c r="B15" s="3"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="8"/>
-      <c r="M15" s="8"/>
-      <c r="N15" s="8"/>
-      <c r="O15" s="8"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="22"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="22"/>
+      <c r="K15" s="22"/>
+      <c r="L15" s="22"/>
+      <c r="M15" s="22"/>
+      <c r="N15" s="22"/>
+      <c r="O15" s="22"/>
     </row>
     <row r="16" spans="1:17">
       <c r="B16" s="3"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8"/>
-      <c r="L16" s="8"/>
-      <c r="M16" s="8"/>
-      <c r="N16" s="8"/>
-      <c r="O16" s="8"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="22"/>
+      <c r="J16" s="22"/>
+      <c r="K16" s="22"/>
+      <c r="L16" s="22"/>
+      <c r="M16" s="22"/>
+      <c r="N16" s="22"/>
+      <c r="O16" s="22"/>
     </row>
     <row r="17" spans="2:15">
       <c r="B17" s="3"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="8"/>
-      <c r="M17" s="8"/>
-      <c r="N17" s="8"/>
-      <c r="O17" s="8"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="22"/>
+      <c r="I17" s="22"/>
+      <c r="J17" s="22"/>
+      <c r="K17" s="22"/>
+      <c r="L17" s="22"/>
+      <c r="M17" s="22"/>
+      <c r="N17" s="22"/>
+      <c r="O17" s="22"/>
     </row>
     <row r="18" spans="2:15">
       <c r="B18" s="3"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8"/>
-      <c r="L18" s="8"/>
-      <c r="M18" s="8"/>
-      <c r="N18" s="8"/>
-      <c r="O18" s="8"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="22"/>
+      <c r="K18" s="22"/>
+      <c r="L18" s="22"/>
+      <c r="M18" s="22"/>
+      <c r="N18" s="22"/>
+      <c r="O18" s="22"/>
     </row>
     <row r="19" spans="2:15">
       <c r="B19" s="3"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
-      <c r="J19" s="8"/>
-      <c r="K19" s="8"/>
-      <c r="L19" s="8"/>
-      <c r="M19" s="8"/>
-      <c r="N19" s="8"/>
-      <c r="O19" s="8"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="22"/>
+      <c r="E19" s="22"/>
+      <c r="F19" s="22"/>
+      <c r="G19" s="22"/>
+      <c r="H19" s="22"/>
+      <c r="I19" s="22"/>
+      <c r="J19" s="22"/>
+      <c r="K19" s="22"/>
+      <c r="L19" s="22"/>
+      <c r="M19" s="22"/>
+      <c r="N19" s="22"/>
+      <c r="O19" s="22"/>
     </row>
     <row r="20" spans="2:15">
       <c r="B20" s="3"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
-      <c r="J20" s="8"/>
-      <c r="K20" s="8"/>
-      <c r="L20" s="8"/>
-      <c r="M20" s="8"/>
-      <c r="N20" s="8"/>
-      <c r="O20" s="8"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="22"/>
+      <c r="J20" s="22"/>
+      <c r="K20" s="22"/>
+      <c r="L20" s="22"/>
+      <c r="M20" s="22"/>
+      <c r="N20" s="22"/>
+      <c r="O20" s="22"/>
     </row>
     <row r="21" spans="2:15">
       <c r="B21" s="3"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8"/>
-      <c r="J21" s="8"/>
-      <c r="K21" s="8"/>
-      <c r="L21" s="8"/>
-      <c r="M21" s="8"/>
-      <c r="N21" s="8"/>
-      <c r="O21" s="8"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="22"/>
+      <c r="I21" s="22"/>
+      <c r="J21" s="22"/>
+      <c r="K21" s="22"/>
+      <c r="L21" s="22"/>
+      <c r="M21" s="22"/>
+      <c r="N21" s="22"/>
+      <c r="O21" s="22"/>
     </row>
     <row r="22" spans="2:15">
       <c r="B22" s="3"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="8"/>
-      <c r="I22" s="8"/>
-      <c r="J22" s="8"/>
-      <c r="K22" s="8"/>
-      <c r="L22" s="8"/>
-      <c r="M22" s="8"/>
-      <c r="N22" s="8"/>
-      <c r="O22" s="8"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="22"/>
+      <c r="K22" s="22"/>
+      <c r="L22" s="22"/>
+      <c r="M22" s="22"/>
+      <c r="N22" s="22"/>
+      <c r="O22" s="22"/>
     </row>
     <row r="23" spans="2:15">
       <c r="B23" s="3"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="8"/>
-      <c r="I23" s="8"/>
-      <c r="J23" s="8"/>
-      <c r="K23" s="8"/>
-      <c r="L23" s="8"/>
-      <c r="M23" s="8"/>
-      <c r="N23" s="8"/>
-      <c r="O23" s="8"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="22"/>
+      <c r="I23" s="22"/>
+      <c r="J23" s="22"/>
+      <c r="K23" s="22"/>
+      <c r="L23" s="22"/>
+      <c r="M23" s="22"/>
+      <c r="N23" s="22"/>
+      <c r="O23" s="22"/>
     </row>
     <row r="24" spans="2:15">
       <c r="B24" s="3"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
-      <c r="I24" s="8"/>
-      <c r="J24" s="8"/>
-      <c r="K24" s="8"/>
-      <c r="L24" s="8"/>
-      <c r="M24" s="8"/>
-      <c r="N24" s="8"/>
-      <c r="O24" s="8"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="22"/>
+      <c r="I24" s="22"/>
+      <c r="J24" s="22"/>
+      <c r="K24" s="22"/>
+      <c r="L24" s="22"/>
+      <c r="M24" s="22"/>
+      <c r="N24" s="22"/>
+      <c r="O24" s="22"/>
     </row>
     <row r="25" spans="2:15">
       <c r="B25" s="3"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
-      <c r="I25" s="8"/>
-      <c r="J25" s="8"/>
-      <c r="K25" s="8"/>
-      <c r="L25" s="8"/>
-      <c r="M25" s="8"/>
-      <c r="N25" s="8"/>
-      <c r="O25" s="8"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="22"/>
+      <c r="H25" s="22"/>
+      <c r="I25" s="22"/>
+      <c r="J25" s="22"/>
+      <c r="K25" s="22"/>
+      <c r="L25" s="22"/>
+      <c r="M25" s="22"/>
+      <c r="N25" s="22"/>
+      <c r="O25" s="22"/>
     </row>
     <row r="26" spans="2:15">
       <c r="B26" s="3"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="8"/>
-      <c r="I26" s="8"/>
-      <c r="J26" s="8"/>
-      <c r="K26" s="8"/>
-      <c r="L26" s="8"/>
-      <c r="M26" s="8"/>
-      <c r="N26" s="8"/>
-      <c r="O26" s="8"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="22"/>
+      <c r="H26" s="22"/>
+      <c r="I26" s="22"/>
+      <c r="J26" s="22"/>
+      <c r="K26" s="22"/>
+      <c r="L26" s="22"/>
+      <c r="M26" s="22"/>
+      <c r="N26" s="22"/>
+      <c r="O26" s="22"/>
     </row>
     <row r="27" spans="2:15">
       <c r="B27" s="3"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
-      <c r="H27" s="8"/>
-      <c r="I27" s="8"/>
-      <c r="J27" s="8"/>
-      <c r="K27" s="8"/>
-      <c r="L27" s="8"/>
-      <c r="M27" s="8"/>
-      <c r="N27" s="8"/>
-      <c r="O27" s="8"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="22"/>
+      <c r="H27" s="22"/>
+      <c r="I27" s="22"/>
+      <c r="J27" s="22"/>
+      <c r="K27" s="22"/>
+      <c r="L27" s="22"/>
+      <c r="M27" s="22"/>
+      <c r="N27" s="22"/>
+      <c r="O27" s="22"/>
     </row>
     <row r="28" spans="2:15">
       <c r="B28" s="3"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
-      <c r="H28" s="8"/>
-      <c r="I28" s="8"/>
-      <c r="J28" s="8"/>
-      <c r="K28" s="8"/>
-      <c r="L28" s="8"/>
-      <c r="M28" s="8"/>
-      <c r="N28" s="8"/>
-      <c r="O28" s="8"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="22"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="22"/>
+      <c r="H28" s="22"/>
+      <c r="I28" s="22"/>
+      <c r="J28" s="22"/>
+      <c r="K28" s="22"/>
+      <c r="L28" s="22"/>
+      <c r="M28" s="22"/>
+      <c r="N28" s="22"/>
+      <c r="O28" s="22"/>
     </row>
     <row r="29" spans="2:15">
       <c r="B29" s="3"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
-      <c r="I29" s="8"/>
-      <c r="J29" s="8"/>
-      <c r="K29" s="8"/>
-      <c r="L29" s="8"/>
-      <c r="M29" s="8"/>
-      <c r="N29" s="8"/>
-      <c r="O29" s="8"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="22"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="22"/>
+      <c r="H29" s="22"/>
+      <c r="I29" s="22"/>
+      <c r="J29" s="22"/>
+      <c r="K29" s="22"/>
+      <c r="L29" s="22"/>
+      <c r="M29" s="22"/>
+      <c r="N29" s="22"/>
+      <c r="O29" s="22"/>
     </row>
     <row r="30" spans="2:15">
       <c r="B30" s="3"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
-      <c r="H30" s="8"/>
-      <c r="I30" s="8"/>
-      <c r="J30" s="8"/>
-      <c r="K30" s="8"/>
-      <c r="L30" s="8"/>
-      <c r="M30" s="8"/>
-      <c r="N30" s="8"/>
-      <c r="O30" s="8"/>
+      <c r="C30" s="22"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="22"/>
+      <c r="H30" s="22"/>
+      <c r="I30" s="22"/>
+      <c r="J30" s="22"/>
+      <c r="K30" s="22"/>
+      <c r="L30" s="22"/>
+      <c r="M30" s="22"/>
+      <c r="N30" s="22"/>
+      <c r="O30" s="22"/>
     </row>
     <row r="31" spans="2:15">
       <c r="B31" s="3"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="8"/>
-      <c r="I31" s="8"/>
-      <c r="J31" s="8"/>
-      <c r="K31" s="8"/>
-      <c r="L31" s="8"/>
-      <c r="M31" s="8"/>
-      <c r="N31" s="8"/>
-      <c r="O31" s="8"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="22"/>
+      <c r="H31" s="22"/>
+      <c r="I31" s="22"/>
+      <c r="J31" s="22"/>
+      <c r="K31" s="22"/>
+      <c r="L31" s="22"/>
+      <c r="M31" s="22"/>
+      <c r="N31" s="22"/>
+      <c r="O31" s="22"/>
     </row>
     <row r="32" spans="2:15">
       <c r="B32" s="3"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="8"/>
-      <c r="H32" s="8"/>
-      <c r="I32" s="8"/>
-      <c r="J32" s="8"/>
-      <c r="K32" s="8"/>
-      <c r="L32" s="8"/>
-      <c r="M32" s="8"/>
-      <c r="N32" s="8"/>
-      <c r="O32" s="8"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="22"/>
+      <c r="H32" s="22"/>
+      <c r="I32" s="22"/>
+      <c r="J32" s="22"/>
+      <c r="K32" s="22"/>
+      <c r="L32" s="22"/>
+      <c r="M32" s="22"/>
+      <c r="N32" s="22"/>
+      <c r="O32" s="22"/>
     </row>
     <row r="33" spans="2:15">
       <c r="B33" s="3"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
-      <c r="G33" s="8"/>
-      <c r="H33" s="8"/>
-      <c r="I33" s="8"/>
-      <c r="J33" s="8"/>
-      <c r="K33" s="8"/>
-      <c r="L33" s="8"/>
-      <c r="M33" s="8"/>
-      <c r="N33" s="8"/>
-      <c r="O33" s="8"/>
+      <c r="C33" s="22"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="22"/>
+      <c r="F33" s="22"/>
+      <c r="G33" s="22"/>
+      <c r="H33" s="22"/>
+      <c r="I33" s="22"/>
+      <c r="J33" s="22"/>
+      <c r="K33" s="22"/>
+      <c r="L33" s="22"/>
+      <c r="M33" s="22"/>
+      <c r="N33" s="22"/>
+      <c r="O33" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="122">
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="G33:L33"/>
-    <mergeCell ref="M33:O33"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="G31:L31"/>
-    <mergeCell ref="M31:O31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="G32:L32"/>
-    <mergeCell ref="M32:O32"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="G29:L29"/>
-    <mergeCell ref="M29:O29"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="G30:L30"/>
-    <mergeCell ref="M30:O30"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="G27:L27"/>
-    <mergeCell ref="M27:O27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="G28:L28"/>
-    <mergeCell ref="M28:O28"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="G25:L25"/>
-    <mergeCell ref="M25:O25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="G26:L26"/>
-    <mergeCell ref="M26:O26"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="G23:L23"/>
-    <mergeCell ref="M23:O23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="G24:L24"/>
-    <mergeCell ref="M24:O24"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="G21:L21"/>
-    <mergeCell ref="M21:O21"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="G22:L22"/>
-    <mergeCell ref="M22:O22"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="G19:L19"/>
-    <mergeCell ref="M19:O19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:L20"/>
-    <mergeCell ref="M20:O20"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:L17"/>
-    <mergeCell ref="M17:O17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="G18:L18"/>
-    <mergeCell ref="M18:O18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:L15"/>
-    <mergeCell ref="M15:O15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:L16"/>
-    <mergeCell ref="M16:O16"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="M5:O5"/>
-    <mergeCell ref="G5:L5"/>
-    <mergeCell ref="M6:O6"/>
-    <mergeCell ref="A1:D2"/>
-    <mergeCell ref="E1:M2"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:L6"/>
+    <mergeCell ref="M7:O7"/>
+    <mergeCell ref="M8:O8"/>
+    <mergeCell ref="M9:O9"/>
+    <mergeCell ref="M10:O10"/>
+    <mergeCell ref="M11:O11"/>
+    <mergeCell ref="M12:O12"/>
+    <mergeCell ref="M13:O13"/>
+    <mergeCell ref="M14:O14"/>
+    <mergeCell ref="G7:L7"/>
+    <mergeCell ref="G8:L8"/>
+    <mergeCell ref="G9:L9"/>
+    <mergeCell ref="G10:L10"/>
+    <mergeCell ref="G11:L11"/>
+    <mergeCell ref="G12:L12"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="G13:L13"/>
     <mergeCell ref="C14:D14"/>
@@ -12104,20 +12028,96 @@
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="G14:L14"/>
-    <mergeCell ref="M7:O7"/>
-    <mergeCell ref="M8:O8"/>
-    <mergeCell ref="M9:O9"/>
-    <mergeCell ref="M10:O10"/>
-    <mergeCell ref="M11:O11"/>
-    <mergeCell ref="M12:O12"/>
-    <mergeCell ref="M13:O13"/>
-    <mergeCell ref="M14:O14"/>
-    <mergeCell ref="G7:L7"/>
-    <mergeCell ref="G8:L8"/>
-    <mergeCell ref="G9:L9"/>
-    <mergeCell ref="G10:L10"/>
-    <mergeCell ref="G11:L11"/>
-    <mergeCell ref="G12:L12"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="M5:O5"/>
+    <mergeCell ref="G5:L5"/>
+    <mergeCell ref="M6:O6"/>
+    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="E1:M2"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:L6"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:L17"/>
+    <mergeCell ref="M17:O17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="G18:L18"/>
+    <mergeCell ref="M18:O18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:L15"/>
+    <mergeCell ref="M15:O15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:L16"/>
+    <mergeCell ref="M16:O16"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="G21:L21"/>
+    <mergeCell ref="M21:O21"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="G22:L22"/>
+    <mergeCell ref="M22:O22"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="G19:L19"/>
+    <mergeCell ref="M19:O19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:L20"/>
+    <mergeCell ref="M20:O20"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G25:L25"/>
+    <mergeCell ref="M25:O25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="G26:L26"/>
+    <mergeCell ref="M26:O26"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="G23:L23"/>
+    <mergeCell ref="M23:O23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="G24:L24"/>
+    <mergeCell ref="M24:O24"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="G29:L29"/>
+    <mergeCell ref="M29:O29"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="G30:L30"/>
+    <mergeCell ref="M30:O30"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="G27:L27"/>
+    <mergeCell ref="M27:O27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="G28:L28"/>
+    <mergeCell ref="M28:O28"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="G33:L33"/>
+    <mergeCell ref="M33:O33"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="G31:L31"/>
+    <mergeCell ref="M31:O31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="G32:L32"/>
+    <mergeCell ref="M32:O32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -12132,76 +12132,76 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10" t="s">
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10" t="s">
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25" t="s">
         <v>155</v>
       </c>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="8" t="s">
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="O1" s="8"/>
-      <c r="P1" s="8" t="s">
+      <c r="O1" s="22"/>
+      <c r="P1" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="Q1" s="8"/>
-      <c r="R1" s="8" t="s">
+      <c r="Q1" s="22"/>
+      <c r="R1" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="8"/>
-      <c r="T1" s="8"/>
-      <c r="U1" s="8"/>
+      <c r="S1" s="22"/>
+      <c r="T1" s="22"/>
+      <c r="U1" s="22"/>
     </row>
     <row r="2" spans="1:26">
-      <c r="A2" s="10"/>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10" t="s">
+      <c r="A2" s="25"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10" t="s">
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="8" t="s">
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
+      <c r="M2" s="25"/>
+      <c r="N2" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="O2" s="8"/>
-      <c r="P2" s="9">
+      <c r="O2" s="22"/>
+      <c r="P2" s="24">
         <f>DATE(2026,4,6)</f>
         <v>46118</v>
       </c>
-      <c r="Q2" s="8"/>
-      <c r="R2" s="8" t="s">
+      <c r="Q2" s="22"/>
+      <c r="R2" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="S2" s="8"/>
-      <c r="T2" s="8"/>
-      <c r="U2" s="8"/>
+      <c r="S2" s="22"/>
+      <c r="T2" s="22"/>
+      <c r="U2" s="22"/>
     </row>
     <row r="5" spans="1:26">
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="7" t="s">
         <v>153</v>
       </c>
     </row>
@@ -12211,7 +12211,7 @@
       </c>
     </row>
     <row r="8" spans="1:26">
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="7" t="s">
         <v>154</v>
       </c>
     </row>
@@ -12221,7 +12221,7 @@
       </c>
     </row>
     <row r="11" spans="1:26">
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="7" t="s">
         <v>161</v>
       </c>
     </row>
@@ -12229,238 +12229,238 @@
       <c r="B13" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="22" t="s">
         <v>162</v>
       </c>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8" t="s">
+      <c r="D13" s="22"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="22" t="s">
         <v>163</v>
       </c>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8" t="s">
+      <c r="G13" s="22"/>
+      <c r="H13" s="22" t="s">
         <v>184</v>
       </c>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8" t="s">
+      <c r="I13" s="22"/>
+      <c r="J13" s="22"/>
+      <c r="K13" s="22" t="s">
         <v>190</v>
       </c>
-      <c r="L13" s="8"/>
-      <c r="M13" s="8"/>
-      <c r="N13" s="8" t="s">
+      <c r="L13" s="22"/>
+      <c r="M13" s="22"/>
+      <c r="N13" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="O13" s="8"/>
-      <c r="P13" s="8"/>
-      <c r="Q13" s="8"/>
-      <c r="R13" s="8"/>
-      <c r="S13" s="8"/>
-      <c r="T13" s="8" t="s">
+      <c r="O13" s="22"/>
+      <c r="P13" s="22"/>
+      <c r="Q13" s="22"/>
+      <c r="R13" s="22"/>
+      <c r="S13" s="22"/>
+      <c r="T13" s="22" t="s">
         <v>165</v>
       </c>
-      <c r="U13" s="8"/>
-      <c r="V13" s="8"/>
-      <c r="W13" s="8"/>
-      <c r="X13" s="8" t="s">
+      <c r="U13" s="22"/>
+      <c r="V13" s="22"/>
+      <c r="W13" s="22"/>
+      <c r="X13" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="Y13" s="8"/>
-      <c r="Z13" s="8"/>
+      <c r="Y13" s="22"/>
+      <c r="Z13" s="22"/>
     </row>
     <row r="14" spans="1:26">
       <c r="B14" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="22" t="s">
         <v>170</v>
       </c>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8" t="s">
+      <c r="D14" s="22"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="22" t="s">
         <v>189</v>
       </c>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8" t="s">
+      <c r="G14" s="22"/>
+      <c r="H14" s="22" t="s">
         <v>186</v>
       </c>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8" t="s">
+      <c r="I14" s="22"/>
+      <c r="J14" s="22"/>
+      <c r="K14" s="22" t="s">
         <v>188</v>
       </c>
-      <c r="L14" s="8"/>
-      <c r="M14" s="8"/>
-      <c r="N14" s="8" t="s">
+      <c r="L14" s="22"/>
+      <c r="M14" s="22"/>
+      <c r="N14" s="22" t="s">
         <v>178</v>
       </c>
-      <c r="O14" s="8"/>
-      <c r="P14" s="8"/>
-      <c r="Q14" s="8"/>
-      <c r="R14" s="8"/>
-      <c r="S14" s="8"/>
-      <c r="T14" s="8" t="s">
+      <c r="O14" s="22"/>
+      <c r="P14" s="22"/>
+      <c r="Q14" s="22"/>
+      <c r="R14" s="22"/>
+      <c r="S14" s="22"/>
+      <c r="T14" s="22" t="s">
         <v>173</v>
       </c>
-      <c r="U14" s="8"/>
-      <c r="V14" s="8"/>
-      <c r="W14" s="8"/>
-      <c r="X14" s="8"/>
-      <c r="Y14" s="8"/>
-      <c r="Z14" s="8"/>
+      <c r="U14" s="22"/>
+      <c r="V14" s="22"/>
+      <c r="W14" s="22"/>
+      <c r="X14" s="22"/>
+      <c r="Y14" s="22"/>
+      <c r="Z14" s="22"/>
     </row>
     <row r="15" spans="1:26">
       <c r="B15" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="22" t="s">
         <v>171</v>
       </c>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8" t="s">
+      <c r="D15" s="22"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8" t="s">
+      <c r="G15" s="22"/>
+      <c r="H15" s="22" t="s">
         <v>185</v>
       </c>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8" t="s">
+      <c r="I15" s="22"/>
+      <c r="J15" s="22"/>
+      <c r="K15" s="22" t="s">
         <v>191</v>
       </c>
-      <c r="L15" s="8"/>
-      <c r="M15" s="8"/>
-      <c r="N15" s="8" t="s">
+      <c r="L15" s="22"/>
+      <c r="M15" s="22"/>
+      <c r="N15" s="22" t="s">
         <v>177</v>
       </c>
-      <c r="O15" s="8"/>
-      <c r="P15" s="8"/>
-      <c r="Q15" s="8"/>
-      <c r="R15" s="8"/>
-      <c r="S15" s="8"/>
-      <c r="T15" s="8" t="s">
+      <c r="O15" s="22"/>
+      <c r="P15" s="22"/>
+      <c r="Q15" s="22"/>
+      <c r="R15" s="22"/>
+      <c r="S15" s="22"/>
+      <c r="T15" s="22" t="s">
         <v>174</v>
       </c>
-      <c r="U15" s="8"/>
-      <c r="V15" s="8"/>
-      <c r="W15" s="8"/>
-      <c r="X15" s="8"/>
-      <c r="Y15" s="8"/>
-      <c r="Z15" s="8"/>
+      <c r="U15" s="22"/>
+      <c r="V15" s="22"/>
+      <c r="W15" s="22"/>
+      <c r="X15" s="22"/>
+      <c r="Y15" s="22"/>
+      <c r="Z15" s="22"/>
     </row>
     <row r="16" spans="1:26">
       <c r="B16" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="22" t="s">
         <v>181</v>
       </c>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8" t="s">
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22" t="s">
         <v>182</v>
       </c>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8" t="s">
+      <c r="G16" s="22"/>
+      <c r="H16" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8" t="s">
+      <c r="I16" s="22"/>
+      <c r="J16" s="22"/>
+      <c r="K16" s="22" t="s">
         <v>192</v>
       </c>
-      <c r="L16" s="8"/>
-      <c r="M16" s="8"/>
-      <c r="N16" s="8" t="s">
+      <c r="L16" s="22"/>
+      <c r="M16" s="22"/>
+      <c r="N16" s="22" t="s">
         <v>179</v>
       </c>
-      <c r="O16" s="8"/>
-      <c r="P16" s="8"/>
-      <c r="Q16" s="8"/>
-      <c r="R16" s="8"/>
-      <c r="S16" s="8"/>
-      <c r="T16" s="8" t="s">
+      <c r="O16" s="22"/>
+      <c r="P16" s="22"/>
+      <c r="Q16" s="22"/>
+      <c r="R16" s="22"/>
+      <c r="S16" s="22"/>
+      <c r="T16" s="22" t="s">
         <v>175</v>
       </c>
-      <c r="U16" s="8"/>
-      <c r="V16" s="8"/>
-      <c r="W16" s="8"/>
-      <c r="X16" s="8"/>
-      <c r="Y16" s="8"/>
-      <c r="Z16" s="8"/>
+      <c r="U16" s="22"/>
+      <c r="V16" s="22"/>
+      <c r="W16" s="22"/>
+      <c r="X16" s="22"/>
+      <c r="Y16" s="22"/>
+      <c r="Z16" s="22"/>
     </row>
     <row r="17" spans="2:26">
       <c r="B17" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="22" t="s">
         <v>172</v>
       </c>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8" t="s">
+      <c r="D17" s="22"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="22" t="s">
         <v>183</v>
       </c>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8" t="s">
+      <c r="G17" s="22"/>
+      <c r="H17" s="22" t="s">
         <v>185</v>
       </c>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8" t="s">
+      <c r="I17" s="22"/>
+      <c r="J17" s="22"/>
+      <c r="K17" s="22" t="s">
         <v>193</v>
       </c>
-      <c r="L17" s="8"/>
-      <c r="M17" s="8"/>
-      <c r="N17" s="8" t="s">
+      <c r="L17" s="22"/>
+      <c r="M17" s="22"/>
+      <c r="N17" s="22" t="s">
         <v>180</v>
       </c>
-      <c r="O17" s="8"/>
-      <c r="P17" s="8"/>
-      <c r="Q17" s="8"/>
-      <c r="R17" s="8"/>
-      <c r="S17" s="8"/>
-      <c r="T17" s="8" t="s">
+      <c r="O17" s="22"/>
+      <c r="P17" s="22"/>
+      <c r="Q17" s="22"/>
+      <c r="R17" s="22"/>
+      <c r="S17" s="22"/>
+      <c r="T17" s="22" t="s">
         <v>176</v>
       </c>
-      <c r="U17" s="8"/>
-      <c r="V17" s="8"/>
-      <c r="W17" s="8"/>
-      <c r="X17" s="8"/>
-      <c r="Y17" s="8"/>
-      <c r="Z17" s="8"/>
+      <c r="U17" s="22"/>
+      <c r="V17" s="22"/>
+      <c r="W17" s="22"/>
+      <c r="X17" s="22"/>
+      <c r="Y17" s="22"/>
+      <c r="Z17" s="22"/>
     </row>
     <row r="18" spans="2:26">
       <c r="B18" s="3"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8"/>
-      <c r="L18" s="8"/>
-      <c r="M18" s="8"/>
-      <c r="N18" s="8"/>
-      <c r="O18" s="8"/>
-      <c r="P18" s="8"/>
-      <c r="Q18" s="8"/>
-      <c r="R18" s="8"/>
-      <c r="S18" s="8"/>
-      <c r="T18" s="8"/>
-      <c r="U18" s="8"/>
-      <c r="V18" s="8"/>
-      <c r="W18" s="8"/>
-      <c r="X18" s="8"/>
-      <c r="Y18" s="8"/>
-      <c r="Z18" s="8"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="22"/>
+      <c r="K18" s="22"/>
+      <c r="L18" s="22"/>
+      <c r="M18" s="22"/>
+      <c r="N18" s="22"/>
+      <c r="O18" s="22"/>
+      <c r="P18" s="22"/>
+      <c r="Q18" s="22"/>
+      <c r="R18" s="22"/>
+      <c r="S18" s="22"/>
+      <c r="T18" s="22"/>
+      <c r="U18" s="22"/>
+      <c r="V18" s="22"/>
+      <c r="W18" s="22"/>
+      <c r="X18" s="22"/>
+      <c r="Y18" s="22"/>
+      <c r="Z18" s="22"/>
     </row>
     <row r="20" spans="2:26">
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="7" t="s">
         <v>194</v>
       </c>
     </row>
@@ -12501,141 +12501,141 @@
       </c>
     </row>
     <row r="28" spans="2:26">
-      <c r="B28" s="12" t="s">
+      <c r="B28" s="7" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="30" spans="2:26">
-      <c r="B30" s="8" t="s">
+      <c r="B30" s="22" t="s">
         <v>204</v>
       </c>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8" t="s">
+      <c r="C30" s="22"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22" t="s">
         <v>205</v>
       </c>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
-      <c r="H30" s="8"/>
-      <c r="I30" s="8"/>
-      <c r="J30" s="8"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="22"/>
+      <c r="H30" s="22"/>
+      <c r="I30" s="22"/>
+      <c r="J30" s="22"/>
     </row>
     <row r="31" spans="2:26">
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="22" t="s">
         <v>206</v>
       </c>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8" t="s">
+      <c r="C31" s="22"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22" t="s">
         <v>207</v>
       </c>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="8"/>
-      <c r="I31" s="8"/>
-      <c r="J31" s="8"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="22"/>
+      <c r="H31" s="22"/>
+      <c r="I31" s="22"/>
+      <c r="J31" s="22"/>
     </row>
     <row r="32" spans="2:26">
-      <c r="B32" s="8" t="s">
+      <c r="B32" s="22" t="s">
         <v>208</v>
       </c>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8" t="s">
+      <c r="C32" s="22"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22" t="s">
         <v>211</v>
       </c>
-      <c r="F32" s="8"/>
-      <c r="G32" s="8"/>
-      <c r="H32" s="8"/>
-      <c r="I32" s="8"/>
-      <c r="J32" s="8"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="22"/>
+      <c r="H32" s="22"/>
+      <c r="I32" s="22"/>
+      <c r="J32" s="22"/>
     </row>
     <row r="33" spans="2:19">
-      <c r="B33" s="8" t="s">
+      <c r="B33" s="22" t="s">
         <v>209</v>
       </c>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8" t="s">
+      <c r="C33" s="22"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="22" t="s">
         <v>210</v>
       </c>
-      <c r="F33" s="8"/>
-      <c r="G33" s="8"/>
-      <c r="H33" s="8"/>
-      <c r="I33" s="8"/>
-      <c r="J33" s="8"/>
+      <c r="F33" s="22"/>
+      <c r="G33" s="22"/>
+      <c r="H33" s="22"/>
+      <c r="I33" s="22"/>
+      <c r="J33" s="22"/>
     </row>
     <row r="34" spans="2:19">
-      <c r="B34" s="8" t="s">
+      <c r="B34" s="22" t="s">
         <v>213</v>
       </c>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8" t="s">
+      <c r="C34" s="22"/>
+      <c r="D34" s="22"/>
+      <c r="E34" s="22" t="s">
         <v>218</v>
       </c>
-      <c r="F34" s="8"/>
-      <c r="G34" s="8"/>
-      <c r="H34" s="8"/>
-      <c r="I34" s="8"/>
-      <c r="J34" s="8"/>
+      <c r="F34" s="22"/>
+      <c r="G34" s="22"/>
+      <c r="H34" s="22"/>
+      <c r="I34" s="22"/>
+      <c r="J34" s="22"/>
     </row>
     <row r="35" spans="2:19">
-      <c r="B35" s="13" t="s">
+      <c r="B35" s="26" t="s">
         <v>212</v>
       </c>
-      <c r="C35" s="14"/>
-      <c r="D35" s="15"/>
-      <c r="E35" s="8" t="s">
+      <c r="C35" s="27"/>
+      <c r="D35" s="28"/>
+      <c r="E35" s="22" t="s">
         <v>215</v>
       </c>
-      <c r="F35" s="8"/>
-      <c r="G35" s="8"/>
-      <c r="H35" s="8"/>
-      <c r="I35" s="8"/>
-      <c r="J35" s="8"/>
+      <c r="F35" s="22"/>
+      <c r="G35" s="22"/>
+      <c r="H35" s="22"/>
+      <c r="I35" s="22"/>
+      <c r="J35" s="22"/>
     </row>
     <row r="36" spans="2:19">
-      <c r="B36" s="16"/>
-      <c r="C36" s="17"/>
-      <c r="D36" s="18"/>
-      <c r="E36" s="8" t="s">
+      <c r="B36" s="29"/>
+      <c r="C36" s="30"/>
+      <c r="D36" s="31"/>
+      <c r="E36" s="22" t="s">
         <v>214</v>
       </c>
-      <c r="F36" s="8"/>
-      <c r="G36" s="8"/>
-      <c r="H36" s="8"/>
-      <c r="I36" s="8"/>
-      <c r="J36" s="8"/>
+      <c r="F36" s="22"/>
+      <c r="G36" s="22"/>
+      <c r="H36" s="22"/>
+      <c r="I36" s="22"/>
+      <c r="J36" s="22"/>
     </row>
     <row r="37" spans="2:19">
-      <c r="B37" s="16"/>
-      <c r="C37" s="17"/>
-      <c r="D37" s="18"/>
-      <c r="E37" s="8" t="s">
+      <c r="B37" s="29"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="22" t="s">
         <v>216</v>
       </c>
-      <c r="F37" s="8"/>
-      <c r="G37" s="8"/>
-      <c r="H37" s="8"/>
-      <c r="I37" s="8"/>
-      <c r="J37" s="8"/>
+      <c r="F37" s="22"/>
+      <c r="G37" s="22"/>
+      <c r="H37" s="22"/>
+      <c r="I37" s="22"/>
+      <c r="J37" s="22"/>
     </row>
     <row r="38" spans="2:19">
-      <c r="B38" s="19"/>
-      <c r="C38" s="20"/>
-      <c r="D38" s="21"/>
-      <c r="E38" s="8" t="s">
+      <c r="B38" s="32"/>
+      <c r="C38" s="33"/>
+      <c r="D38" s="34"/>
+      <c r="E38" s="22" t="s">
         <v>217</v>
       </c>
-      <c r="F38" s="8"/>
-      <c r="G38" s="8"/>
-      <c r="H38" s="8"/>
-      <c r="I38" s="8"/>
-      <c r="J38" s="8"/>
+      <c r="F38" s="22"/>
+      <c r="G38" s="22"/>
+      <c r="H38" s="22"/>
+      <c r="I38" s="22"/>
+      <c r="J38" s="22"/>
     </row>
     <row r="40" spans="2:19">
-      <c r="B40" s="12" t="s">
+      <c r="B40" s="7" t="s">
         <v>219</v>
       </c>
     </row>
@@ -12645,31 +12645,31 @@
       </c>
     </row>
     <row r="42" spans="2:19">
-      <c r="S42" s="22"/>
+      <c r="S42" s="8"/>
     </row>
     <row r="43" spans="2:19">
       <c r="B43" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="S43" s="23"/>
+      <c r="S43" s="9"/>
     </row>
     <row r="44" spans="2:19">
       <c r="B44" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="S44" s="24"/>
+      <c r="S44" s="10"/>
     </row>
     <row r="45" spans="2:19">
-      <c r="B45" s="22" t="s">
+      <c r="B45" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="S45" s="22"/>
+      <c r="S45" s="8"/>
     </row>
     <row r="46" spans="2:19">
-      <c r="B46" s="23" t="s">
+      <c r="B46" s="9" t="s">
         <v>228</v>
       </c>
-      <c r="S46" s="23"/>
+      <c r="S46" s="9"/>
     </row>
     <row r="47" spans="2:19">
       <c r="B47" s="1" t="s">
@@ -12682,22 +12682,22 @@
       </c>
     </row>
     <row r="49" spans="1:26">
-      <c r="B49" s="22" t="s">
+      <c r="B49" s="8" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="50" spans="1:26">
-      <c r="B50" s="23" t="s">
+      <c r="B50" s="9" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="51" spans="1:26">
-      <c r="B51" s="22" t="s">
+      <c r="B51" s="8" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="52" spans="1:26">
-      <c r="B52" s="23" t="s">
+      <c r="B52" s="9" t="s">
         <v>223</v>
       </c>
     </row>
@@ -12732,8 +12732,8 @@
       </c>
     </row>
     <row r="60" spans="1:26">
-      <c r="A60" s="12"/>
-      <c r="B60" s="12" t="s">
+      <c r="A60" s="7"/>
+      <c r="B60" s="7" t="s">
         <v>236</v>
       </c>
     </row>
@@ -12741,149 +12741,149 @@
       <c r="B62" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="C62" s="8" t="s">
+      <c r="C62" s="22" t="s">
         <v>171</v>
       </c>
-      <c r="D62" s="8"/>
-      <c r="E62" s="8"/>
+      <c r="D62" s="22"/>
+      <c r="E62" s="22"/>
       <c r="I62" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="J62" s="8" t="s">
+      <c r="J62" s="22" t="s">
         <v>181</v>
       </c>
-      <c r="K62" s="8"/>
-      <c r="L62" s="8"/>
+      <c r="K62" s="22"/>
+      <c r="L62" s="22"/>
       <c r="Q62" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="R62" s="8" t="s">
+      <c r="R62" s="22" t="s">
         <v>172</v>
       </c>
-      <c r="S62" s="8"/>
-      <c r="T62" s="8"/>
-      <c r="W62" s="25"/>
-      <c r="X62" s="25"/>
-      <c r="Y62" s="25"/>
-      <c r="Z62" s="25"/>
-    </row>
-    <row r="63" spans="1:26" s="28" customFormat="1">
-      <c r="W63" s="29"/>
-      <c r="X63" s="29"/>
-      <c r="Y63" s="29"/>
-      <c r="Z63" s="29"/>
-    </row>
-    <row r="64" spans="1:26" s="28" customFormat="1"/>
-    <row r="65" s="28" customFormat="1"/>
-    <row r="66" s="28" customFormat="1"/>
-    <row r="67" s="28" customFormat="1"/>
-    <row r="68" s="28" customFormat="1"/>
-    <row r="69" s="28" customFormat="1"/>
-    <row r="70" s="28" customFormat="1"/>
-    <row r="71" s="28" customFormat="1"/>
-    <row r="72" s="28" customFormat="1"/>
-    <row r="73" s="28" customFormat="1"/>
-    <row r="74" s="28" customFormat="1"/>
-    <row r="75" s="28" customFormat="1"/>
-    <row r="76" s="30" customFormat="1"/>
-    <row r="77" s="30" customFormat="1"/>
-    <row r="78" s="31" customFormat="1"/>
-    <row r="79" s="31" customFormat="1"/>
-    <row r="80" s="31" customFormat="1"/>
-    <row r="81" spans="13:20" s="31" customFormat="1"/>
-    <row r="82" spans="13:20" s="31" customFormat="1"/>
-    <row r="83" spans="13:20" s="31" customFormat="1"/>
-    <row r="84" spans="13:20" s="31" customFormat="1"/>
-    <row r="85" spans="13:20" s="31" customFormat="1"/>
-    <row r="86" spans="13:20" s="31" customFormat="1"/>
-    <row r="87" spans="13:20" s="31" customFormat="1"/>
-    <row r="88" spans="13:20" s="32" customFormat="1"/>
-    <row r="89" spans="13:20" s="32" customFormat="1"/>
-    <row r="90" spans="13:20" s="32" customFormat="1"/>
-    <row r="91" spans="13:20" s="32" customFormat="1"/>
-    <row r="92" spans="13:20" s="32" customFormat="1"/>
-    <row r="93" spans="13:20" s="32" customFormat="1"/>
-    <row r="94" spans="13:20" s="32" customFormat="1"/>
-    <row r="95" spans="13:20" s="32" customFormat="1"/>
-    <row r="96" spans="13:20" s="32" customFormat="1">
-      <c r="M96" s="32" t="b">
+      <c r="S62" s="22"/>
+      <c r="T62" s="22"/>
+      <c r="W62" s="11"/>
+      <c r="X62" s="11"/>
+      <c r="Y62" s="11"/>
+      <c r="Z62" s="11"/>
+    </row>
+    <row r="63" spans="1:26" s="14" customFormat="1">
+      <c r="W63" s="15"/>
+      <c r="X63" s="15"/>
+      <c r="Y63" s="15"/>
+      <c r="Z63" s="15"/>
+    </row>
+    <row r="64" spans="1:26" s="14" customFormat="1"/>
+    <row r="65" s="14" customFormat="1"/>
+    <row r="66" s="14" customFormat="1"/>
+    <row r="67" s="14" customFormat="1"/>
+    <row r="68" s="14" customFormat="1"/>
+    <row r="69" s="14" customFormat="1"/>
+    <row r="70" s="14" customFormat="1"/>
+    <row r="71" s="14" customFormat="1"/>
+    <row r="72" s="14" customFormat="1"/>
+    <row r="73" s="14" customFormat="1"/>
+    <row r="74" s="14" customFormat="1"/>
+    <row r="75" s="14" customFormat="1"/>
+    <row r="76" s="16" customFormat="1"/>
+    <row r="77" s="16" customFormat="1"/>
+    <row r="78" s="17" customFormat="1"/>
+    <row r="79" s="17" customFormat="1"/>
+    <row r="80" s="17" customFormat="1"/>
+    <row r="81" spans="13:20" s="17" customFormat="1"/>
+    <row r="82" spans="13:20" s="17" customFormat="1"/>
+    <row r="83" spans="13:20" s="17" customFormat="1"/>
+    <row r="84" spans="13:20" s="17" customFormat="1"/>
+    <row r="85" spans="13:20" s="17" customFormat="1"/>
+    <row r="86" spans="13:20" s="17" customFormat="1"/>
+    <row r="87" spans="13:20" s="17" customFormat="1"/>
+    <row r="88" spans="13:20" s="18" customFormat="1"/>
+    <row r="89" spans="13:20" s="18" customFormat="1"/>
+    <row r="90" spans="13:20" s="18" customFormat="1"/>
+    <row r="91" spans="13:20" s="18" customFormat="1"/>
+    <row r="92" spans="13:20" s="18" customFormat="1"/>
+    <row r="93" spans="13:20" s="18" customFormat="1"/>
+    <row r="94" spans="13:20" s="18" customFormat="1"/>
+    <row r="95" spans="13:20" s="18" customFormat="1"/>
+    <row r="96" spans="13:20" s="18" customFormat="1">
+      <c r="M96" s="18" t="b">
         <v>1</v>
       </c>
-      <c r="T96" s="32" t="b">
+      <c r="T96" s="18" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="11:11" s="32" customFormat="1"/>
-    <row r="98" spans="11:11" s="32" customFormat="1"/>
-    <row r="99" spans="11:11" s="32" customFormat="1"/>
-    <row r="100" spans="11:11" s="32" customFormat="1"/>
-    <row r="101" spans="11:11" s="32" customFormat="1"/>
-    <row r="102" spans="11:11" s="32" customFormat="1"/>
-    <row r="103" spans="11:11" s="32" customFormat="1"/>
-    <row r="104" spans="11:11" s="32" customFormat="1"/>
-    <row r="105" spans="11:11" s="32" customFormat="1"/>
-    <row r="106" spans="11:11" s="32" customFormat="1">
-      <c r="K106" s="32" t="b">
+    <row r="97" spans="11:11" s="18" customFormat="1"/>
+    <row r="98" spans="11:11" s="18" customFormat="1"/>
+    <row r="99" spans="11:11" s="18" customFormat="1"/>
+    <row r="100" spans="11:11" s="18" customFormat="1"/>
+    <row r="101" spans="11:11" s="18" customFormat="1"/>
+    <row r="102" spans="11:11" s="18" customFormat="1"/>
+    <row r="103" spans="11:11" s="18" customFormat="1"/>
+    <row r="104" spans="11:11" s="18" customFormat="1"/>
+    <row r="105" spans="11:11" s="18" customFormat="1"/>
+    <row r="106" spans="11:11" s="18" customFormat="1">
+      <c r="K106" s="18" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="11:11" s="32" customFormat="1"/>
-    <row r="108" spans="11:11" s="32" customFormat="1"/>
-    <row r="109" spans="11:11" s="32" customFormat="1"/>
-    <row r="110" spans="11:11" s="32" customFormat="1"/>
-    <row r="111" spans="11:11" s="32" customFormat="1"/>
-    <row r="112" spans="11:11" s="32" customFormat="1"/>
-    <row r="113" spans="11:19" s="32" customFormat="1">
-      <c r="M113" s="32" t="b">
+    <row r="107" spans="11:11" s="18" customFormat="1"/>
+    <row r="108" spans="11:11" s="18" customFormat="1"/>
+    <row r="109" spans="11:11" s="18" customFormat="1"/>
+    <row r="110" spans="11:11" s="18" customFormat="1"/>
+    <row r="111" spans="11:11" s="18" customFormat="1"/>
+    <row r="112" spans="11:11" s="18" customFormat="1"/>
+    <row r="113" spans="11:19" s="18" customFormat="1">
+      <c r="M113" s="18" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="11:19" s="32" customFormat="1">
-      <c r="S114" s="32" t="s">
+    <row r="114" spans="11:19" s="18" customFormat="1">
+      <c r="S114" s="18" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="115" spans="11:19" s="32" customFormat="1"/>
-    <row r="116" spans="11:19" s="32" customFormat="1"/>
-    <row r="117" spans="11:19" s="32" customFormat="1"/>
-    <row r="118" spans="11:19" s="32" customFormat="1"/>
-    <row r="119" spans="11:19" s="32" customFormat="1"/>
-    <row r="120" spans="11:19" s="32" customFormat="1"/>
-    <row r="121" spans="11:19" s="32" customFormat="1"/>
-    <row r="122" spans="11:19" s="32" customFormat="1">
-      <c r="K122" s="32" t="b">
+    <row r="115" spans="11:19" s="18" customFormat="1"/>
+    <row r="116" spans="11:19" s="18" customFormat="1"/>
+    <row r="117" spans="11:19" s="18" customFormat="1"/>
+    <row r="118" spans="11:19" s="18" customFormat="1"/>
+    <row r="119" spans="11:19" s="18" customFormat="1"/>
+    <row r="120" spans="11:19" s="18" customFormat="1"/>
+    <row r="121" spans="11:19" s="18" customFormat="1"/>
+    <row r="122" spans="11:19" s="18" customFormat="1">
+      <c r="K122" s="18" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="11:19" s="34" customFormat="1"/>
-    <row r="124" spans="11:19" s="34" customFormat="1"/>
-    <row r="125" spans="11:19" s="34" customFormat="1"/>
-    <row r="126" spans="11:19" s="34" customFormat="1"/>
-    <row r="127" spans="11:19" s="34" customFormat="1"/>
-    <row r="128" spans="11:19" s="34" customFormat="1"/>
-    <row r="129" s="34" customFormat="1"/>
-    <row r="130" s="34" customFormat="1"/>
-    <row r="131" s="34" customFormat="1"/>
-    <row r="132" s="34" customFormat="1"/>
-    <row r="133" s="34" customFormat="1"/>
-    <row r="134" s="34" customFormat="1"/>
-    <row r="135" s="34" customFormat="1"/>
-    <row r="136" s="33" customFormat="1"/>
-    <row r="137" s="33" customFormat="1"/>
-    <row r="138" s="33" customFormat="1"/>
-    <row r="139" s="33" customFormat="1"/>
-    <row r="140" s="33" customFormat="1"/>
-    <row r="141" s="33" customFormat="1"/>
-    <row r="142" s="33" customFormat="1"/>
-    <row r="143" s="33" customFormat="1"/>
-    <row r="144" s="33" customFormat="1"/>
-    <row r="145" spans="6:6" s="33" customFormat="1"/>
-    <row r="146" spans="6:6" s="33" customFormat="1"/>
+    <row r="123" spans="11:19" s="20" customFormat="1"/>
+    <row r="124" spans="11:19" s="20" customFormat="1"/>
+    <row r="125" spans="11:19" s="20" customFormat="1"/>
+    <row r="126" spans="11:19" s="20" customFormat="1"/>
+    <row r="127" spans="11:19" s="20" customFormat="1"/>
+    <row r="128" spans="11:19" s="20" customFormat="1"/>
+    <row r="129" s="20" customFormat="1"/>
+    <row r="130" s="20" customFormat="1"/>
+    <row r="131" s="20" customFormat="1"/>
+    <row r="132" s="20" customFormat="1"/>
+    <row r="133" s="20" customFormat="1"/>
+    <row r="134" s="20" customFormat="1"/>
+    <row r="135" s="20" customFormat="1"/>
+    <row r="136" s="19" customFormat="1"/>
+    <row r="137" s="19" customFormat="1"/>
+    <row r="138" s="19" customFormat="1"/>
+    <row r="139" s="19" customFormat="1"/>
+    <row r="140" s="19" customFormat="1"/>
+    <row r="141" s="19" customFormat="1"/>
+    <row r="142" s="19" customFormat="1"/>
+    <row r="143" s="19" customFormat="1"/>
+    <row r="144" s="19" customFormat="1"/>
+    <row r="145" spans="6:6" s="19" customFormat="1"/>
+    <row r="146" spans="6:6" s="19" customFormat="1"/>
     <row r="148" spans="6:6">
-      <c r="F148" s="35"/>
+      <c r="F148" s="21"/>
     </row>
     <row r="149" spans="6:6">
-      <c r="F149" s="35"/>
+      <c r="F149" s="21"/>
     </row>
     <row r="189" spans="2:2">
       <c r="B189" s="1" t="s">
@@ -12892,24 +12892,47 @@
     </row>
   </sheetData>
   <mergeCells count="73">
-    <mergeCell ref="C62:E62"/>
-    <mergeCell ref="J62:L62"/>
-    <mergeCell ref="R62:T62"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="E33:J33"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="E34:J34"/>
-    <mergeCell ref="B35:D38"/>
-    <mergeCell ref="E35:J35"/>
-    <mergeCell ref="E36:J36"/>
-    <mergeCell ref="E37:J37"/>
-    <mergeCell ref="E38:J38"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="E30:J30"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="E31:J31"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="E32:J32"/>
+    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:M2"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="T2:U2"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="X13:Z13"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="H14:J14"/>
+    <mergeCell ref="K14:M14"/>
+    <mergeCell ref="N14:S14"/>
+    <mergeCell ref="T14:W14"/>
+    <mergeCell ref="X14:Z14"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="H13:J13"/>
+    <mergeCell ref="K13:M13"/>
+    <mergeCell ref="N13:S13"/>
+    <mergeCell ref="T13:W13"/>
+    <mergeCell ref="X15:Z15"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="K16:M16"/>
+    <mergeCell ref="N16:S16"/>
+    <mergeCell ref="T16:W16"/>
+    <mergeCell ref="X16:Z16"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="H15:J15"/>
+    <mergeCell ref="K15:M15"/>
+    <mergeCell ref="N15:S15"/>
+    <mergeCell ref="T15:W15"/>
     <mergeCell ref="X17:Z17"/>
     <mergeCell ref="C18:E18"/>
     <mergeCell ref="F18:G18"/>
@@ -12924,47 +12947,24 @@
     <mergeCell ref="K17:M17"/>
     <mergeCell ref="N17:S17"/>
     <mergeCell ref="T17:W17"/>
-    <mergeCell ref="X15:Z15"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="K16:M16"/>
-    <mergeCell ref="N16:S16"/>
-    <mergeCell ref="T16:W16"/>
-    <mergeCell ref="X16:Z16"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="H15:J15"/>
-    <mergeCell ref="K15:M15"/>
-    <mergeCell ref="N15:S15"/>
-    <mergeCell ref="T15:W15"/>
-    <mergeCell ref="X13:Z13"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="H14:J14"/>
-    <mergeCell ref="K14:M14"/>
-    <mergeCell ref="N14:S14"/>
-    <mergeCell ref="T14:W14"/>
-    <mergeCell ref="X14:Z14"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="H13:J13"/>
-    <mergeCell ref="K13:M13"/>
-    <mergeCell ref="N13:S13"/>
-    <mergeCell ref="T13:W13"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:M2"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="R2:S2"/>
-    <mergeCell ref="T2:U2"/>
-    <mergeCell ref="A1:D2"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="H1:M1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="E30:J30"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="E31:J31"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="E32:J32"/>
+    <mergeCell ref="C62:E62"/>
+    <mergeCell ref="J62:L62"/>
+    <mergeCell ref="R62:T62"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="E33:J33"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="E34:J34"/>
+    <mergeCell ref="B35:D38"/>
+    <mergeCell ref="E35:J35"/>
+    <mergeCell ref="E36:J36"/>
+    <mergeCell ref="E37:J37"/>
+    <mergeCell ref="E38:J38"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -12981,55 +12981,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10" t="s">
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="8" t="s">
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="O1" s="8"/>
-      <c r="P1" s="8" t="s">
+      <c r="O1" s="22"/>
+      <c r="P1" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="Q1" s="8"/>
+      <c r="Q1" s="22"/>
     </row>
     <row r="2" spans="1:17">
-      <c r="A2" s="10"/>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="8" t="s">
+      <c r="A2" s="25"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
+      <c r="M2" s="25"/>
+      <c r="N2" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="O2" s="8"/>
-      <c r="P2" s="9">
+      <c r="O2" s="22"/>
+      <c r="P2" s="24">
         <f>DATE(2026,4,6)</f>
         <v>46118</v>
       </c>
-      <c r="Q2" s="8"/>
+      <c r="Q2" s="22"/>
     </row>
     <row r="4" spans="1:17">
       <c r="A4" s="1" t="s">
@@ -13037,166 +13037,146 @@
       </c>
     </row>
     <row r="6" spans="1:17">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11" t="s">
+      <c r="B6" s="35"/>
+      <c r="C6" s="35" t="s">
         <v>60</v>
       </c>
-      <c r="D6" s="11"/>
+      <c r="D6" s="35"/>
     </row>
     <row r="7" spans="1:17">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8" t="s">
+      <c r="B7" s="22"/>
+      <c r="C7" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8" t="s">
+      <c r="D7" s="22"/>
+      <c r="E7" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8" t="s">
+      <c r="F7" s="22"/>
+      <c r="G7" s="22" t="s">
         <v>71</v>
       </c>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8" t="s">
+      <c r="H7" s="22"/>
+      <c r="I7" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8" t="s">
+      <c r="J7" s="22"/>
+      <c r="K7" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="L7" s="8"/>
+      <c r="L7" s="22"/>
     </row>
     <row r="8" spans="1:17">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8" t="s">
+      <c r="B8" s="22"/>
+      <c r="C8" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8" t="s">
+      <c r="D8" s="22"/>
+      <c r="E8" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8" t="s">
+      <c r="F8" s="22"/>
+      <c r="G8" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8" t="s">
+      <c r="H8" s="22"/>
+      <c r="I8" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8" t="s">
+      <c r="J8" s="22"/>
+      <c r="K8" s="22" t="s">
         <v>150</v>
       </c>
-      <c r="L8" s="8"/>
+      <c r="L8" s="22"/>
     </row>
     <row r="9" spans="1:17">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8" t="s">
+      <c r="B9" s="22"/>
+      <c r="C9" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8" t="s">
+      <c r="D9" s="22"/>
+      <c r="E9" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8" t="s">
+      <c r="F9" s="22"/>
+      <c r="G9" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8" t="s">
+      <c r="H9" s="22"/>
+      <c r="I9" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
+      <c r="J9" s="22"/>
+      <c r="K9" s="22"/>
+      <c r="L9" s="22"/>
     </row>
     <row r="10" spans="1:17">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8" t="s">
+      <c r="B10" s="22"/>
+      <c r="C10" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8" t="s">
+      <c r="D10" s="22"/>
+      <c r="E10" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8" t="s">
+      <c r="F10" s="22"/>
+      <c r="G10" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8" t="s">
+      <c r="H10" s="22"/>
+      <c r="I10" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
+      <c r="J10" s="22"/>
+      <c r="K10" s="22"/>
+      <c r="L10" s="22"/>
     </row>
     <row r="11" spans="1:17">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8" t="s">
+      <c r="B11" s="22"/>
+      <c r="C11" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8" t="s">
+      <c r="D11" s="22"/>
+      <c r="E11" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8" t="s">
+      <c r="F11" s="22"/>
+      <c r="G11" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8" t="s">
+      <c r="H11" s="22"/>
+      <c r="I11" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
+      <c r="J11" s="22"/>
+      <c r="K11" s="22"/>
+      <c r="L11" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="E1:M2"/>
-    <mergeCell ref="A1:D2"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="K11:L11"/>
     <mergeCell ref="G10:H10"/>
     <mergeCell ref="G11:H11"/>
     <mergeCell ref="I7:J7"/>
@@ -13205,11 +13185,31 @@
     <mergeCell ref="I10:J10"/>
     <mergeCell ref="I11:J11"/>
     <mergeCell ref="G7:H7"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="E1:M2"/>
+    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P1:Q1"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E8:F11">
@@ -13232,73 +13232,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10" t="s">
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10" t="s">
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25" t="s">
         <v>155</v>
       </c>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="8" t="s">
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="O1" s="8"/>
-      <c r="P1" s="8" t="s">
+      <c r="O1" s="22"/>
+      <c r="P1" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="Q1" s="8"/>
-      <c r="R1" s="8" t="s">
+      <c r="Q1" s="22"/>
+      <c r="R1" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="8"/>
-      <c r="T1" s="8"/>
-      <c r="U1" s="8"/>
+      <c r="S1" s="22"/>
+      <c r="T1" s="22"/>
+      <c r="U1" s="22"/>
     </row>
     <row r="2" spans="1:21">
-      <c r="A2" s="10"/>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10" t="s">
+      <c r="A2" s="25"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10" t="s">
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="8" t="s">
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
+      <c r="M2" s="25"/>
+      <c r="N2" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="O2" s="8"/>
-      <c r="P2" s="9">
+      <c r="O2" s="22"/>
+      <c r="P2" s="24">
         <f>DATE(2026,4,6)</f>
         <v>46118</v>
       </c>
-      <c r="Q2" s="8"/>
-      <c r="R2" s="8" t="s">
+      <c r="Q2" s="22"/>
+      <c r="R2" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="S2" s="8"/>
-      <c r="T2" s="8"/>
-      <c r="U2" s="8"/>
+      <c r="S2" s="22"/>
+      <c r="T2" s="22"/>
+      <c r="U2" s="22"/>
     </row>
     <row r="10" spans="1:21">
       <c r="B10" s="1" t="s">
@@ -13334,13 +13334,13 @@
       <c r="C43" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="S43" s="7" t="s">
+      <c r="S43" s="23" t="s">
         <v>143</v>
       </c>
-      <c r="T43" s="7"/>
-      <c r="U43" s="7"/>
-      <c r="V43" s="7"/>
-      <c r="W43" s="7"/>
+      <c r="T43" s="23"/>
+      <c r="U43" s="23"/>
+      <c r="V43" s="23"/>
+      <c r="W43" s="23"/>
       <c r="Z43" s="2"/>
       <c r="AA43" s="2"/>
       <c r="AB43" s="2"/>
@@ -13349,23 +13349,23 @@
       <c r="C44" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="Z44" s="7" t="s">
+      <c r="Z44" s="23" t="s">
         <v>159</v>
       </c>
-      <c r="AA44" s="7"/>
-      <c r="AB44" s="7"/>
-      <c r="AK44" s="7" t="s">
+      <c r="AA44" s="23"/>
+      <c r="AB44" s="23"/>
+      <c r="AK44" s="23" t="s">
         <v>145</v>
       </c>
-      <c r="AL44" s="7"/>
-      <c r="AM44" s="7"/>
-      <c r="AN44" s="7"/>
-      <c r="AO44" s="7"/>
-      <c r="AP44" s="7" t="s">
+      <c r="AL44" s="23"/>
+      <c r="AM44" s="23"/>
+      <c r="AN44" s="23"/>
+      <c r="AO44" s="23"/>
+      <c r="AP44" s="23" t="s">
         <v>147</v>
       </c>
-      <c r="AQ44" s="7"/>
-      <c r="AR44" s="7"/>
+      <c r="AQ44" s="23"/>
+      <c r="AR44" s="23"/>
     </row>
     <row r="45" spans="2:44">
       <c r="C45" s="1" t="s">
@@ -13376,24 +13376,24 @@
       <c r="AG46" s="6"/>
     </row>
     <row r="47" spans="2:44">
-      <c r="G47" s="7" t="s">
+      <c r="G47" s="23" t="s">
         <v>140</v>
       </c>
-      <c r="H47" s="7"/>
-      <c r="I47" s="7"/>
-      <c r="J47" s="7"/>
-      <c r="M47" s="7" t="s">
+      <c r="H47" s="23"/>
+      <c r="I47" s="23"/>
+      <c r="J47" s="23"/>
+      <c r="M47" s="23" t="s">
         <v>141</v>
       </c>
-      <c r="N47" s="7"/>
-      <c r="O47" s="7"/>
-      <c r="P47" s="7"/>
-      <c r="S47" s="7" t="s">
+      <c r="N47" s="23"/>
+      <c r="O47" s="23"/>
+      <c r="P47" s="23"/>
+      <c r="S47" s="23" t="s">
         <v>142</v>
       </c>
-      <c r="T47" s="7"/>
-      <c r="U47" s="7"/>
-      <c r="V47" s="7"/>
+      <c r="T47" s="23"/>
+      <c r="U47" s="23"/>
+      <c r="V47" s="23"/>
     </row>
     <row r="48" spans="2:44">
       <c r="Q48" s="1" t="s">
@@ -13422,13 +13422,11 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:D2"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="AK44:AO44"/>
+    <mergeCell ref="AP44:AR44"/>
+    <mergeCell ref="G47:J47"/>
+    <mergeCell ref="M47:P47"/>
+    <mergeCell ref="S47:V47"/>
     <mergeCell ref="S43:W43"/>
     <mergeCell ref="Z44:AB44"/>
     <mergeCell ref="R1:S1"/>
@@ -13437,11 +13435,13 @@
     <mergeCell ref="H2:M2"/>
     <mergeCell ref="R2:S2"/>
     <mergeCell ref="T2:U2"/>
-    <mergeCell ref="AK44:AO44"/>
-    <mergeCell ref="AP44:AR44"/>
-    <mergeCell ref="G47:J47"/>
-    <mergeCell ref="M47:P47"/>
-    <mergeCell ref="S47:V47"/>
+    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="H1:M1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -13718,76 +13718,76 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10" t="s">
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10" t="s">
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25" t="s">
         <v>155</v>
       </c>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="8" t="s">
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="O1" s="8"/>
-      <c r="P1" s="8" t="s">
+      <c r="O1" s="22"/>
+      <c r="P1" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="Q1" s="8"/>
-      <c r="R1" s="8" t="s">
+      <c r="Q1" s="22"/>
+      <c r="R1" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="8"/>
-      <c r="T1" s="8"/>
-      <c r="U1" s="8"/>
+      <c r="S1" s="22"/>
+      <c r="T1" s="22"/>
+      <c r="U1" s="22"/>
     </row>
     <row r="2" spans="1:26">
-      <c r="A2" s="10"/>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10" t="s">
+      <c r="A2" s="25"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10" t="s">
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="8" t="s">
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
+      <c r="M2" s="25"/>
+      <c r="N2" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="O2" s="8"/>
-      <c r="P2" s="9">
+      <c r="O2" s="22"/>
+      <c r="P2" s="24">
         <f>DATE(2026,4,6)</f>
         <v>46118</v>
       </c>
-      <c r="Q2" s="8"/>
-      <c r="R2" s="8" t="s">
+      <c r="Q2" s="22"/>
+      <c r="R2" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="S2" s="8"/>
-      <c r="T2" s="8"/>
-      <c r="U2" s="8"/>
+      <c r="S2" s="22"/>
+      <c r="T2" s="22"/>
+      <c r="U2" s="22"/>
     </row>
     <row r="5" spans="1:26">
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="7" t="s">
         <v>153</v>
       </c>
     </row>
@@ -13797,7 +13797,7 @@
       </c>
     </row>
     <row r="8" spans="1:26">
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="7" t="s">
         <v>154</v>
       </c>
     </row>
@@ -13807,7 +13807,7 @@
       </c>
     </row>
     <row r="11" spans="1:26">
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="7" t="s">
         <v>161</v>
       </c>
     </row>
@@ -13815,238 +13815,238 @@
       <c r="B13" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="22" t="s">
         <v>162</v>
       </c>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8" t="s">
+      <c r="D13" s="22"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="22" t="s">
         <v>163</v>
       </c>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8" t="s">
+      <c r="G13" s="22"/>
+      <c r="H13" s="22" t="s">
         <v>184</v>
       </c>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8" t="s">
+      <c r="I13" s="22"/>
+      <c r="J13" s="22"/>
+      <c r="K13" s="22" t="s">
         <v>190</v>
       </c>
-      <c r="L13" s="8"/>
-      <c r="M13" s="8"/>
-      <c r="N13" s="8" t="s">
+      <c r="L13" s="22"/>
+      <c r="M13" s="22"/>
+      <c r="N13" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="O13" s="8"/>
-      <c r="P13" s="8"/>
-      <c r="Q13" s="8"/>
-      <c r="R13" s="8"/>
-      <c r="S13" s="8"/>
-      <c r="T13" s="8" t="s">
+      <c r="O13" s="22"/>
+      <c r="P13" s="22"/>
+      <c r="Q13" s="22"/>
+      <c r="R13" s="22"/>
+      <c r="S13" s="22"/>
+      <c r="T13" s="22" t="s">
         <v>165</v>
       </c>
-      <c r="U13" s="8"/>
-      <c r="V13" s="8"/>
-      <c r="W13" s="8"/>
-      <c r="X13" s="8" t="s">
+      <c r="U13" s="22"/>
+      <c r="V13" s="22"/>
+      <c r="W13" s="22"/>
+      <c r="X13" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="Y13" s="8"/>
-      <c r="Z13" s="8"/>
+      <c r="Y13" s="22"/>
+      <c r="Z13" s="22"/>
     </row>
     <row r="14" spans="1:26">
       <c r="B14" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="22" t="s">
         <v>170</v>
       </c>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8" t="s">
+      <c r="D14" s="22"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="22" t="s">
         <v>189</v>
       </c>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8" t="s">
+      <c r="G14" s="22"/>
+      <c r="H14" s="22" t="s">
         <v>186</v>
       </c>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8" t="s">
+      <c r="I14" s="22"/>
+      <c r="J14" s="22"/>
+      <c r="K14" s="22" t="s">
         <v>188</v>
       </c>
-      <c r="L14" s="8"/>
-      <c r="M14" s="8"/>
-      <c r="N14" s="8" t="s">
+      <c r="L14" s="22"/>
+      <c r="M14" s="22"/>
+      <c r="N14" s="22" t="s">
         <v>178</v>
       </c>
-      <c r="O14" s="8"/>
-      <c r="P14" s="8"/>
-      <c r="Q14" s="8"/>
-      <c r="R14" s="8"/>
-      <c r="S14" s="8"/>
-      <c r="T14" s="8" t="s">
+      <c r="O14" s="22"/>
+      <c r="P14" s="22"/>
+      <c r="Q14" s="22"/>
+      <c r="R14" s="22"/>
+      <c r="S14" s="22"/>
+      <c r="T14" s="22" t="s">
         <v>173</v>
       </c>
-      <c r="U14" s="8"/>
-      <c r="V14" s="8"/>
-      <c r="W14" s="8"/>
-      <c r="X14" s="8"/>
-      <c r="Y14" s="8"/>
-      <c r="Z14" s="8"/>
+      <c r="U14" s="22"/>
+      <c r="V14" s="22"/>
+      <c r="W14" s="22"/>
+      <c r="X14" s="22"/>
+      <c r="Y14" s="22"/>
+      <c r="Z14" s="22"/>
     </row>
     <row r="15" spans="1:26">
       <c r="B15" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="22" t="s">
         <v>171</v>
       </c>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8" t="s">
+      <c r="D15" s="22"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8" t="s">
+      <c r="G15" s="22"/>
+      <c r="H15" s="22" t="s">
         <v>185</v>
       </c>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8" t="s">
+      <c r="I15" s="22"/>
+      <c r="J15" s="22"/>
+      <c r="K15" s="22" t="s">
         <v>191</v>
       </c>
-      <c r="L15" s="8"/>
-      <c r="M15" s="8"/>
-      <c r="N15" s="8" t="s">
+      <c r="L15" s="22"/>
+      <c r="M15" s="22"/>
+      <c r="N15" s="22" t="s">
         <v>177</v>
       </c>
-      <c r="O15" s="8"/>
-      <c r="P15" s="8"/>
-      <c r="Q15" s="8"/>
-      <c r="R15" s="8"/>
-      <c r="S15" s="8"/>
-      <c r="T15" s="8" t="s">
+      <c r="O15" s="22"/>
+      <c r="P15" s="22"/>
+      <c r="Q15" s="22"/>
+      <c r="R15" s="22"/>
+      <c r="S15" s="22"/>
+      <c r="T15" s="22" t="s">
         <v>174</v>
       </c>
-      <c r="U15" s="8"/>
-      <c r="V15" s="8"/>
-      <c r="W15" s="8"/>
-      <c r="X15" s="8"/>
-      <c r="Y15" s="8"/>
-      <c r="Z15" s="8"/>
+      <c r="U15" s="22"/>
+      <c r="V15" s="22"/>
+      <c r="W15" s="22"/>
+      <c r="X15" s="22"/>
+      <c r="Y15" s="22"/>
+      <c r="Z15" s="22"/>
     </row>
     <row r="16" spans="1:26">
       <c r="B16" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="22" t="s">
         <v>181</v>
       </c>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8" t="s">
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22" t="s">
         <v>182</v>
       </c>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8" t="s">
+      <c r="G16" s="22"/>
+      <c r="H16" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8" t="s">
+      <c r="I16" s="22"/>
+      <c r="J16" s="22"/>
+      <c r="K16" s="22" t="s">
         <v>192</v>
       </c>
-      <c r="L16" s="8"/>
-      <c r="M16" s="8"/>
-      <c r="N16" s="8" t="s">
+      <c r="L16" s="22"/>
+      <c r="M16" s="22"/>
+      <c r="N16" s="22" t="s">
         <v>179</v>
       </c>
-      <c r="O16" s="8"/>
-      <c r="P16" s="8"/>
-      <c r="Q16" s="8"/>
-      <c r="R16" s="8"/>
-      <c r="S16" s="8"/>
-      <c r="T16" s="8" t="s">
+      <c r="O16" s="22"/>
+      <c r="P16" s="22"/>
+      <c r="Q16" s="22"/>
+      <c r="R16" s="22"/>
+      <c r="S16" s="22"/>
+      <c r="T16" s="22" t="s">
         <v>175</v>
       </c>
-      <c r="U16" s="8"/>
-      <c r="V16" s="8"/>
-      <c r="W16" s="8"/>
-      <c r="X16" s="8"/>
-      <c r="Y16" s="8"/>
-      <c r="Z16" s="8"/>
+      <c r="U16" s="22"/>
+      <c r="V16" s="22"/>
+      <c r="W16" s="22"/>
+      <c r="X16" s="22"/>
+      <c r="Y16" s="22"/>
+      <c r="Z16" s="22"/>
     </row>
     <row r="17" spans="2:26">
       <c r="B17" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="22" t="s">
         <v>172</v>
       </c>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8" t="s">
+      <c r="D17" s="22"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="22" t="s">
         <v>183</v>
       </c>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8" t="s">
+      <c r="G17" s="22"/>
+      <c r="H17" s="22" t="s">
         <v>185</v>
       </c>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8" t="s">
+      <c r="I17" s="22"/>
+      <c r="J17" s="22"/>
+      <c r="K17" s="22" t="s">
         <v>193</v>
       </c>
-      <c r="L17" s="8"/>
-      <c r="M17" s="8"/>
-      <c r="N17" s="8" t="s">
+      <c r="L17" s="22"/>
+      <c r="M17" s="22"/>
+      <c r="N17" s="22" t="s">
         <v>180</v>
       </c>
-      <c r="O17" s="8"/>
-      <c r="P17" s="8"/>
-      <c r="Q17" s="8"/>
-      <c r="R17" s="8"/>
-      <c r="S17" s="8"/>
-      <c r="T17" s="8" t="s">
+      <c r="O17" s="22"/>
+      <c r="P17" s="22"/>
+      <c r="Q17" s="22"/>
+      <c r="R17" s="22"/>
+      <c r="S17" s="22"/>
+      <c r="T17" s="22" t="s">
         <v>176</v>
       </c>
-      <c r="U17" s="8"/>
-      <c r="V17" s="8"/>
-      <c r="W17" s="8"/>
-      <c r="X17" s="8"/>
-      <c r="Y17" s="8"/>
-      <c r="Z17" s="8"/>
+      <c r="U17" s="22"/>
+      <c r="V17" s="22"/>
+      <c r="W17" s="22"/>
+      <c r="X17" s="22"/>
+      <c r="Y17" s="22"/>
+      <c r="Z17" s="22"/>
     </row>
     <row r="18" spans="2:26">
       <c r="B18" s="3"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8"/>
-      <c r="L18" s="8"/>
-      <c r="M18" s="8"/>
-      <c r="N18" s="8"/>
-      <c r="O18" s="8"/>
-      <c r="P18" s="8"/>
-      <c r="Q18" s="8"/>
-      <c r="R18" s="8"/>
-      <c r="S18" s="8"/>
-      <c r="T18" s="8"/>
-      <c r="U18" s="8"/>
-      <c r="V18" s="8"/>
-      <c r="W18" s="8"/>
-      <c r="X18" s="8"/>
-      <c r="Y18" s="8"/>
-      <c r="Z18" s="8"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="22"/>
+      <c r="K18" s="22"/>
+      <c r="L18" s="22"/>
+      <c r="M18" s="22"/>
+      <c r="N18" s="22"/>
+      <c r="O18" s="22"/>
+      <c r="P18" s="22"/>
+      <c r="Q18" s="22"/>
+      <c r="R18" s="22"/>
+      <c r="S18" s="22"/>
+      <c r="T18" s="22"/>
+      <c r="U18" s="22"/>
+      <c r="V18" s="22"/>
+      <c r="W18" s="22"/>
+      <c r="X18" s="22"/>
+      <c r="Y18" s="22"/>
+      <c r="Z18" s="22"/>
     </row>
     <row r="20" spans="2:26">
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="7" t="s">
         <v>194</v>
       </c>
     </row>
@@ -14087,141 +14087,141 @@
       </c>
     </row>
     <row r="28" spans="2:26">
-      <c r="B28" s="12" t="s">
+      <c r="B28" s="7" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="30" spans="2:26">
-      <c r="B30" s="8" t="s">
+      <c r="B30" s="22" t="s">
         <v>204</v>
       </c>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8" t="s">
+      <c r="C30" s="22"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22" t="s">
         <v>205</v>
       </c>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
-      <c r="H30" s="8"/>
-      <c r="I30" s="8"/>
-      <c r="J30" s="8"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="22"/>
+      <c r="H30" s="22"/>
+      <c r="I30" s="22"/>
+      <c r="J30" s="22"/>
     </row>
     <row r="31" spans="2:26">
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="22" t="s">
         <v>206</v>
       </c>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8" t="s">
+      <c r="C31" s="22"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22" t="s">
         <v>207</v>
       </c>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="8"/>
-      <c r="I31" s="8"/>
-      <c r="J31" s="8"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="22"/>
+      <c r="H31" s="22"/>
+      <c r="I31" s="22"/>
+      <c r="J31" s="22"/>
     </row>
     <row r="32" spans="2:26">
-      <c r="B32" s="8" t="s">
+      <c r="B32" s="22" t="s">
         <v>208</v>
       </c>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8" t="s">
+      <c r="C32" s="22"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22" t="s">
         <v>211</v>
       </c>
-      <c r="F32" s="8"/>
-      <c r="G32" s="8"/>
-      <c r="H32" s="8"/>
-      <c r="I32" s="8"/>
-      <c r="J32" s="8"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="22"/>
+      <c r="H32" s="22"/>
+      <c r="I32" s="22"/>
+      <c r="J32" s="22"/>
     </row>
     <row r="33" spans="2:19">
-      <c r="B33" s="8" t="s">
+      <c r="B33" s="22" t="s">
         <v>209</v>
       </c>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8" t="s">
+      <c r="C33" s="22"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="22" t="s">
         <v>210</v>
       </c>
-      <c r="F33" s="8"/>
-      <c r="G33" s="8"/>
-      <c r="H33" s="8"/>
-      <c r="I33" s="8"/>
-      <c r="J33" s="8"/>
+      <c r="F33" s="22"/>
+      <c r="G33" s="22"/>
+      <c r="H33" s="22"/>
+      <c r="I33" s="22"/>
+      <c r="J33" s="22"/>
     </row>
     <row r="34" spans="2:19">
-      <c r="B34" s="8" t="s">
+      <c r="B34" s="22" t="s">
         <v>213</v>
       </c>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8" t="s">
+      <c r="C34" s="22"/>
+      <c r="D34" s="22"/>
+      <c r="E34" s="22" t="s">
         <v>218</v>
       </c>
-      <c r="F34" s="8"/>
-      <c r="G34" s="8"/>
-      <c r="H34" s="8"/>
-      <c r="I34" s="8"/>
-      <c r="J34" s="8"/>
+      <c r="F34" s="22"/>
+      <c r="G34" s="22"/>
+      <c r="H34" s="22"/>
+      <c r="I34" s="22"/>
+      <c r="J34" s="22"/>
     </row>
     <row r="35" spans="2:19">
-      <c r="B35" s="13" t="s">
+      <c r="B35" s="26" t="s">
         <v>212</v>
       </c>
-      <c r="C35" s="14"/>
-      <c r="D35" s="15"/>
-      <c r="E35" s="8" t="s">
+      <c r="C35" s="27"/>
+      <c r="D35" s="28"/>
+      <c r="E35" s="22" t="s">
         <v>215</v>
       </c>
-      <c r="F35" s="8"/>
-      <c r="G35" s="8"/>
-      <c r="H35" s="8"/>
-      <c r="I35" s="8"/>
-      <c r="J35" s="8"/>
+      <c r="F35" s="22"/>
+      <c r="G35" s="22"/>
+      <c r="H35" s="22"/>
+      <c r="I35" s="22"/>
+      <c r="J35" s="22"/>
     </row>
     <row r="36" spans="2:19">
-      <c r="B36" s="16"/>
-      <c r="C36" s="17"/>
-      <c r="D36" s="18"/>
-      <c r="E36" s="8" t="s">
+      <c r="B36" s="29"/>
+      <c r="C36" s="30"/>
+      <c r="D36" s="31"/>
+      <c r="E36" s="22" t="s">
         <v>214</v>
       </c>
-      <c r="F36" s="8"/>
-      <c r="G36" s="8"/>
-      <c r="H36" s="8"/>
-      <c r="I36" s="8"/>
-      <c r="J36" s="8"/>
+      <c r="F36" s="22"/>
+      <c r="G36" s="22"/>
+      <c r="H36" s="22"/>
+      <c r="I36" s="22"/>
+      <c r="J36" s="22"/>
     </row>
     <row r="37" spans="2:19">
-      <c r="B37" s="16"/>
-      <c r="C37" s="17"/>
-      <c r="D37" s="18"/>
-      <c r="E37" s="8" t="s">
+      <c r="B37" s="29"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="22" t="s">
         <v>216</v>
       </c>
-      <c r="F37" s="8"/>
-      <c r="G37" s="8"/>
-      <c r="H37" s="8"/>
-      <c r="I37" s="8"/>
-      <c r="J37" s="8"/>
+      <c r="F37" s="22"/>
+      <c r="G37" s="22"/>
+      <c r="H37" s="22"/>
+      <c r="I37" s="22"/>
+      <c r="J37" s="22"/>
     </row>
     <row r="38" spans="2:19">
-      <c r="B38" s="19"/>
-      <c r="C38" s="20"/>
-      <c r="D38" s="21"/>
-      <c r="E38" s="8" t="s">
+      <c r="B38" s="32"/>
+      <c r="C38" s="33"/>
+      <c r="D38" s="34"/>
+      <c r="E38" s="22" t="s">
         <v>217</v>
       </c>
-      <c r="F38" s="8"/>
-      <c r="G38" s="8"/>
-      <c r="H38" s="8"/>
-      <c r="I38" s="8"/>
-      <c r="J38" s="8"/>
+      <c r="F38" s="22"/>
+      <c r="G38" s="22"/>
+      <c r="H38" s="22"/>
+      <c r="I38" s="22"/>
+      <c r="J38" s="22"/>
     </row>
     <row r="40" spans="2:19">
-      <c r="B40" s="12" t="s">
+      <c r="B40" s="7" t="s">
         <v>219</v>
       </c>
     </row>
@@ -14231,31 +14231,31 @@
       </c>
     </row>
     <row r="42" spans="2:19">
-      <c r="S42" s="22"/>
+      <c r="S42" s="8"/>
     </row>
     <row r="43" spans="2:19">
       <c r="B43" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="S43" s="23"/>
+      <c r="S43" s="9"/>
     </row>
     <row r="44" spans="2:19">
       <c r="B44" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="S44" s="24"/>
+      <c r="S44" s="10"/>
     </row>
     <row r="45" spans="2:19">
-      <c r="B45" s="22" t="s">
+      <c r="B45" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="S45" s="22"/>
+      <c r="S45" s="8"/>
     </row>
     <row r="46" spans="2:19">
-      <c r="B46" s="23" t="s">
+      <c r="B46" s="9" t="s">
         <v>228</v>
       </c>
-      <c r="S46" s="23"/>
+      <c r="S46" s="9"/>
     </row>
     <row r="47" spans="2:19">
       <c r="B47" s="1" t="s">
@@ -14268,22 +14268,22 @@
       </c>
     </row>
     <row r="49" spans="1:26">
-      <c r="B49" s="22" t="s">
+      <c r="B49" s="8" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="50" spans="1:26">
-      <c r="B50" s="23" t="s">
+      <c r="B50" s="9" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="51" spans="1:26">
-      <c r="B51" s="22" t="s">
+      <c r="B51" s="8" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="52" spans="1:26">
-      <c r="B52" s="23" t="s">
+      <c r="B52" s="9" t="s">
         <v>223</v>
       </c>
     </row>
@@ -14318,8 +14318,8 @@
       </c>
     </row>
     <row r="60" spans="1:26">
-      <c r="A60" s="12"/>
-      <c r="B60" s="12" t="s">
+      <c r="A60" s="7"/>
+      <c r="B60" s="7" t="s">
         <v>236</v>
       </c>
     </row>
@@ -14327,50 +14327,50 @@
       <c r="B62" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="C62" s="8" t="s">
+      <c r="C62" s="22" t="s">
         <v>171</v>
       </c>
-      <c r="D62" s="8"/>
-      <c r="E62" s="8"/>
+      <c r="D62" s="22"/>
+      <c r="E62" s="22"/>
       <c r="I62" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="J62" s="8" t="s">
+      <c r="J62" s="22" t="s">
         <v>181</v>
       </c>
-      <c r="K62" s="8"/>
-      <c r="L62" s="8"/>
+      <c r="K62" s="22"/>
+      <c r="L62" s="22"/>
       <c r="Q62" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="R62" s="8" t="s">
+      <c r="R62" s="22" t="s">
         <v>172</v>
       </c>
-      <c r="S62" s="8"/>
-      <c r="T62" s="8"/>
-      <c r="W62" s="25"/>
-      <c r="X62" s="25"/>
-      <c r="Y62" s="25"/>
-      <c r="Z62" s="25"/>
-    </row>
-    <row r="63" spans="1:26" s="26" customFormat="1">
-      <c r="W63" s="27"/>
-      <c r="X63" s="27"/>
-      <c r="Y63" s="27"/>
-      <c r="Z63" s="27"/>
-    </row>
-    <row r="64" spans="1:26" s="26" customFormat="1"/>
-    <row r="65" s="26" customFormat="1"/>
-    <row r="66" s="26" customFormat="1"/>
-    <row r="67" s="26" customFormat="1"/>
-    <row r="68" s="26" customFormat="1"/>
-    <row r="69" s="26" customFormat="1"/>
-    <row r="70" s="26" customFormat="1"/>
-    <row r="71" s="26" customFormat="1"/>
-    <row r="72" s="26" customFormat="1"/>
-    <row r="73" s="26" customFormat="1"/>
-    <row r="74" s="26" customFormat="1"/>
-    <row r="75" s="26" customFormat="1"/>
+      <c r="S62" s="22"/>
+      <c r="T62" s="22"/>
+      <c r="W62" s="11"/>
+      <c r="X62" s="11"/>
+      <c r="Y62" s="11"/>
+      <c r="Z62" s="11"/>
+    </row>
+    <row r="63" spans="1:26" s="12" customFormat="1">
+      <c r="W63" s="13"/>
+      <c r="X63" s="13"/>
+      <c r="Y63" s="13"/>
+      <c r="Z63" s="13"/>
+    </row>
+    <row r="64" spans="1:26" s="12" customFormat="1"/>
+    <row r="65" s="12" customFormat="1"/>
+    <row r="66" s="12" customFormat="1"/>
+    <row r="67" s="12" customFormat="1"/>
+    <row r="68" s="12" customFormat="1"/>
+    <row r="69" s="12" customFormat="1"/>
+    <row r="70" s="12" customFormat="1"/>
+    <row r="71" s="12" customFormat="1"/>
+    <row r="72" s="12" customFormat="1"/>
+    <row r="73" s="12" customFormat="1"/>
+    <row r="74" s="12" customFormat="1"/>
+    <row r="75" s="12" customFormat="1"/>
     <row r="88" spans="12:12">
       <c r="L88" s="1" t="b">
         <v>1</v>
@@ -14398,23 +14398,46 @@
     </row>
   </sheetData>
   <mergeCells count="73">
-    <mergeCell ref="E38:J38"/>
-    <mergeCell ref="B35:D38"/>
-    <mergeCell ref="R62:T62"/>
-    <mergeCell ref="C62:E62"/>
-    <mergeCell ref="J62:L62"/>
-    <mergeCell ref="E31:J31"/>
-    <mergeCell ref="E32:J32"/>
-    <mergeCell ref="E33:J33"/>
-    <mergeCell ref="E34:J34"/>
-    <mergeCell ref="E35:J35"/>
-    <mergeCell ref="E36:J36"/>
-    <mergeCell ref="E37:J37"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:M2"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="T2:U2"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="K13:M13"/>
+    <mergeCell ref="N13:S13"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="K15:M15"/>
+    <mergeCell ref="N15:S15"/>
+    <mergeCell ref="T15:W15"/>
+    <mergeCell ref="T13:W13"/>
+    <mergeCell ref="T14:W14"/>
+    <mergeCell ref="N14:S14"/>
+    <mergeCell ref="K14:M14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="T18:W18"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="K16:M16"/>
+    <mergeCell ref="N16:S16"/>
+    <mergeCell ref="T16:W16"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="K17:M17"/>
+    <mergeCell ref="N17:S17"/>
+    <mergeCell ref="T17:W17"/>
+    <mergeCell ref="H18:J18"/>
     <mergeCell ref="E30:J30"/>
     <mergeCell ref="X18:Z18"/>
     <mergeCell ref="H13:J13"/>
@@ -14431,46 +14454,23 @@
     <mergeCell ref="F18:G18"/>
     <mergeCell ref="K18:M18"/>
     <mergeCell ref="N18:S18"/>
-    <mergeCell ref="T18:W18"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="K16:M16"/>
-    <mergeCell ref="N16:S16"/>
-    <mergeCell ref="T16:W16"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="K17:M17"/>
-    <mergeCell ref="N17:S17"/>
-    <mergeCell ref="T17:W17"/>
-    <mergeCell ref="T13:W13"/>
-    <mergeCell ref="T14:W14"/>
-    <mergeCell ref="N14:S14"/>
-    <mergeCell ref="K14:M14"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="K15:M15"/>
-    <mergeCell ref="N15:S15"/>
-    <mergeCell ref="T15:W15"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="K13:M13"/>
-    <mergeCell ref="N13:S13"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:M2"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="R2:S2"/>
-    <mergeCell ref="T2:U2"/>
-    <mergeCell ref="A1:D2"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="H1:M1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="E31:J31"/>
+    <mergeCell ref="E32:J32"/>
+    <mergeCell ref="E33:J33"/>
+    <mergeCell ref="E34:J34"/>
+    <mergeCell ref="E35:J35"/>
+    <mergeCell ref="E38:J38"/>
+    <mergeCell ref="B35:D38"/>
+    <mergeCell ref="R62:T62"/>
+    <mergeCell ref="C62:E62"/>
+    <mergeCell ref="J62:L62"/>
+    <mergeCell ref="E36:J36"/>
+    <mergeCell ref="E37:J37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/詳細設計＿練習.xlsx
+++ b/詳細設計＿練習.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="244">
   <si>
     <t>レイアウト</t>
   </si>
@@ -928,6 +928,18 @@
   </si>
   <si>
     <t>上記では３件処理について、処理フローを作成しております。</t>
+  </si>
+  <si>
+    <t>3. 制約事項</t>
+  </si>
+  <si>
+    <t>4. 技術スタック</t>
+  </si>
+  <si>
+    <t>5. 業務ルール・制約事項</t>
+  </si>
+  <si>
+    <t>6. 処理フロー</t>
   </si>
 </sst>
 </file>
@@ -1217,10 +1229,10 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -11331,95 +11343,100 @@
   </cols>
   <sheetData>
     <row r="19" spans="3:18">
-      <c r="C19" s="22" t="s">
+      <c r="C19" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="D19" s="22"/>
-      <c r="E19" s="22" t="s">
+      <c r="D19" s="23"/>
+      <c r="E19" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="F19" s="22"/>
-      <c r="G19" s="22"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="23"/>
     </row>
     <row r="20" spans="3:18">
-      <c r="C20" s="22" t="s">
+      <c r="C20" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="D20" s="22"/>
-      <c r="E20" s="22" t="s">
+      <c r="D20" s="23"/>
+      <c r="E20" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="F20" s="22"/>
-      <c r="G20" s="22"/>
+      <c r="F20" s="23"/>
+      <c r="G20" s="23"/>
     </row>
     <row r="21" spans="3:18">
-      <c r="C21" s="22" t="s">
+      <c r="C21" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D21" s="22"/>
+      <c r="D21" s="23"/>
       <c r="E21" s="24">
         <f>DATE(2026,4,6)</f>
         <v>46118</v>
       </c>
-      <c r="F21" s="22"/>
-      <c r="G21" s="22"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="23"/>
     </row>
     <row r="22" spans="3:18">
-      <c r="C22" s="22" t="s">
+      <c r="C22" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22" t="s">
+      <c r="D22" s="23"/>
+      <c r="E22" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
+      <c r="F22" s="23"/>
+      <c r="G22" s="23"/>
     </row>
     <row r="23" spans="3:18">
-      <c r="C23" s="22" t="s">
+      <c r="C23" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22" t="s">
+      <c r="D23" s="23"/>
+      <c r="E23" s="23" t="s">
         <v>155</v>
       </c>
-      <c r="F23" s="22"/>
-      <c r="G23" s="22"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="23"/>
     </row>
     <row r="24" spans="3:18">
-      <c r="C24" s="22" t="s">
+      <c r="C24" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="D24" s="22"/>
-      <c r="E24" s="22"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="22"/>
+      <c r="D24" s="23"/>
+      <c r="E24" s="23"/>
+      <c r="F24" s="23"/>
+      <c r="G24" s="23"/>
     </row>
     <row r="25" spans="3:18">
-      <c r="C25" s="22" t="s">
+      <c r="C25" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="D25" s="22"/>
-      <c r="E25" s="22"/>
-      <c r="F25" s="22"/>
-      <c r="G25" s="22"/>
-      <c r="O25" s="23" t="s">
+      <c r="D25" s="23"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="23"/>
+      <c r="G25" s="23"/>
+      <c r="O25" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="P25" s="23"/>
-      <c r="Q25" s="23"/>
-      <c r="R25" s="23"/>
+      <c r="P25" s="22"/>
+      <c r="Q25" s="22"/>
+      <c r="R25" s="22"/>
     </row>
     <row r="26" spans="3:18">
-      <c r="O26" s="23" t="s">
+      <c r="O26" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="P26" s="23"/>
-      <c r="Q26" s="23"/>
-      <c r="R26" s="23"/>
+      <c r="P26" s="22"/>
+      <c r="Q26" s="22"/>
+      <c r="R26" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C22:D22"/>
     <mergeCell ref="O25:R25"/>
     <mergeCell ref="O26:R26"/>
     <mergeCell ref="C24:D24"/>
@@ -11431,11 +11448,6 @@
     <mergeCell ref="E24:G24"/>
     <mergeCell ref="E25:G25"/>
     <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:G19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C22:D22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -11469,14 +11481,14 @@
       <c r="K1" s="25"/>
       <c r="L1" s="25"/>
       <c r="M1" s="25"/>
-      <c r="N1" s="22" t="s">
+      <c r="N1" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="O1" s="22"/>
-      <c r="P1" s="22" t="s">
+      <c r="O1" s="23"/>
+      <c r="P1" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="Q1" s="22"/>
+      <c r="Q1" s="23"/>
     </row>
     <row r="2" spans="1:17">
       <c r="A2" s="25"/>
@@ -11492,524 +11504,600 @@
       <c r="K2" s="25"/>
       <c r="L2" s="25"/>
       <c r="M2" s="25"/>
-      <c r="N2" s="22" t="s">
+      <c r="N2" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="O2" s="22"/>
+      <c r="O2" s="23"/>
       <c r="P2" s="24">
         <f>DATE(2026,4,6)</f>
         <v>46118</v>
       </c>
-      <c r="Q2" s="22"/>
+      <c r="Q2" s="23"/>
     </row>
     <row r="5" spans="1:17">
       <c r="B5" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22" t="s">
+      <c r="D5" s="23"/>
+      <c r="E5" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="F5" s="22"/>
-      <c r="G5" s="22" t="s">
+      <c r="F5" s="23"/>
+      <c r="G5" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="H5" s="22"/>
-      <c r="I5" s="22"/>
-      <c r="J5" s="22"/>
-      <c r="K5" s="22"/>
-      <c r="L5" s="22"/>
-      <c r="M5" s="22" t="s">
+      <c r="H5" s="23"/>
+      <c r="I5" s="23"/>
+      <c r="J5" s="23"/>
+      <c r="K5" s="23"/>
+      <c r="L5" s="23"/>
+      <c r="M5" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N5" s="22"/>
-      <c r="O5" s="22"/>
+      <c r="N5" s="23"/>
+      <c r="O5" s="23"/>
     </row>
     <row r="6" spans="1:17">
       <c r="B6" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="D6" s="22"/>
+      <c r="D6" s="23"/>
       <c r="E6" s="24">
         <f>DATE(2026,4,6)</f>
         <v>46118</v>
       </c>
-      <c r="F6" s="22"/>
-      <c r="G6" s="22" t="s">
+      <c r="F6" s="23"/>
+      <c r="G6" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="H6" s="22"/>
-      <c r="I6" s="22"/>
-      <c r="J6" s="22"/>
-      <c r="K6" s="22"/>
-      <c r="L6" s="22"/>
-      <c r="M6" s="22"/>
-      <c r="N6" s="22"/>
-      <c r="O6" s="22"/>
+      <c r="H6" s="23"/>
+      <c r="I6" s="23"/>
+      <c r="J6" s="23"/>
+      <c r="K6" s="23"/>
+      <c r="L6" s="23"/>
+      <c r="M6" s="23"/>
+      <c r="N6" s="23"/>
+      <c r="O6" s="23"/>
     </row>
     <row r="7" spans="1:17">
       <c r="B7" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="22"/>
+      <c r="D7" s="23"/>
       <c r="E7" s="24">
         <f>DATE(2026,4,7)</f>
         <v>46119</v>
       </c>
-      <c r="F7" s="22"/>
-      <c r="G7" s="22" t="s">
+      <c r="F7" s="23"/>
+      <c r="G7" s="23" t="s">
         <v>152</v>
       </c>
-      <c r="H7" s="22"/>
-      <c r="I7" s="22"/>
-      <c r="J7" s="22"/>
-      <c r="K7" s="22"/>
-      <c r="L7" s="22"/>
-      <c r="M7" s="22"/>
-      <c r="N7" s="22"/>
-      <c r="O7" s="22"/>
+      <c r="H7" s="23"/>
+      <c r="I7" s="23"/>
+      <c r="J7" s="23"/>
+      <c r="K7" s="23"/>
+      <c r="L7" s="23"/>
+      <c r="M7" s="23"/>
+      <c r="N7" s="23"/>
+      <c r="O7" s="23"/>
     </row>
     <row r="8" spans="1:17">
       <c r="B8" s="3"/>
-      <c r="C8" s="22"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="22"/>
-      <c r="H8" s="22"/>
-      <c r="I8" s="22"/>
-      <c r="J8" s="22"/>
-      <c r="K8" s="22"/>
-      <c r="L8" s="22"/>
-      <c r="M8" s="22"/>
-      <c r="N8" s="22"/>
-      <c r="O8" s="22"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="23"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="23"/>
+      <c r="I8" s="23"/>
+      <c r="J8" s="23"/>
+      <c r="K8" s="23"/>
+      <c r="L8" s="23"/>
+      <c r="M8" s="23"/>
+      <c r="N8" s="23"/>
+      <c r="O8" s="23"/>
     </row>
     <row r="9" spans="1:17">
       <c r="B9" s="3"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="22"/>
-      <c r="H9" s="22"/>
-      <c r="I9" s="22"/>
-      <c r="J9" s="22"/>
-      <c r="K9" s="22"/>
-      <c r="L9" s="22"/>
-      <c r="M9" s="22"/>
-      <c r="N9" s="22"/>
-      <c r="O9" s="22"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="23"/>
+      <c r="I9" s="23"/>
+      <c r="J9" s="23"/>
+      <c r="K9" s="23"/>
+      <c r="L9" s="23"/>
+      <c r="M9" s="23"/>
+      <c r="N9" s="23"/>
+      <c r="O9" s="23"/>
     </row>
     <row r="10" spans="1:17">
       <c r="B10" s="3"/>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="22"/>
-      <c r="H10" s="22"/>
-      <c r="I10" s="22"/>
-      <c r="J10" s="22"/>
-      <c r="K10" s="22"/>
-      <c r="L10" s="22"/>
-      <c r="M10" s="22"/>
-      <c r="N10" s="22"/>
-      <c r="O10" s="22"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="23"/>
+      <c r="G10" s="23"/>
+      <c r="H10" s="23"/>
+      <c r="I10" s="23"/>
+      <c r="J10" s="23"/>
+      <c r="K10" s="23"/>
+      <c r="L10" s="23"/>
+      <c r="M10" s="23"/>
+      <c r="N10" s="23"/>
+      <c r="O10" s="23"/>
     </row>
     <row r="11" spans="1:17">
       <c r="B11" s="3"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="22"/>
-      <c r="G11" s="22"/>
-      <c r="H11" s="22"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="22"/>
-      <c r="K11" s="22"/>
-      <c r="L11" s="22"/>
-      <c r="M11" s="22"/>
-      <c r="N11" s="22"/>
-      <c r="O11" s="22"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="23"/>
+      <c r="G11" s="23"/>
+      <c r="H11" s="23"/>
+      <c r="I11" s="23"/>
+      <c r="J11" s="23"/>
+      <c r="K11" s="23"/>
+      <c r="L11" s="23"/>
+      <c r="M11" s="23"/>
+      <c r="N11" s="23"/>
+      <c r="O11" s="23"/>
     </row>
     <row r="12" spans="1:17">
       <c r="B12" s="3"/>
-      <c r="C12" s="22"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="22"/>
-      <c r="H12" s="22"/>
-      <c r="I12" s="22"/>
-      <c r="J12" s="22"/>
-      <c r="K12" s="22"/>
-      <c r="L12" s="22"/>
-      <c r="M12" s="22"/>
-      <c r="N12" s="22"/>
-      <c r="O12" s="22"/>
+      <c r="C12" s="23"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="23"/>
+      <c r="G12" s="23"/>
+      <c r="H12" s="23"/>
+      <c r="I12" s="23"/>
+      <c r="J12" s="23"/>
+      <c r="K12" s="23"/>
+      <c r="L12" s="23"/>
+      <c r="M12" s="23"/>
+      <c r="N12" s="23"/>
+      <c r="O12" s="23"/>
     </row>
     <row r="13" spans="1:17">
       <c r="B13" s="3"/>
-      <c r="C13" s="22"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="22"/>
-      <c r="H13" s="22"/>
-      <c r="I13" s="22"/>
-      <c r="J13" s="22"/>
-      <c r="K13" s="22"/>
-      <c r="L13" s="22"/>
-      <c r="M13" s="22"/>
-      <c r="N13" s="22"/>
-      <c r="O13" s="22"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="23"/>
+      <c r="H13" s="23"/>
+      <c r="I13" s="23"/>
+      <c r="J13" s="23"/>
+      <c r="K13" s="23"/>
+      <c r="L13" s="23"/>
+      <c r="M13" s="23"/>
+      <c r="N13" s="23"/>
+      <c r="O13" s="23"/>
     </row>
     <row r="14" spans="1:17">
       <c r="B14" s="3"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="22"/>
-      <c r="H14" s="22"/>
-      <c r="I14" s="22"/>
-      <c r="J14" s="22"/>
-      <c r="K14" s="22"/>
-      <c r="L14" s="22"/>
-      <c r="M14" s="22"/>
-      <c r="N14" s="22"/>
-      <c r="O14" s="22"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="23"/>
+      <c r="H14" s="23"/>
+      <c r="I14" s="23"/>
+      <c r="J14" s="23"/>
+      <c r="K14" s="23"/>
+      <c r="L14" s="23"/>
+      <c r="M14" s="23"/>
+      <c r="N14" s="23"/>
+      <c r="O14" s="23"/>
     </row>
     <row r="15" spans="1:17">
       <c r="B15" s="3"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="22"/>
-      <c r="I15" s="22"/>
-      <c r="J15" s="22"/>
-      <c r="K15" s="22"/>
-      <c r="L15" s="22"/>
-      <c r="M15" s="22"/>
-      <c r="N15" s="22"/>
-      <c r="O15" s="22"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23"/>
+      <c r="I15" s="23"/>
+      <c r="J15" s="23"/>
+      <c r="K15" s="23"/>
+      <c r="L15" s="23"/>
+      <c r="M15" s="23"/>
+      <c r="N15" s="23"/>
+      <c r="O15" s="23"/>
     </row>
     <row r="16" spans="1:17">
       <c r="B16" s="3"/>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="22"/>
-      <c r="H16" s="22"/>
-      <c r="I16" s="22"/>
-      <c r="J16" s="22"/>
-      <c r="K16" s="22"/>
-      <c r="L16" s="22"/>
-      <c r="M16" s="22"/>
-      <c r="N16" s="22"/>
-      <c r="O16" s="22"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="23"/>
+      <c r="G16" s="23"/>
+      <c r="H16" s="23"/>
+      <c r="I16" s="23"/>
+      <c r="J16" s="23"/>
+      <c r="K16" s="23"/>
+      <c r="L16" s="23"/>
+      <c r="M16" s="23"/>
+      <c r="N16" s="23"/>
+      <c r="O16" s="23"/>
     </row>
     <row r="17" spans="2:15">
       <c r="B17" s="3"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="22"/>
-      <c r="H17" s="22"/>
-      <c r="I17" s="22"/>
-      <c r="J17" s="22"/>
-      <c r="K17" s="22"/>
-      <c r="L17" s="22"/>
-      <c r="M17" s="22"/>
-      <c r="N17" s="22"/>
-      <c r="O17" s="22"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="23"/>
+      <c r="H17" s="23"/>
+      <c r="I17" s="23"/>
+      <c r="J17" s="23"/>
+      <c r="K17" s="23"/>
+      <c r="L17" s="23"/>
+      <c r="M17" s="23"/>
+      <c r="N17" s="23"/>
+      <c r="O17" s="23"/>
     </row>
     <row r="18" spans="2:15">
       <c r="B18" s="3"/>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="22"/>
-      <c r="H18" s="22"/>
-      <c r="I18" s="22"/>
-      <c r="J18" s="22"/>
-      <c r="K18" s="22"/>
-      <c r="L18" s="22"/>
-      <c r="M18" s="22"/>
-      <c r="N18" s="22"/>
-      <c r="O18" s="22"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="23"/>
+      <c r="H18" s="23"/>
+      <c r="I18" s="23"/>
+      <c r="J18" s="23"/>
+      <c r="K18" s="23"/>
+      <c r="L18" s="23"/>
+      <c r="M18" s="23"/>
+      <c r="N18" s="23"/>
+      <c r="O18" s="23"/>
     </row>
     <row r="19" spans="2:15">
       <c r="B19" s="3"/>
-      <c r="C19" s="22"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22"/>
-      <c r="G19" s="22"/>
-      <c r="H19" s="22"/>
-      <c r="I19" s="22"/>
-      <c r="J19" s="22"/>
-      <c r="K19" s="22"/>
-      <c r="L19" s="22"/>
-      <c r="M19" s="22"/>
-      <c r="N19" s="22"/>
-      <c r="O19" s="22"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="23"/>
+      <c r="I19" s="23"/>
+      <c r="J19" s="23"/>
+      <c r="K19" s="23"/>
+      <c r="L19" s="23"/>
+      <c r="M19" s="23"/>
+      <c r="N19" s="23"/>
+      <c r="O19" s="23"/>
     </row>
     <row r="20" spans="2:15">
       <c r="B20" s="3"/>
-      <c r="C20" s="22"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="22"/>
-      <c r="H20" s="22"/>
-      <c r="I20" s="22"/>
-      <c r="J20" s="22"/>
-      <c r="K20" s="22"/>
-      <c r="L20" s="22"/>
-      <c r="M20" s="22"/>
-      <c r="N20" s="22"/>
-      <c r="O20" s="22"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="23"/>
+      <c r="F20" s="23"/>
+      <c r="G20" s="23"/>
+      <c r="H20" s="23"/>
+      <c r="I20" s="23"/>
+      <c r="J20" s="23"/>
+      <c r="K20" s="23"/>
+      <c r="L20" s="23"/>
+      <c r="M20" s="23"/>
+      <c r="N20" s="23"/>
+      <c r="O20" s="23"/>
     </row>
     <row r="21" spans="2:15">
       <c r="B21" s="3"/>
-      <c r="C21" s="22"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="22"/>
-      <c r="F21" s="22"/>
-      <c r="G21" s="22"/>
-      <c r="H21" s="22"/>
-      <c r="I21" s="22"/>
-      <c r="J21" s="22"/>
-      <c r="K21" s="22"/>
-      <c r="L21" s="22"/>
-      <c r="M21" s="22"/>
-      <c r="N21" s="22"/>
-      <c r="O21" s="22"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="23"/>
+      <c r="H21" s="23"/>
+      <c r="I21" s="23"/>
+      <c r="J21" s="23"/>
+      <c r="K21" s="23"/>
+      <c r="L21" s="23"/>
+      <c r="M21" s="23"/>
+      <c r="N21" s="23"/>
+      <c r="O21" s="23"/>
     </row>
     <row r="22" spans="2:15">
       <c r="B22" s="3"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="22"/>
-      <c r="J22" s="22"/>
-      <c r="K22" s="22"/>
-      <c r="L22" s="22"/>
-      <c r="M22" s="22"/>
-      <c r="N22" s="22"/>
-      <c r="O22" s="22"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="23"/>
+      <c r="G22" s="23"/>
+      <c r="H22" s="23"/>
+      <c r="I22" s="23"/>
+      <c r="J22" s="23"/>
+      <c r="K22" s="23"/>
+      <c r="L22" s="23"/>
+      <c r="M22" s="23"/>
+      <c r="N22" s="23"/>
+      <c r="O22" s="23"/>
     </row>
     <row r="23" spans="2:15">
       <c r="B23" s="3"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
-      <c r="G23" s="22"/>
-      <c r="H23" s="22"/>
-      <c r="I23" s="22"/>
-      <c r="J23" s="22"/>
-      <c r="K23" s="22"/>
-      <c r="L23" s="22"/>
-      <c r="M23" s="22"/>
-      <c r="N23" s="22"/>
-      <c r="O23" s="22"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="23"/>
+      <c r="H23" s="23"/>
+      <c r="I23" s="23"/>
+      <c r="J23" s="23"/>
+      <c r="K23" s="23"/>
+      <c r="L23" s="23"/>
+      <c r="M23" s="23"/>
+      <c r="N23" s="23"/>
+      <c r="O23" s="23"/>
     </row>
     <row r="24" spans="2:15">
       <c r="B24" s="3"/>
-      <c r="C24" s="22"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="22"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="22"/>
-      <c r="H24" s="22"/>
-      <c r="I24" s="22"/>
-      <c r="J24" s="22"/>
-      <c r="K24" s="22"/>
-      <c r="L24" s="22"/>
-      <c r="M24" s="22"/>
-      <c r="N24" s="22"/>
-      <c r="O24" s="22"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="23"/>
+      <c r="E24" s="23"/>
+      <c r="F24" s="23"/>
+      <c r="G24" s="23"/>
+      <c r="H24" s="23"/>
+      <c r="I24" s="23"/>
+      <c r="J24" s="23"/>
+      <c r="K24" s="23"/>
+      <c r="L24" s="23"/>
+      <c r="M24" s="23"/>
+      <c r="N24" s="23"/>
+      <c r="O24" s="23"/>
     </row>
     <row r="25" spans="2:15">
       <c r="B25" s="3"/>
-      <c r="C25" s="22"/>
-      <c r="D25" s="22"/>
-      <c r="E25" s="22"/>
-      <c r="F25" s="22"/>
-      <c r="G25" s="22"/>
-      <c r="H25" s="22"/>
-      <c r="I25" s="22"/>
-      <c r="J25" s="22"/>
-      <c r="K25" s="22"/>
-      <c r="L25" s="22"/>
-      <c r="M25" s="22"/>
-      <c r="N25" s="22"/>
-      <c r="O25" s="22"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="23"/>
+      <c r="G25" s="23"/>
+      <c r="H25" s="23"/>
+      <c r="I25" s="23"/>
+      <c r="J25" s="23"/>
+      <c r="K25" s="23"/>
+      <c r="L25" s="23"/>
+      <c r="M25" s="23"/>
+      <c r="N25" s="23"/>
+      <c r="O25" s="23"/>
     </row>
     <row r="26" spans="2:15">
       <c r="B26" s="3"/>
-      <c r="C26" s="22"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="22"/>
-      <c r="F26" s="22"/>
-      <c r="G26" s="22"/>
-      <c r="H26" s="22"/>
-      <c r="I26" s="22"/>
-      <c r="J26" s="22"/>
-      <c r="K26" s="22"/>
-      <c r="L26" s="22"/>
-      <c r="M26" s="22"/>
-      <c r="N26" s="22"/>
-      <c r="O26" s="22"/>
+      <c r="C26" s="23"/>
+      <c r="D26" s="23"/>
+      <c r="E26" s="23"/>
+      <c r="F26" s="23"/>
+      <c r="G26" s="23"/>
+      <c r="H26" s="23"/>
+      <c r="I26" s="23"/>
+      <c r="J26" s="23"/>
+      <c r="K26" s="23"/>
+      <c r="L26" s="23"/>
+      <c r="M26" s="23"/>
+      <c r="N26" s="23"/>
+      <c r="O26" s="23"/>
     </row>
     <row r="27" spans="2:15">
       <c r="B27" s="3"/>
-      <c r="C27" s="22"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="22"/>
-      <c r="F27" s="22"/>
-      <c r="G27" s="22"/>
-      <c r="H27" s="22"/>
-      <c r="I27" s="22"/>
-      <c r="J27" s="22"/>
-      <c r="K27" s="22"/>
-      <c r="L27" s="22"/>
-      <c r="M27" s="22"/>
-      <c r="N27" s="22"/>
-      <c r="O27" s="22"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="23"/>
+      <c r="G27" s="23"/>
+      <c r="H27" s="23"/>
+      <c r="I27" s="23"/>
+      <c r="J27" s="23"/>
+      <c r="K27" s="23"/>
+      <c r="L27" s="23"/>
+      <c r="M27" s="23"/>
+      <c r="N27" s="23"/>
+      <c r="O27" s="23"/>
     </row>
     <row r="28" spans="2:15">
       <c r="B28" s="3"/>
-      <c r="C28" s="22"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="22"/>
-      <c r="F28" s="22"/>
-      <c r="G28" s="22"/>
-      <c r="H28" s="22"/>
-      <c r="I28" s="22"/>
-      <c r="J28" s="22"/>
-      <c r="K28" s="22"/>
-      <c r="L28" s="22"/>
-      <c r="M28" s="22"/>
-      <c r="N28" s="22"/>
-      <c r="O28" s="22"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="23"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="23"/>
+      <c r="G28" s="23"/>
+      <c r="H28" s="23"/>
+      <c r="I28" s="23"/>
+      <c r="J28" s="23"/>
+      <c r="K28" s="23"/>
+      <c r="L28" s="23"/>
+      <c r="M28" s="23"/>
+      <c r="N28" s="23"/>
+      <c r="O28" s="23"/>
     </row>
     <row r="29" spans="2:15">
       <c r="B29" s="3"/>
-      <c r="C29" s="22"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="22"/>
-      <c r="F29" s="22"/>
-      <c r="G29" s="22"/>
-      <c r="H29" s="22"/>
-      <c r="I29" s="22"/>
-      <c r="J29" s="22"/>
-      <c r="K29" s="22"/>
-      <c r="L29" s="22"/>
-      <c r="M29" s="22"/>
-      <c r="N29" s="22"/>
-      <c r="O29" s="22"/>
+      <c r="C29" s="23"/>
+      <c r="D29" s="23"/>
+      <c r="E29" s="23"/>
+      <c r="F29" s="23"/>
+      <c r="G29" s="23"/>
+      <c r="H29" s="23"/>
+      <c r="I29" s="23"/>
+      <c r="J29" s="23"/>
+      <c r="K29" s="23"/>
+      <c r="L29" s="23"/>
+      <c r="M29" s="23"/>
+      <c r="N29" s="23"/>
+      <c r="O29" s="23"/>
     </row>
     <row r="30" spans="2:15">
       <c r="B30" s="3"/>
-      <c r="C30" s="22"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="22"/>
-      <c r="F30" s="22"/>
-      <c r="G30" s="22"/>
-      <c r="H30" s="22"/>
-      <c r="I30" s="22"/>
-      <c r="J30" s="22"/>
-      <c r="K30" s="22"/>
-      <c r="L30" s="22"/>
-      <c r="M30" s="22"/>
-      <c r="N30" s="22"/>
-      <c r="O30" s="22"/>
+      <c r="C30" s="23"/>
+      <c r="D30" s="23"/>
+      <c r="E30" s="23"/>
+      <c r="F30" s="23"/>
+      <c r="G30" s="23"/>
+      <c r="H30" s="23"/>
+      <c r="I30" s="23"/>
+      <c r="J30" s="23"/>
+      <c r="K30" s="23"/>
+      <c r="L30" s="23"/>
+      <c r="M30" s="23"/>
+      <c r="N30" s="23"/>
+      <c r="O30" s="23"/>
     </row>
     <row r="31" spans="2:15">
       <c r="B31" s="3"/>
-      <c r="C31" s="22"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="22"/>
-      <c r="F31" s="22"/>
-      <c r="G31" s="22"/>
-      <c r="H31" s="22"/>
-      <c r="I31" s="22"/>
-      <c r="J31" s="22"/>
-      <c r="K31" s="22"/>
-      <c r="L31" s="22"/>
-      <c r="M31" s="22"/>
-      <c r="N31" s="22"/>
-      <c r="O31" s="22"/>
+      <c r="C31" s="23"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="23"/>
+      <c r="G31" s="23"/>
+      <c r="H31" s="23"/>
+      <c r="I31" s="23"/>
+      <c r="J31" s="23"/>
+      <c r="K31" s="23"/>
+      <c r="L31" s="23"/>
+      <c r="M31" s="23"/>
+      <c r="N31" s="23"/>
+      <c r="O31" s="23"/>
     </row>
     <row r="32" spans="2:15">
       <c r="B32" s="3"/>
-      <c r="C32" s="22"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="22"/>
-      <c r="F32" s="22"/>
-      <c r="G32" s="22"/>
-      <c r="H32" s="22"/>
-      <c r="I32" s="22"/>
-      <c r="J32" s="22"/>
-      <c r="K32" s="22"/>
-      <c r="L32" s="22"/>
-      <c r="M32" s="22"/>
-      <c r="N32" s="22"/>
-      <c r="O32" s="22"/>
+      <c r="C32" s="23"/>
+      <c r="D32" s="23"/>
+      <c r="E32" s="23"/>
+      <c r="F32" s="23"/>
+      <c r="G32" s="23"/>
+      <c r="H32" s="23"/>
+      <c r="I32" s="23"/>
+      <c r="J32" s="23"/>
+      <c r="K32" s="23"/>
+      <c r="L32" s="23"/>
+      <c r="M32" s="23"/>
+      <c r="N32" s="23"/>
+      <c r="O32" s="23"/>
     </row>
     <row r="33" spans="2:15">
       <c r="B33" s="3"/>
-      <c r="C33" s="22"/>
-      <c r="D33" s="22"/>
-      <c r="E33" s="22"/>
-      <c r="F33" s="22"/>
-      <c r="G33" s="22"/>
-      <c r="H33" s="22"/>
-      <c r="I33" s="22"/>
-      <c r="J33" s="22"/>
-      <c r="K33" s="22"/>
-      <c r="L33" s="22"/>
-      <c r="M33" s="22"/>
-      <c r="N33" s="22"/>
-      <c r="O33" s="22"/>
+      <c r="C33" s="23"/>
+      <c r="D33" s="23"/>
+      <c r="E33" s="23"/>
+      <c r="F33" s="23"/>
+      <c r="G33" s="23"/>
+      <c r="H33" s="23"/>
+      <c r="I33" s="23"/>
+      <c r="J33" s="23"/>
+      <c r="K33" s="23"/>
+      <c r="L33" s="23"/>
+      <c r="M33" s="23"/>
+      <c r="N33" s="23"/>
+      <c r="O33" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="122">
-    <mergeCell ref="M7:O7"/>
-    <mergeCell ref="M8:O8"/>
-    <mergeCell ref="M9:O9"/>
-    <mergeCell ref="M10:O10"/>
-    <mergeCell ref="M11:O11"/>
-    <mergeCell ref="M12:O12"/>
-    <mergeCell ref="M13:O13"/>
-    <mergeCell ref="M14:O14"/>
-    <mergeCell ref="G7:L7"/>
-    <mergeCell ref="G8:L8"/>
-    <mergeCell ref="G9:L9"/>
-    <mergeCell ref="G10:L10"/>
-    <mergeCell ref="G11:L11"/>
-    <mergeCell ref="G12:L12"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="G33:L33"/>
+    <mergeCell ref="M33:O33"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="G31:L31"/>
+    <mergeCell ref="M31:O31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="G32:L32"/>
+    <mergeCell ref="M32:O32"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="G29:L29"/>
+    <mergeCell ref="M29:O29"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="G30:L30"/>
+    <mergeCell ref="M30:O30"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="G27:L27"/>
+    <mergeCell ref="M27:O27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="G28:L28"/>
+    <mergeCell ref="M28:O28"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G25:L25"/>
+    <mergeCell ref="M25:O25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="G26:L26"/>
+    <mergeCell ref="M26:O26"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="G23:L23"/>
+    <mergeCell ref="M23:O23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="G24:L24"/>
+    <mergeCell ref="M24:O24"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="G21:L21"/>
+    <mergeCell ref="M21:O21"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="G22:L22"/>
+    <mergeCell ref="M22:O22"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="G19:L19"/>
+    <mergeCell ref="M19:O19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:L20"/>
+    <mergeCell ref="M20:O20"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:L17"/>
+    <mergeCell ref="M17:O17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="G18:L18"/>
+    <mergeCell ref="M18:O18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:L15"/>
+    <mergeCell ref="M15:O15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:L16"/>
+    <mergeCell ref="M16:O16"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="M5:O5"/>
+    <mergeCell ref="G5:L5"/>
+    <mergeCell ref="M6:O6"/>
+    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="E1:M2"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:L6"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="G13:L13"/>
     <mergeCell ref="C14:D14"/>
@@ -12028,96 +12116,20 @@
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="G14:L14"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="M5:O5"/>
-    <mergeCell ref="G5:L5"/>
-    <mergeCell ref="M6:O6"/>
-    <mergeCell ref="A1:D2"/>
-    <mergeCell ref="E1:M2"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:L6"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:L17"/>
-    <mergeCell ref="M17:O17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="G18:L18"/>
-    <mergeCell ref="M18:O18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:L15"/>
-    <mergeCell ref="M15:O15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:L16"/>
-    <mergeCell ref="M16:O16"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="G21:L21"/>
-    <mergeCell ref="M21:O21"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="G22:L22"/>
-    <mergeCell ref="M22:O22"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="G19:L19"/>
-    <mergeCell ref="M19:O19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:L20"/>
-    <mergeCell ref="M20:O20"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="G25:L25"/>
-    <mergeCell ref="M25:O25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="G26:L26"/>
-    <mergeCell ref="M26:O26"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="G23:L23"/>
-    <mergeCell ref="M23:O23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="G24:L24"/>
-    <mergeCell ref="M24:O24"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="G29:L29"/>
-    <mergeCell ref="M29:O29"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="G30:L30"/>
-    <mergeCell ref="M30:O30"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="G27:L27"/>
-    <mergeCell ref="M27:O27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="G28:L28"/>
-    <mergeCell ref="M28:O28"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="G33:L33"/>
-    <mergeCell ref="M33:O33"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="G31:L31"/>
-    <mergeCell ref="M31:O31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="G32:L32"/>
-    <mergeCell ref="M32:O32"/>
+    <mergeCell ref="M7:O7"/>
+    <mergeCell ref="M8:O8"/>
+    <mergeCell ref="M9:O9"/>
+    <mergeCell ref="M10:O10"/>
+    <mergeCell ref="M11:O11"/>
+    <mergeCell ref="M12:O12"/>
+    <mergeCell ref="M13:O13"/>
+    <mergeCell ref="M14:O14"/>
+    <mergeCell ref="G7:L7"/>
+    <mergeCell ref="G8:L8"/>
+    <mergeCell ref="G9:L9"/>
+    <mergeCell ref="G10:L10"/>
+    <mergeCell ref="G11:L11"/>
+    <mergeCell ref="G12:L12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -12151,20 +12163,20 @@
       <c r="K1" s="25"/>
       <c r="L1" s="25"/>
       <c r="M1" s="25"/>
-      <c r="N1" s="22" t="s">
+      <c r="N1" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="O1" s="22"/>
-      <c r="P1" s="22" t="s">
+      <c r="O1" s="23"/>
+      <c r="P1" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="Q1" s="22"/>
-      <c r="R1" s="22" t="s">
+      <c r="Q1" s="23"/>
+      <c r="R1" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="22"/>
-      <c r="T1" s="22"/>
-      <c r="U1" s="22"/>
+      <c r="S1" s="23"/>
+      <c r="T1" s="23"/>
+      <c r="U1" s="23"/>
     </row>
     <row r="2" spans="1:26">
       <c r="A2" s="25"/>
@@ -12184,21 +12196,21 @@
       <c r="K2" s="25"/>
       <c r="L2" s="25"/>
       <c r="M2" s="25"/>
-      <c r="N2" s="22" t="s">
+      <c r="N2" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="O2" s="22"/>
+      <c r="O2" s="23"/>
       <c r="P2" s="24">
         <f>DATE(2026,4,6)</f>
         <v>46118</v>
       </c>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="22" t="s">
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="S2" s="22"/>
-      <c r="T2" s="22"/>
-      <c r="U2" s="22"/>
+      <c r="S2" s="23"/>
+      <c r="T2" s="23"/>
+      <c r="U2" s="23"/>
     </row>
     <row r="5" spans="1:26">
       <c r="B5" s="7" t="s">
@@ -12229,239 +12241,239 @@
       <c r="B13" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="23" t="s">
         <v>162</v>
       </c>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22" t="s">
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="23" t="s">
         <v>163</v>
       </c>
-      <c r="G13" s="22"/>
-      <c r="H13" s="22" t="s">
+      <c r="G13" s="23"/>
+      <c r="H13" s="23" t="s">
         <v>184</v>
       </c>
-      <c r="I13" s="22"/>
-      <c r="J13" s="22"/>
-      <c r="K13" s="22" t="s">
+      <c r="I13" s="23"/>
+      <c r="J13" s="23"/>
+      <c r="K13" s="23" t="s">
         <v>190</v>
       </c>
-      <c r="L13" s="22"/>
-      <c r="M13" s="22"/>
-      <c r="N13" s="22" t="s">
+      <c r="L13" s="23"/>
+      <c r="M13" s="23"/>
+      <c r="N13" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="O13" s="22"/>
-      <c r="P13" s="22"/>
-      <c r="Q13" s="22"/>
-      <c r="R13" s="22"/>
-      <c r="S13" s="22"/>
-      <c r="T13" s="22" t="s">
+      <c r="O13" s="23"/>
+      <c r="P13" s="23"/>
+      <c r="Q13" s="23"/>
+      <c r="R13" s="23"/>
+      <c r="S13" s="23"/>
+      <c r="T13" s="23" t="s">
         <v>165</v>
       </c>
-      <c r="U13" s="22"/>
-      <c r="V13" s="22"/>
-      <c r="W13" s="22"/>
-      <c r="X13" s="22" t="s">
+      <c r="U13" s="23"/>
+      <c r="V13" s="23"/>
+      <c r="W13" s="23"/>
+      <c r="X13" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="Y13" s="22"/>
-      <c r="Z13" s="22"/>
+      <c r="Y13" s="23"/>
+      <c r="Z13" s="23"/>
     </row>
     <row r="14" spans="1:26">
       <c r="B14" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="C14" s="22" t="s">
+      <c r="C14" s="23" t="s">
         <v>170</v>
       </c>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22" t="s">
+      <c r="D14" s="23"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="23" t="s">
         <v>189</v>
       </c>
-      <c r="G14" s="22"/>
-      <c r="H14" s="22" t="s">
+      <c r="G14" s="23"/>
+      <c r="H14" s="23" t="s">
         <v>186</v>
       </c>
-      <c r="I14" s="22"/>
-      <c r="J14" s="22"/>
-      <c r="K14" s="22" t="s">
+      <c r="I14" s="23"/>
+      <c r="J14" s="23"/>
+      <c r="K14" s="23" t="s">
         <v>188</v>
       </c>
-      <c r="L14" s="22"/>
-      <c r="M14" s="22"/>
-      <c r="N14" s="22" t="s">
+      <c r="L14" s="23"/>
+      <c r="M14" s="23"/>
+      <c r="N14" s="23" t="s">
         <v>178</v>
       </c>
-      <c r="O14" s="22"/>
-      <c r="P14" s="22"/>
-      <c r="Q14" s="22"/>
-      <c r="R14" s="22"/>
-      <c r="S14" s="22"/>
-      <c r="T14" s="22" t="s">
+      <c r="O14" s="23"/>
+      <c r="P14" s="23"/>
+      <c r="Q14" s="23"/>
+      <c r="R14" s="23"/>
+      <c r="S14" s="23"/>
+      <c r="T14" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="U14" s="22"/>
-      <c r="V14" s="22"/>
-      <c r="W14" s="22"/>
-      <c r="X14" s="22"/>
-      <c r="Y14" s="22"/>
-      <c r="Z14" s="22"/>
+      <c r="U14" s="23"/>
+      <c r="V14" s="23"/>
+      <c r="W14" s="23"/>
+      <c r="X14" s="23"/>
+      <c r="Y14" s="23"/>
+      <c r="Z14" s="23"/>
     </row>
     <row r="15" spans="1:26">
       <c r="B15" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="C15" s="22" t="s">
+      <c r="C15" s="23" t="s">
         <v>171</v>
       </c>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22" t="s">
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="G15" s="22"/>
-      <c r="H15" s="22" t="s">
+      <c r="G15" s="23"/>
+      <c r="H15" s="23" t="s">
         <v>185</v>
       </c>
-      <c r="I15" s="22"/>
-      <c r="J15" s="22"/>
-      <c r="K15" s="22" t="s">
+      <c r="I15" s="23"/>
+      <c r="J15" s="23"/>
+      <c r="K15" s="23" t="s">
         <v>191</v>
       </c>
-      <c r="L15" s="22"/>
-      <c r="M15" s="22"/>
-      <c r="N15" s="22" t="s">
+      <c r="L15" s="23"/>
+      <c r="M15" s="23"/>
+      <c r="N15" s="23" t="s">
         <v>177</v>
       </c>
-      <c r="O15" s="22"/>
-      <c r="P15" s="22"/>
-      <c r="Q15" s="22"/>
-      <c r="R15" s="22"/>
-      <c r="S15" s="22"/>
-      <c r="T15" s="22" t="s">
+      <c r="O15" s="23"/>
+      <c r="P15" s="23"/>
+      <c r="Q15" s="23"/>
+      <c r="R15" s="23"/>
+      <c r="S15" s="23"/>
+      <c r="T15" s="23" t="s">
         <v>174</v>
       </c>
-      <c r="U15" s="22"/>
-      <c r="V15" s="22"/>
-      <c r="W15" s="22"/>
-      <c r="X15" s="22"/>
-      <c r="Y15" s="22"/>
-      <c r="Z15" s="22"/>
+      <c r="U15" s="23"/>
+      <c r="V15" s="23"/>
+      <c r="W15" s="23"/>
+      <c r="X15" s="23"/>
+      <c r="Y15" s="23"/>
+      <c r="Z15" s="23"/>
     </row>
     <row r="16" spans="1:26">
       <c r="B16" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C16" s="22" t="s">
+      <c r="C16" s="23" t="s">
         <v>181</v>
       </c>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22" t="s">
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="23" t="s">
         <v>182</v>
       </c>
-      <c r="G16" s="22"/>
-      <c r="H16" s="22" t="s">
+      <c r="G16" s="23"/>
+      <c r="H16" s="23" t="s">
         <v>187</v>
       </c>
-      <c r="I16" s="22"/>
-      <c r="J16" s="22"/>
-      <c r="K16" s="22" t="s">
+      <c r="I16" s="23"/>
+      <c r="J16" s="23"/>
+      <c r="K16" s="23" t="s">
         <v>192</v>
       </c>
-      <c r="L16" s="22"/>
-      <c r="M16" s="22"/>
-      <c r="N16" s="22" t="s">
+      <c r="L16" s="23"/>
+      <c r="M16" s="23"/>
+      <c r="N16" s="23" t="s">
         <v>179</v>
       </c>
-      <c r="O16" s="22"/>
-      <c r="P16" s="22"/>
-      <c r="Q16" s="22"/>
-      <c r="R16" s="22"/>
-      <c r="S16" s="22"/>
-      <c r="T16" s="22" t="s">
+      <c r="O16" s="23"/>
+      <c r="P16" s="23"/>
+      <c r="Q16" s="23"/>
+      <c r="R16" s="23"/>
+      <c r="S16" s="23"/>
+      <c r="T16" s="23" t="s">
         <v>175</v>
       </c>
-      <c r="U16" s="22"/>
-      <c r="V16" s="22"/>
-      <c r="W16" s="22"/>
-      <c r="X16" s="22"/>
-      <c r="Y16" s="22"/>
-      <c r="Z16" s="22"/>
+      <c r="U16" s="23"/>
+      <c r="V16" s="23"/>
+      <c r="W16" s="23"/>
+      <c r="X16" s="23"/>
+      <c r="Y16" s="23"/>
+      <c r="Z16" s="23"/>
     </row>
     <row r="17" spans="2:26">
       <c r="B17" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="C17" s="22" t="s">
+      <c r="C17" s="23" t="s">
         <v>172</v>
       </c>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22" t="s">
+      <c r="D17" s="23"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="23" t="s">
         <v>183</v>
       </c>
-      <c r="G17" s="22"/>
-      <c r="H17" s="22" t="s">
+      <c r="G17" s="23"/>
+      <c r="H17" s="23" t="s">
         <v>185</v>
       </c>
-      <c r="I17" s="22"/>
-      <c r="J17" s="22"/>
-      <c r="K17" s="22" t="s">
+      <c r="I17" s="23"/>
+      <c r="J17" s="23"/>
+      <c r="K17" s="23" t="s">
         <v>193</v>
       </c>
-      <c r="L17" s="22"/>
-      <c r="M17" s="22"/>
-      <c r="N17" s="22" t="s">
+      <c r="L17" s="23"/>
+      <c r="M17" s="23"/>
+      <c r="N17" s="23" t="s">
         <v>180</v>
       </c>
-      <c r="O17" s="22"/>
-      <c r="P17" s="22"/>
-      <c r="Q17" s="22"/>
-      <c r="R17" s="22"/>
-      <c r="S17" s="22"/>
-      <c r="T17" s="22" t="s">
+      <c r="O17" s="23"/>
+      <c r="P17" s="23"/>
+      <c r="Q17" s="23"/>
+      <c r="R17" s="23"/>
+      <c r="S17" s="23"/>
+      <c r="T17" s="23" t="s">
         <v>176</v>
       </c>
-      <c r="U17" s="22"/>
-      <c r="V17" s="22"/>
-      <c r="W17" s="22"/>
-      <c r="X17" s="22"/>
-      <c r="Y17" s="22"/>
-      <c r="Z17" s="22"/>
+      <c r="U17" s="23"/>
+      <c r="V17" s="23"/>
+      <c r="W17" s="23"/>
+      <c r="X17" s="23"/>
+      <c r="Y17" s="23"/>
+      <c r="Z17" s="23"/>
     </row>
     <row r="18" spans="2:26">
       <c r="B18" s="3"/>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="22"/>
-      <c r="H18" s="22"/>
-      <c r="I18" s="22"/>
-      <c r="J18" s="22"/>
-      <c r="K18" s="22"/>
-      <c r="L18" s="22"/>
-      <c r="M18" s="22"/>
-      <c r="N18" s="22"/>
-      <c r="O18" s="22"/>
-      <c r="P18" s="22"/>
-      <c r="Q18" s="22"/>
-      <c r="R18" s="22"/>
-      <c r="S18" s="22"/>
-      <c r="T18" s="22"/>
-      <c r="U18" s="22"/>
-      <c r="V18" s="22"/>
-      <c r="W18" s="22"/>
-      <c r="X18" s="22"/>
-      <c r="Y18" s="22"/>
-      <c r="Z18" s="22"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="23"/>
+      <c r="H18" s="23"/>
+      <c r="I18" s="23"/>
+      <c r="J18" s="23"/>
+      <c r="K18" s="23"/>
+      <c r="L18" s="23"/>
+      <c r="M18" s="23"/>
+      <c r="N18" s="23"/>
+      <c r="O18" s="23"/>
+      <c r="P18" s="23"/>
+      <c r="Q18" s="23"/>
+      <c r="R18" s="23"/>
+      <c r="S18" s="23"/>
+      <c r="T18" s="23"/>
+      <c r="U18" s="23"/>
+      <c r="V18" s="23"/>
+      <c r="W18" s="23"/>
+      <c r="X18" s="23"/>
+      <c r="Y18" s="23"/>
+      <c r="Z18" s="23"/>
     </row>
     <row r="20" spans="2:26">
       <c r="B20" s="7" t="s">
-        <v>194</v>
+        <v>240</v>
       </c>
     </row>
     <row r="21" spans="2:26">
@@ -12502,83 +12514,83 @@
     </row>
     <row r="28" spans="2:26">
       <c r="B28" s="7" t="s">
-        <v>203</v>
+        <v>241</v>
       </c>
     </row>
     <row r="30" spans="2:26">
-      <c r="B30" s="22" t="s">
+      <c r="B30" s="23" t="s">
         <v>204</v>
       </c>
-      <c r="C30" s="22"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="22" t="s">
+      <c r="C30" s="23"/>
+      <c r="D30" s="23"/>
+      <c r="E30" s="23" t="s">
         <v>205</v>
       </c>
-      <c r="F30" s="22"/>
-      <c r="G30" s="22"/>
-      <c r="H30" s="22"/>
-      <c r="I30" s="22"/>
-      <c r="J30" s="22"/>
+      <c r="F30" s="23"/>
+      <c r="G30" s="23"/>
+      <c r="H30" s="23"/>
+      <c r="I30" s="23"/>
+      <c r="J30" s="23"/>
     </row>
     <row r="31" spans="2:26">
-      <c r="B31" s="22" t="s">
+      <c r="B31" s="23" t="s">
         <v>206</v>
       </c>
-      <c r="C31" s="22"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="22" t="s">
+      <c r="C31" s="23"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="23" t="s">
         <v>207</v>
       </c>
-      <c r="F31" s="22"/>
-      <c r="G31" s="22"/>
-      <c r="H31" s="22"/>
-      <c r="I31" s="22"/>
-      <c r="J31" s="22"/>
+      <c r="F31" s="23"/>
+      <c r="G31" s="23"/>
+      <c r="H31" s="23"/>
+      <c r="I31" s="23"/>
+      <c r="J31" s="23"/>
     </row>
     <row r="32" spans="2:26">
-      <c r="B32" s="22" t="s">
+      <c r="B32" s="23" t="s">
         <v>208</v>
       </c>
-      <c r="C32" s="22"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="22" t="s">
+      <c r="C32" s="23"/>
+      <c r="D32" s="23"/>
+      <c r="E32" s="23" t="s">
         <v>211</v>
       </c>
-      <c r="F32" s="22"/>
-      <c r="G32" s="22"/>
-      <c r="H32" s="22"/>
-      <c r="I32" s="22"/>
-      <c r="J32" s="22"/>
+      <c r="F32" s="23"/>
+      <c r="G32" s="23"/>
+      <c r="H32" s="23"/>
+      <c r="I32" s="23"/>
+      <c r="J32" s="23"/>
     </row>
     <row r="33" spans="2:19">
-      <c r="B33" s="22" t="s">
+      <c r="B33" s="23" t="s">
         <v>209</v>
       </c>
-      <c r="C33" s="22"/>
-      <c r="D33" s="22"/>
-      <c r="E33" s="22" t="s">
+      <c r="C33" s="23"/>
+      <c r="D33" s="23"/>
+      <c r="E33" s="23" t="s">
         <v>210</v>
       </c>
-      <c r="F33" s="22"/>
-      <c r="G33" s="22"/>
-      <c r="H33" s="22"/>
-      <c r="I33" s="22"/>
-      <c r="J33" s="22"/>
+      <c r="F33" s="23"/>
+      <c r="G33" s="23"/>
+      <c r="H33" s="23"/>
+      <c r="I33" s="23"/>
+      <c r="J33" s="23"/>
     </row>
     <row r="34" spans="2:19">
-      <c r="B34" s="22" t="s">
+      <c r="B34" s="23" t="s">
         <v>213</v>
       </c>
-      <c r="C34" s="22"/>
-      <c r="D34" s="22"/>
-      <c r="E34" s="22" t="s">
+      <c r="C34" s="23"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="23" t="s">
         <v>218</v>
       </c>
-      <c r="F34" s="22"/>
-      <c r="G34" s="22"/>
-      <c r="H34" s="22"/>
-      <c r="I34" s="22"/>
-      <c r="J34" s="22"/>
+      <c r="F34" s="23"/>
+      <c r="G34" s="23"/>
+      <c r="H34" s="23"/>
+      <c r="I34" s="23"/>
+      <c r="J34" s="23"/>
     </row>
     <row r="35" spans="2:19">
       <c r="B35" s="26" t="s">
@@ -12586,57 +12598,57 @@
       </c>
       <c r="C35" s="27"/>
       <c r="D35" s="28"/>
-      <c r="E35" s="22" t="s">
+      <c r="E35" s="23" t="s">
         <v>215</v>
       </c>
-      <c r="F35" s="22"/>
-      <c r="G35" s="22"/>
-      <c r="H35" s="22"/>
-      <c r="I35" s="22"/>
-      <c r="J35" s="22"/>
+      <c r="F35" s="23"/>
+      <c r="G35" s="23"/>
+      <c r="H35" s="23"/>
+      <c r="I35" s="23"/>
+      <c r="J35" s="23"/>
     </row>
     <row r="36" spans="2:19">
       <c r="B36" s="29"/>
       <c r="C36" s="30"/>
       <c r="D36" s="31"/>
-      <c r="E36" s="22" t="s">
+      <c r="E36" s="23" t="s">
         <v>214</v>
       </c>
-      <c r="F36" s="22"/>
-      <c r="G36" s="22"/>
-      <c r="H36" s="22"/>
-      <c r="I36" s="22"/>
-      <c r="J36" s="22"/>
+      <c r="F36" s="23"/>
+      <c r="G36" s="23"/>
+      <c r="H36" s="23"/>
+      <c r="I36" s="23"/>
+      <c r="J36" s="23"/>
     </row>
     <row r="37" spans="2:19">
       <c r="B37" s="29"/>
       <c r="C37" s="30"/>
       <c r="D37" s="31"/>
-      <c r="E37" s="22" t="s">
+      <c r="E37" s="23" t="s">
         <v>216</v>
       </c>
-      <c r="F37" s="22"/>
-      <c r="G37" s="22"/>
-      <c r="H37" s="22"/>
-      <c r="I37" s="22"/>
-      <c r="J37" s="22"/>
+      <c r="F37" s="23"/>
+      <c r="G37" s="23"/>
+      <c r="H37" s="23"/>
+      <c r="I37" s="23"/>
+      <c r="J37" s="23"/>
     </row>
     <row r="38" spans="2:19">
       <c r="B38" s="32"/>
       <c r="C38" s="33"/>
       <c r="D38" s="34"/>
-      <c r="E38" s="22" t="s">
+      <c r="E38" s="23" t="s">
         <v>217</v>
       </c>
-      <c r="F38" s="22"/>
-      <c r="G38" s="22"/>
-      <c r="H38" s="22"/>
-      <c r="I38" s="22"/>
-      <c r="J38" s="22"/>
+      <c r="F38" s="23"/>
+      <c r="G38" s="23"/>
+      <c r="H38" s="23"/>
+      <c r="I38" s="23"/>
+      <c r="J38" s="23"/>
     </row>
     <row r="40" spans="2:19">
       <c r="B40" s="7" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
     </row>
     <row r="41" spans="2:19">
@@ -12734,34 +12746,34 @@
     <row r="60" spans="1:26">
       <c r="A60" s="7"/>
       <c r="B60" s="7" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
     </row>
     <row r="62" spans="1:26">
       <c r="B62" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="C62" s="22" t="s">
+      <c r="C62" s="23" t="s">
         <v>171</v>
       </c>
-      <c r="D62" s="22"/>
-      <c r="E62" s="22"/>
+      <c r="D62" s="23"/>
+      <c r="E62" s="23"/>
       <c r="I62" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="J62" s="22" t="s">
+      <c r="J62" s="23" t="s">
         <v>181</v>
       </c>
-      <c r="K62" s="22"/>
-      <c r="L62" s="22"/>
+      <c r="K62" s="23"/>
+      <c r="L62" s="23"/>
       <c r="Q62" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="R62" s="22" t="s">
+      <c r="R62" s="23" t="s">
         <v>172</v>
       </c>
-      <c r="S62" s="22"/>
-      <c r="T62" s="22"/>
+      <c r="S62" s="23"/>
+      <c r="T62" s="23"/>
       <c r="W62" s="11"/>
       <c r="X62" s="11"/>
       <c r="Y62" s="11"/>
@@ -12892,19 +12904,52 @@
     </row>
   </sheetData>
   <mergeCells count="73">
-    <mergeCell ref="A1:D2"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="H1:M1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:M2"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="R2:S2"/>
-    <mergeCell ref="T2:U2"/>
-    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="C62:E62"/>
+    <mergeCell ref="J62:L62"/>
+    <mergeCell ref="R62:T62"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="E33:J33"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="E34:J34"/>
+    <mergeCell ref="B35:D38"/>
+    <mergeCell ref="E35:J35"/>
+    <mergeCell ref="E36:J36"/>
+    <mergeCell ref="E37:J37"/>
+    <mergeCell ref="E38:J38"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="E30:J30"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="E31:J31"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="E32:J32"/>
+    <mergeCell ref="X17:Z17"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="K18:M18"/>
+    <mergeCell ref="N18:S18"/>
+    <mergeCell ref="T18:W18"/>
+    <mergeCell ref="X18:Z18"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="K17:M17"/>
+    <mergeCell ref="N17:S17"/>
+    <mergeCell ref="T17:W17"/>
+    <mergeCell ref="X15:Z15"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="K16:M16"/>
+    <mergeCell ref="N16:S16"/>
+    <mergeCell ref="T16:W16"/>
+    <mergeCell ref="X16:Z16"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="H15:J15"/>
+    <mergeCell ref="K15:M15"/>
+    <mergeCell ref="N15:S15"/>
+    <mergeCell ref="T15:W15"/>
     <mergeCell ref="X13:Z13"/>
     <mergeCell ref="C14:E14"/>
     <mergeCell ref="F14:G14"/>
@@ -12919,52 +12964,19 @@
     <mergeCell ref="K13:M13"/>
     <mergeCell ref="N13:S13"/>
     <mergeCell ref="T13:W13"/>
-    <mergeCell ref="X15:Z15"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="K16:M16"/>
-    <mergeCell ref="N16:S16"/>
-    <mergeCell ref="T16:W16"/>
-    <mergeCell ref="X16:Z16"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="H15:J15"/>
-    <mergeCell ref="K15:M15"/>
-    <mergeCell ref="N15:S15"/>
-    <mergeCell ref="T15:W15"/>
-    <mergeCell ref="X17:Z17"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="K18:M18"/>
-    <mergeCell ref="N18:S18"/>
-    <mergeCell ref="T18:W18"/>
-    <mergeCell ref="X18:Z18"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="K17:M17"/>
-    <mergeCell ref="N17:S17"/>
-    <mergeCell ref="T17:W17"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="E30:J30"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="E31:J31"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="E32:J32"/>
-    <mergeCell ref="C62:E62"/>
-    <mergeCell ref="J62:L62"/>
-    <mergeCell ref="R62:T62"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="E33:J33"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="E34:J34"/>
-    <mergeCell ref="B35:D38"/>
-    <mergeCell ref="E35:J35"/>
-    <mergeCell ref="E36:J36"/>
-    <mergeCell ref="E37:J37"/>
-    <mergeCell ref="E38:J38"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:M2"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="T2:U2"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P1:Q1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -12998,14 +13010,14 @@
       <c r="K1" s="25"/>
       <c r="L1" s="25"/>
       <c r="M1" s="25"/>
-      <c r="N1" s="22" t="s">
+      <c r="N1" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="O1" s="22"/>
-      <c r="P1" s="22" t="s">
+      <c r="O1" s="23"/>
+      <c r="P1" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="Q1" s="22"/>
+      <c r="Q1" s="23"/>
     </row>
     <row r="2" spans="1:17">
       <c r="A2" s="25"/>
@@ -13021,15 +13033,15 @@
       <c r="K2" s="25"/>
       <c r="L2" s="25"/>
       <c r="M2" s="25"/>
-      <c r="N2" s="22" t="s">
+      <c r="N2" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="O2" s="22"/>
+      <c r="O2" s="23"/>
       <c r="P2" s="24">
         <f>DATE(2026,4,6)</f>
         <v>46118</v>
       </c>
-      <c r="Q2" s="22"/>
+      <c r="Q2" s="23"/>
     </row>
     <row r="4" spans="1:17">
       <c r="A4" s="1" t="s">
@@ -13047,136 +13059,156 @@
       <c r="D6" s="35"/>
     </row>
     <row r="7" spans="1:17">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="B7" s="22"/>
-      <c r="C7" s="22" t="s">
+      <c r="B7" s="23"/>
+      <c r="C7" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22" t="s">
+      <c r="D7" s="23"/>
+      <c r="E7" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="F7" s="22"/>
-      <c r="G7" s="22" t="s">
+      <c r="F7" s="23"/>
+      <c r="G7" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="H7" s="22"/>
-      <c r="I7" s="22" t="s">
+      <c r="H7" s="23"/>
+      <c r="I7" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="J7" s="22"/>
-      <c r="K7" s="22" t="s">
+      <c r="J7" s="23"/>
+      <c r="K7" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="L7" s="22"/>
+      <c r="L7" s="23"/>
     </row>
     <row r="8" spans="1:17">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="B8" s="22"/>
-      <c r="C8" s="22" t="s">
+      <c r="B8" s="23"/>
+      <c r="C8" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="D8" s="22"/>
-      <c r="E8" s="22" t="s">
+      <c r="D8" s="23"/>
+      <c r="E8" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="22"/>
-      <c r="G8" s="22" t="s">
+      <c r="F8" s="23"/>
+      <c r="G8" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="H8" s="22"/>
-      <c r="I8" s="22" t="s">
+      <c r="H8" s="23"/>
+      <c r="I8" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="J8" s="22"/>
-      <c r="K8" s="22" t="s">
+      <c r="J8" s="23"/>
+      <c r="K8" s="23" t="s">
         <v>150</v>
       </c>
-      <c r="L8" s="22"/>
+      <c r="L8" s="23"/>
     </row>
     <row r="9" spans="1:17">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="B9" s="22"/>
-      <c r="C9" s="22" t="s">
+      <c r="B9" s="23"/>
+      <c r="C9" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22" t="s">
+      <c r="D9" s="23"/>
+      <c r="E9" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="F9" s="22"/>
-      <c r="G9" s="22" t="s">
+      <c r="F9" s="23"/>
+      <c r="G9" s="23" t="s">
         <v>73</v>
       </c>
-      <c r="H9" s="22"/>
-      <c r="I9" s="22" t="s">
+      <c r="H9" s="23"/>
+      <c r="I9" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="J9" s="22"/>
-      <c r="K9" s="22"/>
-      <c r="L9" s="22"/>
+      <c r="J9" s="23"/>
+      <c r="K9" s="23"/>
+      <c r="L9" s="23"/>
     </row>
     <row r="10" spans="1:17">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="B10" s="22"/>
-      <c r="C10" s="22" t="s">
+      <c r="B10" s="23"/>
+      <c r="C10" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22" t="s">
+      <c r="D10" s="23"/>
+      <c r="E10" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="F10" s="22"/>
-      <c r="G10" s="22" t="s">
+      <c r="F10" s="23"/>
+      <c r="G10" s="23" t="s">
         <v>73</v>
       </c>
-      <c r="H10" s="22"/>
-      <c r="I10" s="22" t="s">
+      <c r="H10" s="23"/>
+      <c r="I10" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="J10" s="22"/>
-      <c r="K10" s="22"/>
-      <c r="L10" s="22"/>
+      <c r="J10" s="23"/>
+      <c r="K10" s="23"/>
+      <c r="L10" s="23"/>
     </row>
     <row r="11" spans="1:17">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="B11" s="22"/>
-      <c r="C11" s="22" t="s">
+      <c r="B11" s="23"/>
+      <c r="C11" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22" t="s">
+      <c r="D11" s="23"/>
+      <c r="E11" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="F11" s="22"/>
-      <c r="G11" s="22" t="s">
+      <c r="F11" s="23"/>
+      <c r="G11" s="23" t="s">
         <v>73</v>
       </c>
-      <c r="H11" s="22"/>
-      <c r="I11" s="22" t="s">
+      <c r="H11" s="23"/>
+      <c r="I11" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="J11" s="22"/>
-      <c r="K11" s="22"/>
-      <c r="L11" s="22"/>
+      <c r="J11" s="23"/>
+      <c r="K11" s="23"/>
+      <c r="L11" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="E1:M2"/>
+    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
     <mergeCell ref="G10:H10"/>
     <mergeCell ref="G11:H11"/>
     <mergeCell ref="I7:J7"/>
@@ -13185,31 +13217,11 @@
     <mergeCell ref="I10:J10"/>
     <mergeCell ref="I11:J11"/>
     <mergeCell ref="G7:H7"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="E1:M2"/>
-    <mergeCell ref="A1:D2"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="K11:L11"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E8:F11">
@@ -13251,20 +13263,20 @@
       <c r="K1" s="25"/>
       <c r="L1" s="25"/>
       <c r="M1" s="25"/>
-      <c r="N1" s="22" t="s">
+      <c r="N1" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="O1" s="22"/>
-      <c r="P1" s="22" t="s">
+      <c r="O1" s="23"/>
+      <c r="P1" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="Q1" s="22"/>
-      <c r="R1" s="22" t="s">
+      <c r="Q1" s="23"/>
+      <c r="R1" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="22"/>
-      <c r="T1" s="22"/>
-      <c r="U1" s="22"/>
+      <c r="S1" s="23"/>
+      <c r="T1" s="23"/>
+      <c r="U1" s="23"/>
     </row>
     <row r="2" spans="1:21">
       <c r="A2" s="25"/>
@@ -13284,21 +13296,21 @@
       <c r="K2" s="25"/>
       <c r="L2" s="25"/>
       <c r="M2" s="25"/>
-      <c r="N2" s="22" t="s">
+      <c r="N2" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="O2" s="22"/>
+      <c r="O2" s="23"/>
       <c r="P2" s="24">
         <f>DATE(2026,4,6)</f>
         <v>46118</v>
       </c>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="22" t="s">
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="S2" s="22"/>
-      <c r="T2" s="22"/>
-      <c r="U2" s="22"/>
+      <c r="S2" s="23"/>
+      <c r="T2" s="23"/>
+      <c r="U2" s="23"/>
     </row>
     <row r="10" spans="1:21">
       <c r="B10" s="1" t="s">
@@ -13334,13 +13346,13 @@
       <c r="C43" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="S43" s="23" t="s">
+      <c r="S43" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="T43" s="23"/>
-      <c r="U43" s="23"/>
-      <c r="V43" s="23"/>
-      <c r="W43" s="23"/>
+      <c r="T43" s="22"/>
+      <c r="U43" s="22"/>
+      <c r="V43" s="22"/>
+      <c r="W43" s="22"/>
       <c r="Z43" s="2"/>
       <c r="AA43" s="2"/>
       <c r="AB43" s="2"/>
@@ -13349,23 +13361,23 @@
       <c r="C44" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="Z44" s="23" t="s">
+      <c r="Z44" s="22" t="s">
         <v>159</v>
       </c>
-      <c r="AA44" s="23"/>
-      <c r="AB44" s="23"/>
-      <c r="AK44" s="23" t="s">
+      <c r="AA44" s="22"/>
+      <c r="AB44" s="22"/>
+      <c r="AK44" s="22" t="s">
         <v>145</v>
       </c>
-      <c r="AL44" s="23"/>
-      <c r="AM44" s="23"/>
-      <c r="AN44" s="23"/>
-      <c r="AO44" s="23"/>
-      <c r="AP44" s="23" t="s">
+      <c r="AL44" s="22"/>
+      <c r="AM44" s="22"/>
+      <c r="AN44" s="22"/>
+      <c r="AO44" s="22"/>
+      <c r="AP44" s="22" t="s">
         <v>147</v>
       </c>
-      <c r="AQ44" s="23"/>
-      <c r="AR44" s="23"/>
+      <c r="AQ44" s="22"/>
+      <c r="AR44" s="22"/>
     </row>
     <row r="45" spans="2:44">
       <c r="C45" s="1" t="s">
@@ -13376,24 +13388,24 @@
       <c r="AG46" s="6"/>
     </row>
     <row r="47" spans="2:44">
-      <c r="G47" s="23" t="s">
+      <c r="G47" s="22" t="s">
         <v>140</v>
       </c>
-      <c r="H47" s="23"/>
-      <c r="I47" s="23"/>
-      <c r="J47" s="23"/>
-      <c r="M47" s="23" t="s">
+      <c r="H47" s="22"/>
+      <c r="I47" s="22"/>
+      <c r="J47" s="22"/>
+      <c r="M47" s="22" t="s">
         <v>141</v>
       </c>
-      <c r="N47" s="23"/>
-      <c r="O47" s="23"/>
-      <c r="P47" s="23"/>
-      <c r="S47" s="23" t="s">
+      <c r="N47" s="22"/>
+      <c r="O47" s="22"/>
+      <c r="P47" s="22"/>
+      <c r="S47" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="T47" s="23"/>
-      <c r="U47" s="23"/>
-      <c r="V47" s="23"/>
+      <c r="T47" s="22"/>
+      <c r="U47" s="22"/>
+      <c r="V47" s="22"/>
     </row>
     <row r="48" spans="2:44">
       <c r="Q48" s="1" t="s">
@@ -13422,11 +13434,13 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="AK44:AO44"/>
-    <mergeCell ref="AP44:AR44"/>
-    <mergeCell ref="G47:J47"/>
-    <mergeCell ref="M47:P47"/>
-    <mergeCell ref="S47:V47"/>
+    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="H1:M1"/>
     <mergeCell ref="S43:W43"/>
     <mergeCell ref="Z44:AB44"/>
     <mergeCell ref="R1:S1"/>
@@ -13435,13 +13449,11 @@
     <mergeCell ref="H2:M2"/>
     <mergeCell ref="R2:S2"/>
     <mergeCell ref="T2:U2"/>
-    <mergeCell ref="A1:D2"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="AK44:AO44"/>
+    <mergeCell ref="AP44:AR44"/>
+    <mergeCell ref="G47:J47"/>
+    <mergeCell ref="M47:P47"/>
+    <mergeCell ref="S47:V47"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -13737,20 +13749,20 @@
       <c r="K1" s="25"/>
       <c r="L1" s="25"/>
       <c r="M1" s="25"/>
-      <c r="N1" s="22" t="s">
+      <c r="N1" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="O1" s="22"/>
-      <c r="P1" s="22" t="s">
+      <c r="O1" s="23"/>
+      <c r="P1" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="Q1" s="22"/>
-      <c r="R1" s="22" t="s">
+      <c r="Q1" s="23"/>
+      <c r="R1" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="22"/>
-      <c r="T1" s="22"/>
-      <c r="U1" s="22"/>
+      <c r="S1" s="23"/>
+      <c r="T1" s="23"/>
+      <c r="U1" s="23"/>
     </row>
     <row r="2" spans="1:26">
       <c r="A2" s="25"/>
@@ -13770,21 +13782,21 @@
       <c r="K2" s="25"/>
       <c r="L2" s="25"/>
       <c r="M2" s="25"/>
-      <c r="N2" s="22" t="s">
+      <c r="N2" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="O2" s="22"/>
+      <c r="O2" s="23"/>
       <c r="P2" s="24">
         <f>DATE(2026,4,6)</f>
         <v>46118</v>
       </c>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="22" t="s">
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="S2" s="22"/>
-      <c r="T2" s="22"/>
-      <c r="U2" s="22"/>
+      <c r="S2" s="23"/>
+      <c r="T2" s="23"/>
+      <c r="U2" s="23"/>
     </row>
     <row r="5" spans="1:26">
       <c r="B5" s="7" t="s">
@@ -13815,235 +13827,235 @@
       <c r="B13" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="23" t="s">
         <v>162</v>
       </c>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22" t="s">
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="23" t="s">
         <v>163</v>
       </c>
-      <c r="G13" s="22"/>
-      <c r="H13" s="22" t="s">
+      <c r="G13" s="23"/>
+      <c r="H13" s="23" t="s">
         <v>184</v>
       </c>
-      <c r="I13" s="22"/>
-      <c r="J13" s="22"/>
-      <c r="K13" s="22" t="s">
+      <c r="I13" s="23"/>
+      <c r="J13" s="23"/>
+      <c r="K13" s="23" t="s">
         <v>190</v>
       </c>
-      <c r="L13" s="22"/>
-      <c r="M13" s="22"/>
-      <c r="N13" s="22" t="s">
+      <c r="L13" s="23"/>
+      <c r="M13" s="23"/>
+      <c r="N13" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="O13" s="22"/>
-      <c r="P13" s="22"/>
-      <c r="Q13" s="22"/>
-      <c r="R13" s="22"/>
-      <c r="S13" s="22"/>
-      <c r="T13" s="22" t="s">
+      <c r="O13" s="23"/>
+      <c r="P13" s="23"/>
+      <c r="Q13" s="23"/>
+      <c r="R13" s="23"/>
+      <c r="S13" s="23"/>
+      <c r="T13" s="23" t="s">
         <v>165</v>
       </c>
-      <c r="U13" s="22"/>
-      <c r="V13" s="22"/>
-      <c r="W13" s="22"/>
-      <c r="X13" s="22" t="s">
+      <c r="U13" s="23"/>
+      <c r="V13" s="23"/>
+      <c r="W13" s="23"/>
+      <c r="X13" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="Y13" s="22"/>
-      <c r="Z13" s="22"/>
+      <c r="Y13" s="23"/>
+      <c r="Z13" s="23"/>
     </row>
     <row r="14" spans="1:26">
       <c r="B14" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="C14" s="22" t="s">
+      <c r="C14" s="23" t="s">
         <v>170</v>
       </c>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22" t="s">
+      <c r="D14" s="23"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="23" t="s">
         <v>189</v>
       </c>
-      <c r="G14" s="22"/>
-      <c r="H14" s="22" t="s">
+      <c r="G14" s="23"/>
+      <c r="H14" s="23" t="s">
         <v>186</v>
       </c>
-      <c r="I14" s="22"/>
-      <c r="J14" s="22"/>
-      <c r="K14" s="22" t="s">
+      <c r="I14" s="23"/>
+      <c r="J14" s="23"/>
+      <c r="K14" s="23" t="s">
         <v>188</v>
       </c>
-      <c r="L14" s="22"/>
-      <c r="M14" s="22"/>
-      <c r="N14" s="22" t="s">
+      <c r="L14" s="23"/>
+      <c r="M14" s="23"/>
+      <c r="N14" s="23" t="s">
         <v>178</v>
       </c>
-      <c r="O14" s="22"/>
-      <c r="P14" s="22"/>
-      <c r="Q14" s="22"/>
-      <c r="R14" s="22"/>
-      <c r="S14" s="22"/>
-      <c r="T14" s="22" t="s">
+      <c r="O14" s="23"/>
+      <c r="P14" s="23"/>
+      <c r="Q14" s="23"/>
+      <c r="R14" s="23"/>
+      <c r="S14" s="23"/>
+      <c r="T14" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="U14" s="22"/>
-      <c r="V14" s="22"/>
-      <c r="W14" s="22"/>
-      <c r="X14" s="22"/>
-      <c r="Y14" s="22"/>
-      <c r="Z14" s="22"/>
+      <c r="U14" s="23"/>
+      <c r="V14" s="23"/>
+      <c r="W14" s="23"/>
+      <c r="X14" s="23"/>
+      <c r="Y14" s="23"/>
+      <c r="Z14" s="23"/>
     </row>
     <row r="15" spans="1:26">
       <c r="B15" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="C15" s="22" t="s">
+      <c r="C15" s="23" t="s">
         <v>171</v>
       </c>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22" t="s">
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="G15" s="22"/>
-      <c r="H15" s="22" t="s">
+      <c r="G15" s="23"/>
+      <c r="H15" s="23" t="s">
         <v>185</v>
       </c>
-      <c r="I15" s="22"/>
-      <c r="J15" s="22"/>
-      <c r="K15" s="22" t="s">
+      <c r="I15" s="23"/>
+      <c r="J15" s="23"/>
+      <c r="K15" s="23" t="s">
         <v>191</v>
       </c>
-      <c r="L15" s="22"/>
-      <c r="M15" s="22"/>
-      <c r="N15" s="22" t="s">
+      <c r="L15" s="23"/>
+      <c r="M15" s="23"/>
+      <c r="N15" s="23" t="s">
         <v>177</v>
       </c>
-      <c r="O15" s="22"/>
-      <c r="P15" s="22"/>
-      <c r="Q15" s="22"/>
-      <c r="R15" s="22"/>
-      <c r="S15" s="22"/>
-      <c r="T15" s="22" t="s">
+      <c r="O15" s="23"/>
+      <c r="P15" s="23"/>
+      <c r="Q15" s="23"/>
+      <c r="R15" s="23"/>
+      <c r="S15" s="23"/>
+      <c r="T15" s="23" t="s">
         <v>174</v>
       </c>
-      <c r="U15" s="22"/>
-      <c r="V15" s="22"/>
-      <c r="W15" s="22"/>
-      <c r="X15" s="22"/>
-      <c r="Y15" s="22"/>
-      <c r="Z15" s="22"/>
+      <c r="U15" s="23"/>
+      <c r="V15" s="23"/>
+      <c r="W15" s="23"/>
+      <c r="X15" s="23"/>
+      <c r="Y15" s="23"/>
+      <c r="Z15" s="23"/>
     </row>
     <row r="16" spans="1:26">
       <c r="B16" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C16" s="22" t="s">
+      <c r="C16" s="23" t="s">
         <v>181</v>
       </c>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22" t="s">
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="23" t="s">
         <v>182</v>
       </c>
-      <c r="G16" s="22"/>
-      <c r="H16" s="22" t="s">
+      <c r="G16" s="23"/>
+      <c r="H16" s="23" t="s">
         <v>187</v>
       </c>
-      <c r="I16" s="22"/>
-      <c r="J16" s="22"/>
-      <c r="K16" s="22" t="s">
+      <c r="I16" s="23"/>
+      <c r="J16" s="23"/>
+      <c r="K16" s="23" t="s">
         <v>192</v>
       </c>
-      <c r="L16" s="22"/>
-      <c r="M16" s="22"/>
-      <c r="N16" s="22" t="s">
+      <c r="L16" s="23"/>
+      <c r="M16" s="23"/>
+      <c r="N16" s="23" t="s">
         <v>179</v>
       </c>
-      <c r="O16" s="22"/>
-      <c r="P16" s="22"/>
-      <c r="Q16" s="22"/>
-      <c r="R16" s="22"/>
-      <c r="S16" s="22"/>
-      <c r="T16" s="22" t="s">
+      <c r="O16" s="23"/>
+      <c r="P16" s="23"/>
+      <c r="Q16" s="23"/>
+      <c r="R16" s="23"/>
+      <c r="S16" s="23"/>
+      <c r="T16" s="23" t="s">
         <v>175</v>
       </c>
-      <c r="U16" s="22"/>
-      <c r="V16" s="22"/>
-      <c r="W16" s="22"/>
-      <c r="X16" s="22"/>
-      <c r="Y16" s="22"/>
-      <c r="Z16" s="22"/>
+      <c r="U16" s="23"/>
+      <c r="V16" s="23"/>
+      <c r="W16" s="23"/>
+      <c r="X16" s="23"/>
+      <c r="Y16" s="23"/>
+      <c r="Z16" s="23"/>
     </row>
     <row r="17" spans="2:26">
       <c r="B17" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="C17" s="22" t="s">
+      <c r="C17" s="23" t="s">
         <v>172</v>
       </c>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22" t="s">
+      <c r="D17" s="23"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="23" t="s">
         <v>183</v>
       </c>
-      <c r="G17" s="22"/>
-      <c r="H17" s="22" t="s">
+      <c r="G17" s="23"/>
+      <c r="H17" s="23" t="s">
         <v>185</v>
       </c>
-      <c r="I17" s="22"/>
-      <c r="J17" s="22"/>
-      <c r="K17" s="22" t="s">
+      <c r="I17" s="23"/>
+      <c r="J17" s="23"/>
+      <c r="K17" s="23" t="s">
         <v>193</v>
       </c>
-      <c r="L17" s="22"/>
-      <c r="M17" s="22"/>
-      <c r="N17" s="22" t="s">
+      <c r="L17" s="23"/>
+      <c r="M17" s="23"/>
+      <c r="N17" s="23" t="s">
         <v>180</v>
       </c>
-      <c r="O17" s="22"/>
-      <c r="P17" s="22"/>
-      <c r="Q17" s="22"/>
-      <c r="R17" s="22"/>
-      <c r="S17" s="22"/>
-      <c r="T17" s="22" t="s">
+      <c r="O17" s="23"/>
+      <c r="P17" s="23"/>
+      <c r="Q17" s="23"/>
+      <c r="R17" s="23"/>
+      <c r="S17" s="23"/>
+      <c r="T17" s="23" t="s">
         <v>176</v>
       </c>
-      <c r="U17" s="22"/>
-      <c r="V17" s="22"/>
-      <c r="W17" s="22"/>
-      <c r="X17" s="22"/>
-      <c r="Y17" s="22"/>
-      <c r="Z17" s="22"/>
+      <c r="U17" s="23"/>
+      <c r="V17" s="23"/>
+      <c r="W17" s="23"/>
+      <c r="X17" s="23"/>
+      <c r="Y17" s="23"/>
+      <c r="Z17" s="23"/>
     </row>
     <row r="18" spans="2:26">
       <c r="B18" s="3"/>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="22"/>
-      <c r="H18" s="22"/>
-      <c r="I18" s="22"/>
-      <c r="J18" s="22"/>
-      <c r="K18" s="22"/>
-      <c r="L18" s="22"/>
-      <c r="M18" s="22"/>
-      <c r="N18" s="22"/>
-      <c r="O18" s="22"/>
-      <c r="P18" s="22"/>
-      <c r="Q18" s="22"/>
-      <c r="R18" s="22"/>
-      <c r="S18" s="22"/>
-      <c r="T18" s="22"/>
-      <c r="U18" s="22"/>
-      <c r="V18" s="22"/>
-      <c r="W18" s="22"/>
-      <c r="X18" s="22"/>
-      <c r="Y18" s="22"/>
-      <c r="Z18" s="22"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="23"/>
+      <c r="H18" s="23"/>
+      <c r="I18" s="23"/>
+      <c r="J18" s="23"/>
+      <c r="K18" s="23"/>
+      <c r="L18" s="23"/>
+      <c r="M18" s="23"/>
+      <c r="N18" s="23"/>
+      <c r="O18" s="23"/>
+      <c r="P18" s="23"/>
+      <c r="Q18" s="23"/>
+      <c r="R18" s="23"/>
+      <c r="S18" s="23"/>
+      <c r="T18" s="23"/>
+      <c r="U18" s="23"/>
+      <c r="V18" s="23"/>
+      <c r="W18" s="23"/>
+      <c r="X18" s="23"/>
+      <c r="Y18" s="23"/>
+      <c r="Z18" s="23"/>
     </row>
     <row r="20" spans="2:26">
       <c r="B20" s="7" t="s">
@@ -14092,79 +14104,79 @@
       </c>
     </row>
     <row r="30" spans="2:26">
-      <c r="B30" s="22" t="s">
+      <c r="B30" s="23" t="s">
         <v>204</v>
       </c>
-      <c r="C30" s="22"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="22" t="s">
+      <c r="C30" s="23"/>
+      <c r="D30" s="23"/>
+      <c r="E30" s="23" t="s">
         <v>205</v>
       </c>
-      <c r="F30" s="22"/>
-      <c r="G30" s="22"/>
-      <c r="H30" s="22"/>
-      <c r="I30" s="22"/>
-      <c r="J30" s="22"/>
+      <c r="F30" s="23"/>
+      <c r="G30" s="23"/>
+      <c r="H30" s="23"/>
+      <c r="I30" s="23"/>
+      <c r="J30" s="23"/>
     </row>
     <row r="31" spans="2:26">
-      <c r="B31" s="22" t="s">
+      <c r="B31" s="23" t="s">
         <v>206</v>
       </c>
-      <c r="C31" s="22"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="22" t="s">
+      <c r="C31" s="23"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="23" t="s">
         <v>207</v>
       </c>
-      <c r="F31" s="22"/>
-      <c r="G31" s="22"/>
-      <c r="H31" s="22"/>
-      <c r="I31" s="22"/>
-      <c r="J31" s="22"/>
+      <c r="F31" s="23"/>
+      <c r="G31" s="23"/>
+      <c r="H31" s="23"/>
+      <c r="I31" s="23"/>
+      <c r="J31" s="23"/>
     </row>
     <row r="32" spans="2:26">
-      <c r="B32" s="22" t="s">
+      <c r="B32" s="23" t="s">
         <v>208</v>
       </c>
-      <c r="C32" s="22"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="22" t="s">
+      <c r="C32" s="23"/>
+      <c r="D32" s="23"/>
+      <c r="E32" s="23" t="s">
         <v>211</v>
       </c>
-      <c r="F32" s="22"/>
-      <c r="G32" s="22"/>
-      <c r="H32" s="22"/>
-      <c r="I32" s="22"/>
-      <c r="J32" s="22"/>
+      <c r="F32" s="23"/>
+      <c r="G32" s="23"/>
+      <c r="H32" s="23"/>
+      <c r="I32" s="23"/>
+      <c r="J32" s="23"/>
     </row>
     <row r="33" spans="2:19">
-      <c r="B33" s="22" t="s">
+      <c r="B33" s="23" t="s">
         <v>209</v>
       </c>
-      <c r="C33" s="22"/>
-      <c r="D33" s="22"/>
-      <c r="E33" s="22" t="s">
+      <c r="C33" s="23"/>
+      <c r="D33" s="23"/>
+      <c r="E33" s="23" t="s">
         <v>210</v>
       </c>
-      <c r="F33" s="22"/>
-      <c r="G33" s="22"/>
-      <c r="H33" s="22"/>
-      <c r="I33" s="22"/>
-      <c r="J33" s="22"/>
+      <c r="F33" s="23"/>
+      <c r="G33" s="23"/>
+      <c r="H33" s="23"/>
+      <c r="I33" s="23"/>
+      <c r="J33" s="23"/>
     </row>
     <row r="34" spans="2:19">
-      <c r="B34" s="22" t="s">
+      <c r="B34" s="23" t="s">
         <v>213</v>
       </c>
-      <c r="C34" s="22"/>
-      <c r="D34" s="22"/>
-      <c r="E34" s="22" t="s">
+      <c r="C34" s="23"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="23" t="s">
         <v>218</v>
       </c>
-      <c r="F34" s="22"/>
-      <c r="G34" s="22"/>
-      <c r="H34" s="22"/>
-      <c r="I34" s="22"/>
-      <c r="J34" s="22"/>
+      <c r="F34" s="23"/>
+      <c r="G34" s="23"/>
+      <c r="H34" s="23"/>
+      <c r="I34" s="23"/>
+      <c r="J34" s="23"/>
     </row>
     <row r="35" spans="2:19">
       <c r="B35" s="26" t="s">
@@ -14172,53 +14184,53 @@
       </c>
       <c r="C35" s="27"/>
       <c r="D35" s="28"/>
-      <c r="E35" s="22" t="s">
+      <c r="E35" s="23" t="s">
         <v>215</v>
       </c>
-      <c r="F35" s="22"/>
-      <c r="G35" s="22"/>
-      <c r="H35" s="22"/>
-      <c r="I35" s="22"/>
-      <c r="J35" s="22"/>
+      <c r="F35" s="23"/>
+      <c r="G35" s="23"/>
+      <c r="H35" s="23"/>
+      <c r="I35" s="23"/>
+      <c r="J35" s="23"/>
     </row>
     <row r="36" spans="2:19">
       <c r="B36" s="29"/>
       <c r="C36" s="30"/>
       <c r="D36" s="31"/>
-      <c r="E36" s="22" t="s">
+      <c r="E36" s="23" t="s">
         <v>214</v>
       </c>
-      <c r="F36" s="22"/>
-      <c r="G36" s="22"/>
-      <c r="H36" s="22"/>
-      <c r="I36" s="22"/>
-      <c r="J36" s="22"/>
+      <c r="F36" s="23"/>
+      <c r="G36" s="23"/>
+      <c r="H36" s="23"/>
+      <c r="I36" s="23"/>
+      <c r="J36" s="23"/>
     </row>
     <row r="37" spans="2:19">
       <c r="B37" s="29"/>
       <c r="C37" s="30"/>
       <c r="D37" s="31"/>
-      <c r="E37" s="22" t="s">
+      <c r="E37" s="23" t="s">
         <v>216</v>
       </c>
-      <c r="F37" s="22"/>
-      <c r="G37" s="22"/>
-      <c r="H37" s="22"/>
-      <c r="I37" s="22"/>
-      <c r="J37" s="22"/>
+      <c r="F37" s="23"/>
+      <c r="G37" s="23"/>
+      <c r="H37" s="23"/>
+      <c r="I37" s="23"/>
+      <c r="J37" s="23"/>
     </row>
     <row r="38" spans="2:19">
       <c r="B38" s="32"/>
       <c r="C38" s="33"/>
       <c r="D38" s="34"/>
-      <c r="E38" s="22" t="s">
+      <c r="E38" s="23" t="s">
         <v>217</v>
       </c>
-      <c r="F38" s="22"/>
-      <c r="G38" s="22"/>
-      <c r="H38" s="22"/>
-      <c r="I38" s="22"/>
-      <c r="J38" s="22"/>
+      <c r="F38" s="23"/>
+      <c r="G38" s="23"/>
+      <c r="H38" s="23"/>
+      <c r="I38" s="23"/>
+      <c r="J38" s="23"/>
     </row>
     <row r="40" spans="2:19">
       <c r="B40" s="7" t="s">
@@ -14327,27 +14339,27 @@
       <c r="B62" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="C62" s="22" t="s">
+      <c r="C62" s="23" t="s">
         <v>171</v>
       </c>
-      <c r="D62" s="22"/>
-      <c r="E62" s="22"/>
+      <c r="D62" s="23"/>
+      <c r="E62" s="23"/>
       <c r="I62" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="J62" s="22" t="s">
+      <c r="J62" s="23" t="s">
         <v>181</v>
       </c>
-      <c r="K62" s="22"/>
-      <c r="L62" s="22"/>
+      <c r="K62" s="23"/>
+      <c r="L62" s="23"/>
       <c r="Q62" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="R62" s="22" t="s">
+      <c r="R62" s="23" t="s">
         <v>172</v>
       </c>
-      <c r="S62" s="22"/>
-      <c r="T62" s="22"/>
+      <c r="S62" s="23"/>
+      <c r="T62" s="23"/>
       <c r="W62" s="11"/>
       <c r="X62" s="11"/>
       <c r="Y62" s="11"/>
@@ -14398,46 +14410,23 @@
     </row>
   </sheetData>
   <mergeCells count="73">
-    <mergeCell ref="A1:D2"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="H1:M1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:M2"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="R2:S2"/>
-    <mergeCell ref="T2:U2"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="K13:M13"/>
-    <mergeCell ref="N13:S13"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="K15:M15"/>
-    <mergeCell ref="N15:S15"/>
-    <mergeCell ref="T15:W15"/>
-    <mergeCell ref="T13:W13"/>
-    <mergeCell ref="T14:W14"/>
-    <mergeCell ref="N14:S14"/>
-    <mergeCell ref="K14:M14"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="T18:W18"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="K16:M16"/>
-    <mergeCell ref="N16:S16"/>
-    <mergeCell ref="T16:W16"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="K17:M17"/>
-    <mergeCell ref="N17:S17"/>
-    <mergeCell ref="T17:W17"/>
-    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="E38:J38"/>
+    <mergeCell ref="B35:D38"/>
+    <mergeCell ref="R62:T62"/>
+    <mergeCell ref="C62:E62"/>
+    <mergeCell ref="J62:L62"/>
+    <mergeCell ref="E36:J36"/>
+    <mergeCell ref="E37:J37"/>
+    <mergeCell ref="E31:J31"/>
+    <mergeCell ref="E32:J32"/>
+    <mergeCell ref="E33:J33"/>
+    <mergeCell ref="E34:J34"/>
+    <mergeCell ref="E35:J35"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="E30:J30"/>
     <mergeCell ref="X18:Z18"/>
     <mergeCell ref="H13:J13"/>
@@ -14454,23 +14443,46 @@
     <mergeCell ref="F18:G18"/>
     <mergeCell ref="K18:M18"/>
     <mergeCell ref="N18:S18"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="E31:J31"/>
-    <mergeCell ref="E32:J32"/>
-    <mergeCell ref="E33:J33"/>
-    <mergeCell ref="E34:J34"/>
-    <mergeCell ref="E35:J35"/>
-    <mergeCell ref="E38:J38"/>
-    <mergeCell ref="B35:D38"/>
-    <mergeCell ref="R62:T62"/>
-    <mergeCell ref="C62:E62"/>
-    <mergeCell ref="J62:L62"/>
-    <mergeCell ref="E36:J36"/>
-    <mergeCell ref="E37:J37"/>
+    <mergeCell ref="T18:W18"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="K16:M16"/>
+    <mergeCell ref="N16:S16"/>
+    <mergeCell ref="T16:W16"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="K17:M17"/>
+    <mergeCell ref="N17:S17"/>
+    <mergeCell ref="T17:W17"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="T13:W13"/>
+    <mergeCell ref="T14:W14"/>
+    <mergeCell ref="N14:S14"/>
+    <mergeCell ref="K14:M14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="K15:M15"/>
+    <mergeCell ref="N15:S15"/>
+    <mergeCell ref="T15:W15"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="K13:M13"/>
+    <mergeCell ref="N13:S13"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:M2"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="T2:U2"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P1:Q1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
